--- a/notes/meetings/meeting-20260417/美丫丫手机页面2.0.xlsx
+++ b/notes/meetings/meeting-20260417/美丫丫手机页面2.0.xlsx
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="217">
   <si>
     <t>排行榜</t>
   </si>
@@ -270,12 +270,6 @@
     <t>日历选择器，默认当天</t>
   </si>
   <si>
-    <t>日期</t>
-  </si>
-  <si>
-    <t>2026.4.24</t>
-  </si>
-  <si>
     <t>不能随意选时间间隔</t>
   </si>
   <si>
@@ -289,9 +283,6 @@
   </si>
   <si>
     <t>本年</t>
-  </si>
-  <si>
-    <t>禁止自定义</t>
   </si>
   <si>
     <t>能不能自定义，你根据下面数据的统计规则来设定</t>
@@ -325,13 +316,10 @@
     <t>实耗榜单</t>
   </si>
   <si>
-    <t>新客排名</t>
+    <t>新会员排名</t>
   </si>
   <si>
     <t>本月：</t>
-  </si>
-  <si>
-    <t>新客量排名</t>
   </si>
   <si>
     <t>项目数排名</t>
@@ -530,7 +518,7 @@
     <t>人均客量</t>
   </si>
   <si>
-    <t>人均新客</t>
+    <t>人均新会员</t>
   </si>
   <si>
     <t>人均项目数</t>
@@ -549,6 +537,15 @@
   </si>
   <si>
     <t>以下数据默认按月</t>
+  </si>
+  <si>
+    <t>日期</t>
+  </si>
+  <si>
+    <t>2026.4.24</t>
+  </si>
+  <si>
+    <t>禁止自定义</t>
   </si>
   <si>
     <t>和员工端相同即可</t>
@@ -799,7 +796,7 @@
 时间段计算，不计算单日数据</t>
   </si>
   <si>
-    <t>新客经营</t>
+    <t>新会员经营</t>
   </si>
   <si>
     <t>新增会员数</t>
@@ -2039,13 +2036,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2911,7 +2908,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="243">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3338,16 +3335,16 @@
     <xf numFmtId="0" fontId="17" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="16" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="8" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3386,7 +3383,16 @@
     <xf numFmtId="0" fontId="20" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="17" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3416,16 +3422,16 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3434,7 +3440,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3512,10 +3518,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3533,6 +3539,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3545,7 +3560,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4223,13 +4238,9 @@
       <c r="U5" s="27"/>
       <c r="V5" s="97"/>
       <c r="Z5" s="29"/>
-      <c r="AA5" s="100" t="s">
-        <v>3</v>
-      </c>
+      <c r="AA5" s="100"/>
       <c r="AB5" s="100"/>
-      <c r="AC5" s="126" t="s">
-        <v>4</v>
-      </c>
+      <c r="AC5" s="126"/>
       <c r="AD5" s="126"/>
       <c r="AE5" s="126"/>
       <c r="AF5" s="34"/>
@@ -4246,13 +4257,9 @@
       <c r="AQ5" s="27"/>
       <c r="AR5" s="97"/>
       <c r="AW5" s="29"/>
-      <c r="AX5" s="100" t="s">
-        <v>3</v>
-      </c>
+      <c r="AX5" s="100"/>
       <c r="AY5" s="100"/>
-      <c r="AZ5" s="126" t="s">
-        <v>4</v>
-      </c>
+      <c r="AZ5" s="126"/>
       <c r="BA5" s="126"/>
       <c r="BB5" s="126"/>
       <c r="BC5" s="34"/>
@@ -4271,7 +4278,7 @@
     </row>
     <row r="6" ht="16.5" customHeight="1" spans="2:67">
       <c r="B6" s="25" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D6" s="29"/>
       <c r="E6" s="34"/>
@@ -4334,7 +4341,7 @@
     <row r="7" ht="16.5" customHeight="1" spans="4:67">
       <c r="D7" s="29"/>
       <c r="E7" s="25" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J7" s="67"/>
       <c r="K7" s="67"/>
@@ -4351,23 +4358,21 @@
       <c r="V7" s="97"/>
       <c r="Z7" s="29"/>
       <c r="AA7" s="82" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB7" s="85"/>
       <c r="AC7" s="34"/>
       <c r="AD7" s="82" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE7" s="85"/>
       <c r="AG7" s="82" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH7" s="85"/>
       <c r="AI7" s="34"/>
       <c r="AJ7" s="66"/>
-      <c r="AK7" s="142" t="s">
-        <v>10</v>
-      </c>
+      <c r="AK7" s="142"/>
       <c r="AL7" s="143"/>
       <c r="AM7" s="143"/>
       <c r="AN7" s="143"/>
@@ -4377,34 +4382,32 @@
       <c r="AR7" s="97"/>
       <c r="AW7" s="29"/>
       <c r="AX7" s="82" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AY7" s="85"/>
       <c r="AZ7" s="34"/>
       <c r="BA7" s="82" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB7" s="85"/>
       <c r="BD7" s="82" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BE7" s="85"/>
       <c r="BF7" s="34"/>
       <c r="BG7" s="66"/>
-      <c r="BH7" s="142" t="s">
-        <v>10</v>
-      </c>
-      <c r="BI7" s="143"/>
-      <c r="BJ7" s="143"/>
-      <c r="BK7" s="143"/>
-      <c r="BL7" s="145"/>
+      <c r="BH7" s="158"/>
+      <c r="BI7" s="160"/>
+      <c r="BJ7" s="160"/>
+      <c r="BK7" s="160"/>
+      <c r="BL7" s="161"/>
       <c r="BM7" s="101"/>
       <c r="BN7" s="101"/>
-      <c r="BO7" s="161"/>
+      <c r="BO7" s="164"/>
     </row>
     <row r="8" spans="1:67">
       <c r="A8" s="30" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B8" s="30"/>
       <c r="D8" s="29"/>
@@ -4497,11 +4500,11 @@
     <row r="10" ht="16.5" customHeight="1" spans="4:70">
       <c r="D10" s="29"/>
       <c r="E10" s="36" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F10" s="37"/>
       <c r="G10" s="38" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H10" s="38"/>
       <c r="I10" s="70">
@@ -4512,11 +4515,11 @@
       <c r="L10" s="71"/>
       <c r="M10" s="34"/>
       <c r="N10" s="36" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="O10" s="37"/>
       <c r="P10" s="38" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q10" s="38"/>
       <c r="R10" s="70">
@@ -4528,21 +4531,21 @@
       <c r="V10" s="97"/>
       <c r="Z10" s="29"/>
       <c r="AA10" s="102" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AB10" s="103"/>
       <c r="AC10" s="103"/>
       <c r="AD10" s="103"/>
       <c r="AE10" s="128"/>
       <c r="AG10" s="108" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AH10" s="109"/>
       <c r="AI10" s="109"/>
       <c r="AJ10" s="109"/>
       <c r="AK10" s="131"/>
       <c r="AM10" s="108" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AN10" s="109"/>
       <c r="AO10" s="109"/>
@@ -4550,27 +4553,27 @@
       <c r="AQ10" s="131"/>
       <c r="AR10" s="97"/>
       <c r="AS10" s="152" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AT10" s="152"/>
       <c r="AU10" s="152"/>
       <c r="AW10" s="29"/>
       <c r="AX10" s="108" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AY10" s="109"/>
       <c r="AZ10" s="109"/>
       <c r="BA10" s="109"/>
       <c r="BB10" s="131"/>
       <c r="BD10" s="108" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BE10" s="109"/>
       <c r="BF10" s="109"/>
       <c r="BG10" s="109"/>
       <c r="BH10" s="131"/>
       <c r="BJ10" s="108" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BK10" s="109"/>
       <c r="BL10" s="109"/>
@@ -4578,7 +4581,7 @@
       <c r="BN10" s="131"/>
       <c r="BO10" s="97"/>
       <c r="BP10" s="152" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BQ10" s="152"/>
       <c r="BR10" s="152"/>
@@ -4646,7 +4649,7 @@
       <c r="D12" s="31"/>
       <c r="E12" s="39"/>
       <c r="G12" s="26" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H12" s="26"/>
       <c r="I12" s="72">
@@ -4658,7 +4661,7 @@
       <c r="M12" s="78"/>
       <c r="N12" s="39"/>
       <c r="P12" s="26" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q12" s="26"/>
       <c r="R12" s="72">
@@ -4733,7 +4736,7 @@
       <c r="V13" s="97"/>
       <c r="Z13" s="31"/>
       <c r="AA13" s="108" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AB13" s="109"/>
       <c r="AC13" s="109"/>
@@ -4741,7 +4744,7 @@
       <c r="AE13" s="131"/>
       <c r="AF13" s="106"/>
       <c r="AG13" s="108" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AH13" s="109"/>
       <c r="AI13" s="109"/>
@@ -4749,7 +4752,7 @@
       <c r="AK13" s="131"/>
       <c r="AL13" s="107"/>
       <c r="AM13" s="108" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AN13" s="109"/>
       <c r="AO13" s="109"/>
@@ -4761,7 +4764,7 @@
       <c r="AU13" s="152"/>
       <c r="AW13" s="31"/>
       <c r="AX13" s="108" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AY13" s="109"/>
       <c r="AZ13" s="109"/>
@@ -4769,7 +4772,7 @@
       <c r="BB13" s="131"/>
       <c r="BC13" s="106"/>
       <c r="BD13" s="108" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BE13" s="109"/>
       <c r="BF13" s="109"/>
@@ -4777,7 +4780,7 @@
       <c r="BH13" s="131"/>
       <c r="BI13" s="107"/>
       <c r="BJ13" s="102" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BK13" s="103"/>
       <c r="BL13" s="103"/>
@@ -4792,7 +4795,7 @@
       <c r="D14" s="31"/>
       <c r="E14" s="39"/>
       <c r="G14" s="26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H14" s="26"/>
       <c r="I14" s="72">
@@ -4805,7 +4808,7 @@
       <c r="M14" s="78"/>
       <c r="N14" s="39"/>
       <c r="P14" s="26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Q14" s="26"/>
       <c r="R14" s="72">
@@ -4982,11 +4985,11 @@
     <row r="17" spans="4:70">
       <c r="D17" s="31"/>
       <c r="E17" s="36" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F17" s="37"/>
       <c r="G17" s="38" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H17" s="38"/>
       <c r="I17" s="70">
@@ -4997,11 +5000,11 @@
       <c r="L17" s="71"/>
       <c r="M17" s="34"/>
       <c r="N17" s="36" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="O17" s="37"/>
       <c r="P17" s="38" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Q17" s="38"/>
       <c r="R17" s="86"/>
@@ -5078,11 +5081,11 @@
       <c r="U18" s="73"/>
       <c r="V18" s="97"/>
       <c r="Z18" s="114" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA18" s="115"/>
       <c r="AB18" s="115" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="AC18" s="115"/>
       <c r="AD18" s="115"/>
@@ -5090,7 +5093,7 @@
       <c r="AF18" s="115"/>
       <c r="AG18" s="138"/>
       <c r="AH18" s="115" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI18" s="115"/>
       <c r="AJ18" s="115"/>
@@ -5098,7 +5101,7 @@
       <c r="AL18" s="138"/>
       <c r="AM18" s="138"/>
       <c r="AN18" s="115" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="AO18" s="115"/>
       <c r="AP18" s="115"/>
@@ -5107,11 +5110,11 @@
       <c r="AT18" s="153"/>
       <c r="AU18" s="153"/>
       <c r="AW18" s="114" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AX18" s="115"/>
       <c r="AY18" s="115" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="AZ18" s="115"/>
       <c r="BA18" s="115"/>
@@ -5119,7 +5122,7 @@
       <c r="BC18" s="115"/>
       <c r="BD18" s="138"/>
       <c r="BE18" s="115" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BF18" s="115"/>
       <c r="BG18" s="115"/>
@@ -5127,7 +5130,7 @@
       <c r="BI18" s="138"/>
       <c r="BJ18" s="138"/>
       <c r="BK18" s="115" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="BL18" s="115"/>
       <c r="BM18" s="115"/>
@@ -5140,7 +5143,7 @@
       <c r="D19" s="31"/>
       <c r="E19" s="39"/>
       <c r="G19" s="26" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="H19" s="26"/>
       <c r="I19" s="72">
@@ -5153,7 +5156,7 @@
       <c r="N19" s="39"/>
       <c r="O19" s="34"/>
       <c r="P19" s="78" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q19" s="78"/>
       <c r="R19" s="87"/>
@@ -5168,7 +5171,7 @@
       </c>
       <c r="AA19" s="117"/>
       <c r="AB19" s="118" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="AC19" s="118"/>
       <c r="AD19" s="118"/>
@@ -5189,7 +5192,7 @@
       <c r="AQ19" s="144"/>
       <c r="AR19" s="148"/>
       <c r="AS19" s="152" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AT19" s="152"/>
       <c r="AU19" s="152"/>
@@ -5198,7 +5201,7 @@
       </c>
       <c r="AX19" s="117"/>
       <c r="AY19" s="117" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="AZ19" s="117"/>
       <c r="BA19" s="117"/>
@@ -5212,14 +5215,14 @@
       <c r="BI19" s="34"/>
       <c r="BJ19" s="34"/>
       <c r="BK19" s="34"/>
-      <c r="BL19" s="159">
+      <c r="BL19" s="162">
         <v>16800</v>
       </c>
-      <c r="BM19" s="159"/>
-      <c r="BN19" s="159"/>
-      <c r="BO19" s="162"/>
+      <c r="BM19" s="162"/>
+      <c r="BN19" s="162"/>
+      <c r="BO19" s="165"/>
       <c r="BP19" s="152" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BQ19" s="152"/>
       <c r="BR19" s="152"/>
@@ -5280,11 +5283,11 @@
       <c r="BI20" s="34"/>
       <c r="BJ20" s="34"/>
       <c r="BK20" s="34"/>
-      <c r="BL20" s="159"/>
-      <c r="BM20" s="159"/>
-      <c r="BN20" s="159"/>
+      <c r="BL20" s="162"/>
+      <c r="BM20" s="162"/>
+      <c r="BN20" s="162"/>
       <c r="BO20" s="148" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BP20" s="152"/>
       <c r="BQ20" s="152"/>
@@ -5294,7 +5297,7 @@
       <c r="D21" s="31"/>
       <c r="E21" s="39"/>
       <c r="G21" s="26" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H21" s="26"/>
       <c r="I21" s="72">
@@ -5308,7 +5311,7 @@
       <c r="N21" s="39"/>
       <c r="O21" s="34"/>
       <c r="P21" s="78" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Q21" s="78"/>
       <c r="R21" s="87"/>
@@ -5328,7 +5331,7 @@
       <c r="AF21" s="120"/>
       <c r="AG21" s="58"/>
       <c r="AH21" s="139" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AI21" s="139"/>
       <c r="AJ21" s="139"/>
@@ -5337,7 +5340,7 @@
       <c r="AM21" s="58"/>
       <c r="AN21" s="58"/>
       <c r="AO21" s="149" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP21" s="149"/>
       <c r="AQ21" s="149"/>
@@ -5353,21 +5356,21 @@
       <c r="BB21" s="155"/>
       <c r="BC21" s="155"/>
       <c r="BD21" s="156" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="BE21" s="156"/>
       <c r="BF21" s="156"/>
       <c r="BG21" s="156"/>
-      <c r="BH21" s="158"/>
+      <c r="BH21" s="159"/>
       <c r="BI21" s="156"/>
       <c r="BJ21" s="156"/>
       <c r="BK21" s="156"/>
-      <c r="BL21" s="160" t="s">
-        <v>44</v>
-      </c>
-      <c r="BM21" s="160"/>
-      <c r="BN21" s="158"/>
-      <c r="BO21" s="163"/>
+      <c r="BL21" s="163" t="s">
+        <v>40</v>
+      </c>
+      <c r="BM21" s="163"/>
+      <c r="BN21" s="159"/>
+      <c r="BO21" s="166"/>
       <c r="BP21" s="152"/>
       <c r="BQ21" s="152"/>
       <c r="BR21" s="152"/>
@@ -5397,7 +5400,7 @@
       </c>
       <c r="AA22" s="117"/>
       <c r="AB22" s="117" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AC22" s="117"/>
       <c r="AD22" s="117"/>
@@ -5425,7 +5428,7 @@
       </c>
       <c r="AX22" s="117"/>
       <c r="AY22" s="117" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AZ22" s="117"/>
       <c r="BA22" s="117"/>
@@ -5439,12 +5442,12 @@
       <c r="BI22" s="34"/>
       <c r="BJ22" s="34"/>
       <c r="BK22" s="34"/>
-      <c r="BL22" s="159">
+      <c r="BL22" s="162">
         <v>15500</v>
       </c>
-      <c r="BM22" s="159"/>
-      <c r="BN22" s="159"/>
-      <c r="BO22" s="162"/>
+      <c r="BM22" s="162"/>
+      <c r="BN22" s="162"/>
+      <c r="BO22" s="165"/>
       <c r="BP22" s="152"/>
       <c r="BQ22" s="152"/>
       <c r="BR22" s="152"/>
@@ -5500,11 +5503,11 @@
       <c r="BI23" s="34"/>
       <c r="BJ23" s="34"/>
       <c r="BK23" s="34"/>
-      <c r="BL23" s="159"/>
-      <c r="BM23" s="159"/>
-      <c r="BN23" s="159"/>
+      <c r="BL23" s="162"/>
+      <c r="BM23" s="162"/>
+      <c r="BN23" s="162"/>
       <c r="BO23" s="148" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BP23" s="152"/>
       <c r="BQ23" s="152"/>
@@ -5513,25 +5516,25 @@
     <row r="24" ht="16.5" customHeight="1" spans="4:70">
       <c r="D24" s="32"/>
       <c r="F24" s="43" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="44"/>
       <c r="I24" s="46"/>
       <c r="J24" s="43" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="K24" s="38"/>
       <c r="L24" s="44"/>
       <c r="M24" s="46"/>
       <c r="N24" s="43" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="O24" s="38"/>
       <c r="P24" s="44"/>
       <c r="Q24" s="46"/>
       <c r="R24" s="43" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="S24" s="38"/>
       <c r="T24" s="44"/>
@@ -5546,7 +5549,7 @@
       <c r="AF24" s="120"/>
       <c r="AG24" s="58"/>
       <c r="AH24" s="139" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="AI24" s="139"/>
       <c r="AJ24" s="139"/>
@@ -5555,7 +5558,7 @@
       <c r="AM24" s="58"/>
       <c r="AN24" s="58"/>
       <c r="AO24" s="149" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP24" s="149"/>
       <c r="AQ24" s="149"/>
@@ -5571,21 +5574,21 @@
       <c r="BB24" s="155"/>
       <c r="BC24" s="155"/>
       <c r="BD24" s="156" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="BE24" s="156"/>
       <c r="BF24" s="156"/>
       <c r="BG24" s="156"/>
-      <c r="BH24" s="158"/>
+      <c r="BH24" s="159"/>
       <c r="BI24" s="156"/>
       <c r="BJ24" s="156"/>
       <c r="BK24" s="156"/>
-      <c r="BL24" s="160" t="s">
-        <v>44</v>
-      </c>
-      <c r="BM24" s="160"/>
-      <c r="BN24" s="158"/>
-      <c r="BO24" s="163"/>
+      <c r="BL24" s="163" t="s">
+        <v>40</v>
+      </c>
+      <c r="BM24" s="163"/>
+      <c r="BN24" s="159"/>
+      <c r="BO24" s="166"/>
       <c r="BP24" s="152"/>
       <c r="BQ24" s="152"/>
       <c r="BR24" s="152"/>
@@ -5614,7 +5617,7 @@
       </c>
       <c r="AA25" s="117"/>
       <c r="AB25" s="117" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="AC25" s="117"/>
       <c r="AD25" s="117"/>
@@ -5642,7 +5645,7 @@
       </c>
       <c r="AX25" s="117"/>
       <c r="AY25" s="117" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AZ25" s="117"/>
       <c r="BA25" s="117"/>
@@ -5656,12 +5659,12 @@
       <c r="BI25" s="34"/>
       <c r="BJ25" s="34"/>
       <c r="BK25" s="34"/>
-      <c r="BL25" s="159">
+      <c r="BL25" s="162">
         <v>14900</v>
       </c>
-      <c r="BM25" s="159"/>
-      <c r="BN25" s="159"/>
-      <c r="BO25" s="162"/>
+      <c r="BM25" s="162"/>
+      <c r="BN25" s="162"/>
+      <c r="BO25" s="165"/>
       <c r="BP25" s="152"/>
       <c r="BQ25" s="152"/>
       <c r="BR25" s="152"/>
@@ -5669,25 +5672,25 @@
     <row r="26" ht="16.5" customHeight="1" spans="4:70">
       <c r="D26" s="32"/>
       <c r="F26" s="45" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G26" s="46"/>
       <c r="H26" s="47"/>
       <c r="I26" s="46"/>
       <c r="J26" s="45" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="K26" s="46"/>
       <c r="L26" s="47"/>
       <c r="M26" s="46"/>
       <c r="N26" s="45" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="O26" s="46"/>
       <c r="P26" s="47"/>
       <c r="Q26" s="46"/>
       <c r="R26" s="45" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="S26" s="46"/>
       <c r="T26" s="47"/>
@@ -5730,11 +5733,11 @@
       <c r="BI26" s="34"/>
       <c r="BJ26" s="34"/>
       <c r="BK26" s="34"/>
-      <c r="BL26" s="159"/>
-      <c r="BM26" s="159"/>
-      <c r="BN26" s="159"/>
+      <c r="BL26" s="162"/>
+      <c r="BM26" s="162"/>
+      <c r="BN26" s="162"/>
       <c r="BO26" s="148" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BP26" s="152"/>
       <c r="BQ26" s="152"/>
@@ -5768,7 +5771,7 @@
       <c r="AF27" s="120"/>
       <c r="AG27" s="58"/>
       <c r="AH27" s="139" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AI27" s="139"/>
       <c r="AJ27" s="139"/>
@@ -5777,7 +5780,7 @@
       <c r="AM27" s="58"/>
       <c r="AN27" s="58"/>
       <c r="AO27" s="149" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP27" s="149"/>
       <c r="AQ27" s="149"/>
@@ -5793,21 +5796,21 @@
       <c r="BB27" s="155"/>
       <c r="BC27" s="155"/>
       <c r="BD27" s="156" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="BE27" s="156"/>
       <c r="BF27" s="156"/>
       <c r="BG27" s="156"/>
-      <c r="BH27" s="158"/>
+      <c r="BH27" s="159"/>
       <c r="BI27" s="156"/>
       <c r="BJ27" s="156"/>
       <c r="BK27" s="156"/>
-      <c r="BL27" s="160" t="s">
-        <v>44</v>
-      </c>
-      <c r="BM27" s="160"/>
-      <c r="BN27" s="158"/>
-      <c r="BO27" s="163"/>
+      <c r="BL27" s="163" t="s">
+        <v>40</v>
+      </c>
+      <c r="BM27" s="163"/>
+      <c r="BN27" s="159"/>
+      <c r="BO27" s="166"/>
       <c r="BP27" s="152"/>
       <c r="BQ27" s="152"/>
       <c r="BR27" s="152"/>
@@ -5815,25 +5818,25 @@
     <row r="28" ht="16.5" customHeight="1" spans="4:70">
       <c r="D28" s="32"/>
       <c r="F28" s="48" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G28" s="49"/>
       <c r="H28" s="50"/>
       <c r="I28" s="46"/>
       <c r="J28" s="48" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K28" s="49"/>
       <c r="L28" s="50"/>
       <c r="M28" s="46"/>
       <c r="N28" s="48" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="O28" s="49"/>
       <c r="P28" s="50"/>
       <c r="Q28" s="46"/>
       <c r="R28" s="48" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="S28" s="49"/>
       <c r="T28" s="50"/>
@@ -5844,7 +5847,7 @@
       </c>
       <c r="AA28" s="117"/>
       <c r="AB28" s="117" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AC28" s="117"/>
       <c r="AD28" s="117"/>
@@ -5872,7 +5875,7 @@
       </c>
       <c r="AX28" s="117"/>
       <c r="AY28" s="117" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="AZ28" s="117"/>
       <c r="BA28" s="117"/>
@@ -5886,12 +5889,12 @@
       <c r="BI28" s="34"/>
       <c r="BJ28" s="34"/>
       <c r="BK28" s="34"/>
-      <c r="BL28" s="159">
+      <c r="BL28" s="162">
         <v>12800</v>
       </c>
-      <c r="BM28" s="159"/>
-      <c r="BN28" s="159"/>
-      <c r="BO28" s="162"/>
+      <c r="BM28" s="162"/>
+      <c r="BN28" s="162"/>
+      <c r="BO28" s="165"/>
       <c r="BP28" s="152"/>
       <c r="BQ28" s="152"/>
       <c r="BR28" s="152"/>
@@ -5953,11 +5956,11 @@
       <c r="BI29" s="34"/>
       <c r="BJ29" s="34"/>
       <c r="BK29" s="34"/>
-      <c r="BL29" s="159"/>
-      <c r="BM29" s="159"/>
-      <c r="BN29" s="159"/>
+      <c r="BL29" s="162"/>
+      <c r="BM29" s="162"/>
+      <c r="BN29" s="162"/>
       <c r="BO29" s="148" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BP29" s="152"/>
       <c r="BQ29" s="152"/>
@@ -5992,7 +5995,7 @@
       <c r="AF30" s="120"/>
       <c r="AG30" s="58"/>
       <c r="AH30" s="139" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="AI30" s="139"/>
       <c r="AJ30" s="139"/>
@@ -6001,7 +6004,7 @@
       <c r="AM30" s="58"/>
       <c r="AN30" s="58"/>
       <c r="AO30" s="149" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP30" s="149"/>
       <c r="AQ30" s="149"/>
@@ -6017,21 +6020,21 @@
       <c r="BB30" s="155"/>
       <c r="BC30" s="155"/>
       <c r="BD30" s="157" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="BE30" s="157"/>
       <c r="BF30" s="157"/>
       <c r="BG30" s="157"/>
       <c r="BH30" s="157"/>
-      <c r="BI30" s="158"/>
-      <c r="BJ30" s="158"/>
-      <c r="BK30" s="158"/>
-      <c r="BL30" s="160" t="s">
-        <v>44</v>
-      </c>
-      <c r="BM30" s="160"/>
-      <c r="BN30" s="158"/>
-      <c r="BO30" s="163"/>
+      <c r="BI30" s="159"/>
+      <c r="BJ30" s="159"/>
+      <c r="BK30" s="159"/>
+      <c r="BL30" s="163" t="s">
+        <v>40</v>
+      </c>
+      <c r="BM30" s="163"/>
+      <c r="BN30" s="159"/>
+      <c r="BO30" s="166"/>
       <c r="BP30" s="152"/>
       <c r="BQ30" s="152"/>
       <c r="BR30" s="152"/>
@@ -6061,7 +6064,7 @@
       </c>
       <c r="AA31" s="117"/>
       <c r="AB31" s="117" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="AC31" s="117"/>
       <c r="AD31" s="117"/>
@@ -6089,7 +6092,7 @@
       </c>
       <c r="AX31" s="117"/>
       <c r="AY31" s="117" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="AZ31" s="117"/>
       <c r="BA31" s="117"/>
@@ -6103,12 +6106,12 @@
       <c r="BI31" s="34"/>
       <c r="BJ31" s="34"/>
       <c r="BK31" s="34"/>
-      <c r="BL31" s="159">
+      <c r="BL31" s="162">
         <v>11300</v>
       </c>
-      <c r="BM31" s="159"/>
-      <c r="BN31" s="159"/>
-      <c r="BO31" s="162"/>
+      <c r="BM31" s="162"/>
+      <c r="BN31" s="162"/>
+      <c r="BO31" s="165"/>
       <c r="BP31" s="152"/>
       <c r="BQ31" s="152"/>
       <c r="BR31" s="152"/>
@@ -6116,7 +6119,7 @@
     <row r="32" ht="16.5" customHeight="1" spans="4:70">
       <c r="D32" s="32"/>
       <c r="E32" s="54" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F32" s="54"/>
       <c r="G32" s="54"/>
@@ -6172,11 +6175,11 @@
       <c r="BI32" s="34"/>
       <c r="BJ32" s="34"/>
       <c r="BK32" s="34"/>
-      <c r="BL32" s="159"/>
-      <c r="BM32" s="159"/>
-      <c r="BN32" s="159"/>
+      <c r="BL32" s="162"/>
+      <c r="BM32" s="162"/>
+      <c r="BN32" s="162"/>
       <c r="BO32" s="148" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BP32" s="152"/>
       <c r="BQ32" s="152"/>
@@ -6185,7 +6188,7 @@
     <row r="33" ht="16.5" customHeight="1" spans="4:70">
       <c r="D33" s="32"/>
       <c r="E33" s="55" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F33" s="56"/>
       <c r="G33" s="56"/>
@@ -6195,7 +6198,7 @@
       <c r="I33" s="56"/>
       <c r="J33" s="56"/>
       <c r="K33" s="55" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L33" s="56"/>
       <c r="M33" s="56"/>
@@ -6204,7 +6207,7 @@
       </c>
       <c r="O33" s="56"/>
       <c r="P33" s="55" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="Q33" s="56"/>
       <c r="R33" s="56"/>
@@ -6224,7 +6227,7 @@
       <c r="AF33" s="120"/>
       <c r="AG33" s="58"/>
       <c r="AH33" s="139" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="AI33" s="139"/>
       <c r="AJ33" s="139"/>
@@ -6233,7 +6236,7 @@
       <c r="AM33" s="58"/>
       <c r="AN33" s="58"/>
       <c r="AO33" s="149" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP33" s="149"/>
       <c r="AQ33" s="149"/>
@@ -6249,21 +6252,21 @@
       <c r="BB33" s="155"/>
       <c r="BC33" s="155"/>
       <c r="BD33" s="156" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="BE33" s="156"/>
       <c r="BF33" s="156"/>
       <c r="BG33" s="156"/>
-      <c r="BH33" s="158"/>
-      <c r="BI33" s="158"/>
-      <c r="BJ33" s="158"/>
-      <c r="BK33" s="158"/>
-      <c r="BL33" s="160" t="s">
-        <v>44</v>
-      </c>
-      <c r="BM33" s="160"/>
-      <c r="BN33" s="158"/>
-      <c r="BO33" s="163"/>
+      <c r="BH33" s="159"/>
+      <c r="BI33" s="159"/>
+      <c r="BJ33" s="159"/>
+      <c r="BK33" s="159"/>
+      <c r="BL33" s="163" t="s">
+        <v>40</v>
+      </c>
+      <c r="BM33" s="163"/>
+      <c r="BN33" s="159"/>
+      <c r="BO33" s="166"/>
       <c r="BP33" s="152"/>
       <c r="BQ33" s="152"/>
       <c r="BR33" s="152"/>
@@ -6293,7 +6296,7 @@
       </c>
       <c r="AA34" s="117"/>
       <c r="AB34" s="117" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="AC34" s="117"/>
       <c r="AD34" s="117"/>
@@ -6321,7 +6324,7 @@
       </c>
       <c r="AX34" s="117"/>
       <c r="AY34" s="117" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="AZ34" s="117"/>
       <c r="BA34" s="117"/>
@@ -6335,12 +6338,12 @@
       <c r="BI34" s="34"/>
       <c r="BJ34" s="34"/>
       <c r="BK34" s="34"/>
-      <c r="BL34" s="159">
+      <c r="BL34" s="162">
         <v>10200</v>
       </c>
-      <c r="BM34" s="159"/>
-      <c r="BN34" s="159"/>
-      <c r="BO34" s="162"/>
+      <c r="BM34" s="162"/>
+      <c r="BN34" s="162"/>
+      <c r="BO34" s="165"/>
       <c r="BP34" s="152"/>
       <c r="BQ34" s="152"/>
       <c r="BR34" s="152"/>
@@ -6392,11 +6395,11 @@
       <c r="BI35" s="34"/>
       <c r="BJ35" s="34"/>
       <c r="BK35" s="34"/>
-      <c r="BL35" s="159"/>
-      <c r="BM35" s="159"/>
-      <c r="BN35" s="159"/>
+      <c r="BL35" s="162"/>
+      <c r="BM35" s="162"/>
+      <c r="BN35" s="162"/>
       <c r="BO35" s="148" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="BP35" s="152"/>
       <c r="BQ35" s="152"/>
@@ -6405,7 +6408,7 @@
     <row r="36" ht="16.5" customHeight="1" spans="4:70">
       <c r="D36" s="32"/>
       <c r="E36" s="59" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F36" s="59"/>
       <c r="G36" s="59"/>
@@ -6417,7 +6420,7 @@
       <c r="K36" s="79"/>
       <c r="L36" s="34"/>
       <c r="M36" s="84" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="N36" s="84"/>
       <c r="O36" s="84"/>
@@ -6439,7 +6442,7 @@
       <c r="AF36" s="120"/>
       <c r="AG36" s="58"/>
       <c r="AH36" s="139" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="AI36" s="139"/>
       <c r="AJ36" s="139"/>
@@ -6448,7 +6451,7 @@
       <c r="AM36" s="58"/>
       <c r="AN36" s="58"/>
       <c r="AO36" s="149" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP36" s="149"/>
       <c r="AQ36" s="149"/>
@@ -6464,21 +6467,21 @@
       <c r="BB36" s="155"/>
       <c r="BC36" s="155"/>
       <c r="BD36" s="156" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="BE36" s="156"/>
       <c r="BF36" s="156"/>
       <c r="BG36" s="156"/>
-      <c r="BH36" s="158"/>
-      <c r="BI36" s="158"/>
-      <c r="BJ36" s="158"/>
-      <c r="BK36" s="158"/>
-      <c r="BL36" s="160" t="s">
-        <v>44</v>
-      </c>
-      <c r="BM36" s="160"/>
-      <c r="BN36" s="158"/>
-      <c r="BO36" s="163"/>
+      <c r="BH36" s="159"/>
+      <c r="BI36" s="159"/>
+      <c r="BJ36" s="159"/>
+      <c r="BK36" s="159"/>
+      <c r="BL36" s="163" t="s">
+        <v>40</v>
+      </c>
+      <c r="BM36" s="163"/>
+      <c r="BN36" s="159"/>
+      <c r="BO36" s="166"/>
       <c r="BP36" s="152"/>
       <c r="BQ36" s="152"/>
       <c r="BR36" s="152"/>
@@ -6486,7 +6489,7 @@
     <row r="37" ht="20.4" spans="4:67">
       <c r="D37" s="32"/>
       <c r="E37" s="59" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F37" s="59"/>
       <c r="G37" s="59"/>
@@ -6499,7 +6502,7 @@
       <c r="K37" s="79"/>
       <c r="L37" s="46"/>
       <c r="M37" s="84" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N37" s="84"/>
       <c r="O37" s="84"/>
@@ -6555,7 +6558,7 @@
     <row r="38" ht="20.4" spans="4:67">
       <c r="D38" s="32"/>
       <c r="E38" s="59" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F38" s="59"/>
       <c r="G38" s="59"/>
@@ -6568,14 +6571,14 @@
       <c r="K38" s="79"/>
       <c r="L38" s="78"/>
       <c r="M38" s="84" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="N38" s="84"/>
       <c r="O38" s="84"/>
       <c r="P38" s="84"/>
       <c r="Q38" s="93">
-        <f>N33/Q37</f>
-        <v>200</v>
+        <f>N33/Q36</f>
+        <v>6.66666666666667</v>
       </c>
       <c r="R38" s="93"/>
       <c r="S38" s="93"/>
@@ -6801,7 +6804,7 @@
     <row r="42" ht="20.4" spans="4:67">
       <c r="D42" s="32"/>
       <c r="E42" s="54" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F42" s="54"/>
       <c r="G42" s="54"/>
@@ -6862,7 +6865,7 @@
     <row r="43" spans="4:67">
       <c r="D43" s="32"/>
       <c r="E43" s="61" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F43" s="62"/>
       <c r="G43" s="62"/>
@@ -7044,25 +7047,25 @@
       <c r="D46" s="32"/>
       <c r="E46" s="46"/>
       <c r="F46" s="43" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G46" s="38"/>
       <c r="H46" s="44"/>
       <c r="I46" s="46"/>
       <c r="J46" s="43" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="K46" s="38"/>
       <c r="L46" s="44"/>
       <c r="M46" s="46"/>
       <c r="N46" s="43" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="O46" s="38"/>
       <c r="P46" s="44"/>
       <c r="Q46" s="46"/>
       <c r="R46" s="43" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="S46" s="38"/>
       <c r="T46" s="44"/>
@@ -7170,25 +7173,25 @@
       <c r="D48" s="32"/>
       <c r="E48" s="46"/>
       <c r="F48" s="45" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G48" s="46"/>
       <c r="H48" s="47"/>
       <c r="I48" s="46"/>
       <c r="J48" s="45" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K48" s="46"/>
       <c r="L48" s="47"/>
       <c r="M48" s="46"/>
       <c r="N48" s="45" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O48" s="46"/>
       <c r="P48" s="47"/>
       <c r="Q48" s="46"/>
       <c r="R48" s="45" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="S48" s="46"/>
       <c r="T48" s="47"/>
@@ -7296,80 +7299,80 @@
       <c r="D50" s="32"/>
       <c r="E50" s="46"/>
       <c r="F50" s="48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G50" s="49"/>
       <c r="H50" s="50"/>
       <c r="I50" s="46"/>
       <c r="J50" s="48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K50" s="49"/>
       <c r="L50" s="50"/>
       <c r="M50" s="46"/>
       <c r="N50" s="48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="O50" s="49"/>
       <c r="P50" s="50"/>
       <c r="Q50" s="46"/>
       <c r="R50" s="48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="S50" s="49"/>
       <c r="T50" s="50"/>
       <c r="U50" s="46"/>
       <c r="V50" s="97"/>
       <c r="Z50" s="122" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AA50" s="123"/>
       <c r="AB50" s="123"/>
       <c r="AC50" s="123"/>
       <c r="AD50" s="134"/>
       <c r="AE50" s="135" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="AF50" s="135"/>
       <c r="AG50" s="135"/>
       <c r="AH50" s="135"/>
       <c r="AI50" s="140"/>
       <c r="AJ50" s="123" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="AK50" s="123"/>
       <c r="AL50" s="123"/>
       <c r="AM50" s="123"/>
       <c r="AN50" s="134"/>
       <c r="AO50" s="123" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="AP50" s="123"/>
       <c r="AQ50" s="123"/>
       <c r="AR50" s="134"/>
       <c r="AW50" s="122" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AX50" s="123"/>
       <c r="AY50" s="123"/>
       <c r="AZ50" s="123"/>
       <c r="BA50" s="134"/>
       <c r="BB50" s="123" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="BC50" s="123"/>
       <c r="BD50" s="123"/>
       <c r="BE50" s="123"/>
       <c r="BF50" s="134"/>
       <c r="BG50" s="135" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="BH50" s="135"/>
       <c r="BI50" s="135"/>
       <c r="BJ50" s="135"/>
       <c r="BK50" s="140"/>
       <c r="BL50" s="123" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="BM50" s="123"/>
       <c r="BN50" s="123"/>
@@ -7438,25 +7441,25 @@
       <c r="D52" s="32"/>
       <c r="E52" s="46"/>
       <c r="F52" s="43" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G52" s="38"/>
       <c r="H52" s="44"/>
       <c r="I52" s="46"/>
       <c r="J52" s="43" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K52" s="38"/>
       <c r="L52" s="44"/>
       <c r="M52" s="46"/>
       <c r="N52" s="43" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O52" s="38"/>
       <c r="P52" s="44"/>
       <c r="Q52" s="46"/>
       <c r="R52" s="43" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="S52" s="38"/>
       <c r="T52" s="44"/>
@@ -7488,25 +7491,25 @@
       <c r="D54" s="32"/>
       <c r="E54" s="46"/>
       <c r="F54" s="45" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G54" s="46"/>
       <c r="H54" s="47"/>
       <c r="I54" s="46"/>
       <c r="J54" s="45" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K54" s="46"/>
       <c r="L54" s="47"/>
       <c r="M54" s="46"/>
       <c r="N54" s="45" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="O54" s="46"/>
       <c r="P54" s="47"/>
       <c r="Q54" s="46"/>
       <c r="R54" s="45" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="S54" s="46"/>
       <c r="T54" s="47"/>
@@ -7538,25 +7541,25 @@
       <c r="D56" s="32"/>
       <c r="E56" s="46"/>
       <c r="F56" s="48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="G56" s="49"/>
       <c r="H56" s="50"/>
       <c r="I56" s="46"/>
       <c r="J56" s="48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K56" s="49"/>
       <c r="L56" s="50"/>
       <c r="M56" s="46"/>
       <c r="N56" s="48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="O56" s="49"/>
       <c r="P56" s="50"/>
       <c r="Q56" s="46"/>
       <c r="R56" s="48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="S56" s="49"/>
       <c r="T56" s="50"/>
@@ -7609,7 +7612,7 @@
       <c r="D59" s="32"/>
       <c r="E59" s="46"/>
       <c r="F59" s="43" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G59" s="38"/>
       <c r="H59" s="38"/>
@@ -7617,11 +7620,11 @@
       <c r="J59" s="38"/>
       <c r="K59" s="38"/>
       <c r="L59" s="44" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M59" s="46"/>
       <c r="N59" s="43" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="O59" s="38"/>
       <c r="P59" s="38"/>
@@ -7629,7 +7632,7 @@
       <c r="R59" s="38"/>
       <c r="S59" s="38"/>
       <c r="T59" s="44" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="U59" s="46"/>
       <c r="V59" s="97"/>
@@ -7680,7 +7683,7 @@
       <c r="D62" s="32"/>
       <c r="E62" s="46"/>
       <c r="F62" s="43" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G62" s="38"/>
       <c r="H62" s="38"/>
@@ -7688,11 +7691,11 @@
       <c r="J62" s="38"/>
       <c r="K62" s="38"/>
       <c r="L62" s="44" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="M62" s="46"/>
       <c r="N62" s="43" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="O62" s="38"/>
       <c r="P62" s="38"/>
@@ -7700,7 +7703,7 @@
       <c r="R62" s="38"/>
       <c r="S62" s="38"/>
       <c r="T62" s="44" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="U62" s="46"/>
       <c r="V62" s="97"/>
@@ -7769,36 +7772,36 @@
       <c r="V65" s="97"/>
     </row>
     <row r="66" spans="4:22">
-      <c r="D66" s="164" t="s">
-        <v>83</v>
+      <c r="D66" s="167" t="s">
+        <v>79</v>
       </c>
       <c r="E66" s="135"/>
       <c r="F66" s="135"/>
       <c r="G66" s="135"/>
       <c r="H66" s="140"/>
       <c r="I66" s="123" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J66" s="123"/>
       <c r="K66" s="123"/>
       <c r="L66" s="123"/>
       <c r="M66" s="134"/>
       <c r="N66" s="123" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="O66" s="123"/>
       <c r="P66" s="123"/>
       <c r="Q66" s="123"/>
       <c r="R66" s="134"/>
       <c r="S66" s="123" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="T66" s="123"/>
       <c r="U66" s="123"/>
       <c r="V66" s="134"/>
     </row>
     <row r="67" ht="17.55" spans="4:22">
-      <c r="D67" s="165"/>
+      <c r="D67" s="168"/>
       <c r="E67" s="137"/>
       <c r="F67" s="137"/>
       <c r="G67" s="137"/>
@@ -7819,271 +7822,271 @@
       <c r="V67" s="136"/>
     </row>
     <row r="72" spans="4:64">
-      <c r="D72" s="166" t="s">
-        <v>95</v>
-      </c>
-      <c r="E72" s="166"/>
-      <c r="F72" s="166"/>
-      <c r="G72" s="166"/>
-      <c r="H72" s="166"/>
-      <c r="I72" s="166"/>
-      <c r="J72" s="166"/>
-      <c r="K72" s="166"/>
-      <c r="L72" s="166"/>
-      <c r="M72" s="166"/>
-      <c r="N72" s="166"/>
-      <c r="O72" s="166"/>
-      <c r="P72" s="166"/>
-      <c r="Q72" s="166"/>
-      <c r="R72" s="166"/>
-      <c r="S72" s="166"/>
-      <c r="T72" s="166"/>
-      <c r="U72" s="166"/>
-      <c r="V72" s="166"/>
-      <c r="W72" s="166"/>
-      <c r="X72" s="166"/>
-      <c r="Y72" s="166"/>
-      <c r="Z72" s="166"/>
-      <c r="AA72" s="166"/>
-      <c r="AB72" s="166"/>
-      <c r="AC72" s="166"/>
-      <c r="AD72" s="166"/>
-      <c r="AE72" s="166"/>
-      <c r="AF72" s="166"/>
-      <c r="AG72" s="166"/>
-      <c r="AH72" s="166"/>
-      <c r="AI72" s="166"/>
-      <c r="AJ72" s="166"/>
-      <c r="AK72" s="166"/>
-      <c r="AL72" s="166"/>
-      <c r="AM72" s="166"/>
-      <c r="AN72" s="166"/>
-      <c r="AO72" s="166"/>
-      <c r="AP72" s="166"/>
-      <c r="AQ72" s="166"/>
-      <c r="AR72" s="166"/>
-      <c r="AS72" s="166"/>
-      <c r="AT72" s="166"/>
-      <c r="AU72" s="166"/>
-      <c r="AV72" s="166"/>
-      <c r="AW72" s="166"/>
-      <c r="AX72" s="166"/>
-      <c r="AY72" s="166"/>
-      <c r="AZ72" s="166"/>
-      <c r="BA72" s="166"/>
-      <c r="BB72" s="166"/>
-      <c r="BC72" s="166"/>
-      <c r="BD72" s="166"/>
-      <c r="BE72" s="166"/>
-      <c r="BF72" s="166"/>
-      <c r="BG72" s="166"/>
-      <c r="BH72" s="166"/>
-      <c r="BI72" s="166"/>
-      <c r="BJ72" s="166"/>
-      <c r="BK72" s="166"/>
-      <c r="BL72" s="166"/>
+      <c r="D72" s="169" t="s">
+        <v>91</v>
+      </c>
+      <c r="E72" s="169"/>
+      <c r="F72" s="169"/>
+      <c r="G72" s="169"/>
+      <c r="H72" s="169"/>
+      <c r="I72" s="169"/>
+      <c r="J72" s="169"/>
+      <c r="K72" s="169"/>
+      <c r="L72" s="169"/>
+      <c r="M72" s="169"/>
+      <c r="N72" s="169"/>
+      <c r="O72" s="169"/>
+      <c r="P72" s="169"/>
+      <c r="Q72" s="169"/>
+      <c r="R72" s="169"/>
+      <c r="S72" s="169"/>
+      <c r="T72" s="169"/>
+      <c r="U72" s="169"/>
+      <c r="V72" s="169"/>
+      <c r="W72" s="169"/>
+      <c r="X72" s="169"/>
+      <c r="Y72" s="169"/>
+      <c r="Z72" s="169"/>
+      <c r="AA72" s="169"/>
+      <c r="AB72" s="169"/>
+      <c r="AC72" s="169"/>
+      <c r="AD72" s="169"/>
+      <c r="AE72" s="169"/>
+      <c r="AF72" s="169"/>
+      <c r="AG72" s="169"/>
+      <c r="AH72" s="169"/>
+      <c r="AI72" s="169"/>
+      <c r="AJ72" s="169"/>
+      <c r="AK72" s="169"/>
+      <c r="AL72" s="169"/>
+      <c r="AM72" s="169"/>
+      <c r="AN72" s="169"/>
+      <c r="AO72" s="169"/>
+      <c r="AP72" s="169"/>
+      <c r="AQ72" s="169"/>
+      <c r="AR72" s="169"/>
+      <c r="AS72" s="169"/>
+      <c r="AT72" s="169"/>
+      <c r="AU72" s="169"/>
+      <c r="AV72" s="169"/>
+      <c r="AW72" s="169"/>
+      <c r="AX72" s="169"/>
+      <c r="AY72" s="169"/>
+      <c r="AZ72" s="169"/>
+      <c r="BA72" s="169"/>
+      <c r="BB72" s="169"/>
+      <c r="BC72" s="169"/>
+      <c r="BD72" s="169"/>
+      <c r="BE72" s="169"/>
+      <c r="BF72" s="169"/>
+      <c r="BG72" s="169"/>
+      <c r="BH72" s="169"/>
+      <c r="BI72" s="169"/>
+      <c r="BJ72" s="169"/>
+      <c r="BK72" s="169"/>
+      <c r="BL72" s="169"/>
     </row>
     <row r="73" spans="4:64">
-      <c r="D73" s="166"/>
-      <c r="E73" s="166"/>
-      <c r="F73" s="166"/>
-      <c r="G73" s="166"/>
-      <c r="H73" s="166"/>
-      <c r="I73" s="166"/>
-      <c r="J73" s="166"/>
-      <c r="K73" s="166"/>
-      <c r="L73" s="166"/>
-      <c r="M73" s="166"/>
-      <c r="N73" s="166"/>
-      <c r="O73" s="166"/>
-      <c r="P73" s="166"/>
-      <c r="Q73" s="166"/>
-      <c r="R73" s="166"/>
-      <c r="S73" s="166"/>
-      <c r="T73" s="166"/>
-      <c r="U73" s="166"/>
-      <c r="V73" s="166"/>
-      <c r="W73" s="166"/>
-      <c r="X73" s="166"/>
-      <c r="Y73" s="166"/>
-      <c r="Z73" s="166"/>
-      <c r="AA73" s="166"/>
-      <c r="AB73" s="166"/>
-      <c r="AC73" s="166"/>
-      <c r="AD73" s="166"/>
-      <c r="AE73" s="166"/>
-      <c r="AF73" s="166"/>
-      <c r="AG73" s="166"/>
-      <c r="AH73" s="166"/>
-      <c r="AI73" s="166"/>
-      <c r="AJ73" s="166"/>
-      <c r="AK73" s="166"/>
-      <c r="AL73" s="166"/>
-      <c r="AM73" s="166"/>
-      <c r="AN73" s="166"/>
-      <c r="AO73" s="166"/>
-      <c r="AP73" s="166"/>
-      <c r="AQ73" s="166"/>
-      <c r="AR73" s="166"/>
-      <c r="AS73" s="166"/>
-      <c r="AT73" s="166"/>
-      <c r="AU73" s="166"/>
-      <c r="AV73" s="166"/>
-      <c r="AW73" s="166"/>
-      <c r="AX73" s="166"/>
-      <c r="AY73" s="166"/>
-      <c r="AZ73" s="166"/>
-      <c r="BA73" s="166"/>
-      <c r="BB73" s="166"/>
-      <c r="BC73" s="166"/>
-      <c r="BD73" s="166"/>
-      <c r="BE73" s="166"/>
-      <c r="BF73" s="166"/>
-      <c r="BG73" s="166"/>
-      <c r="BH73" s="166"/>
-      <c r="BI73" s="166"/>
-      <c r="BJ73" s="166"/>
-      <c r="BK73" s="166"/>
-      <c r="BL73" s="166"/>
+      <c r="D73" s="169"/>
+      <c r="E73" s="169"/>
+      <c r="F73" s="169"/>
+      <c r="G73" s="169"/>
+      <c r="H73" s="169"/>
+      <c r="I73" s="169"/>
+      <c r="J73" s="169"/>
+      <c r="K73" s="169"/>
+      <c r="L73" s="169"/>
+      <c r="M73" s="169"/>
+      <c r="N73" s="169"/>
+      <c r="O73" s="169"/>
+      <c r="P73" s="169"/>
+      <c r="Q73" s="169"/>
+      <c r="R73" s="169"/>
+      <c r="S73" s="169"/>
+      <c r="T73" s="169"/>
+      <c r="U73" s="169"/>
+      <c r="V73" s="169"/>
+      <c r="W73" s="169"/>
+      <c r="X73" s="169"/>
+      <c r="Y73" s="169"/>
+      <c r="Z73" s="169"/>
+      <c r="AA73" s="169"/>
+      <c r="AB73" s="169"/>
+      <c r="AC73" s="169"/>
+      <c r="AD73" s="169"/>
+      <c r="AE73" s="169"/>
+      <c r="AF73" s="169"/>
+      <c r="AG73" s="169"/>
+      <c r="AH73" s="169"/>
+      <c r="AI73" s="169"/>
+      <c r="AJ73" s="169"/>
+      <c r="AK73" s="169"/>
+      <c r="AL73" s="169"/>
+      <c r="AM73" s="169"/>
+      <c r="AN73" s="169"/>
+      <c r="AO73" s="169"/>
+      <c r="AP73" s="169"/>
+      <c r="AQ73" s="169"/>
+      <c r="AR73" s="169"/>
+      <c r="AS73" s="169"/>
+      <c r="AT73" s="169"/>
+      <c r="AU73" s="169"/>
+      <c r="AV73" s="169"/>
+      <c r="AW73" s="169"/>
+      <c r="AX73" s="169"/>
+      <c r="AY73" s="169"/>
+      <c r="AZ73" s="169"/>
+      <c r="BA73" s="169"/>
+      <c r="BB73" s="169"/>
+      <c r="BC73" s="169"/>
+      <c r="BD73" s="169"/>
+      <c r="BE73" s="169"/>
+      <c r="BF73" s="169"/>
+      <c r="BG73" s="169"/>
+      <c r="BH73" s="169"/>
+      <c r="BI73" s="169"/>
+      <c r="BJ73" s="169"/>
+      <c r="BK73" s="169"/>
+      <c r="BL73" s="169"/>
     </row>
     <row r="74" spans="4:64">
-      <c r="D74" s="166"/>
-      <c r="E74" s="166"/>
-      <c r="F74" s="166"/>
-      <c r="G74" s="166"/>
-      <c r="H74" s="166"/>
-      <c r="I74" s="166"/>
-      <c r="J74" s="166"/>
-      <c r="K74" s="166"/>
-      <c r="L74" s="166"/>
-      <c r="M74" s="166"/>
-      <c r="N74" s="166"/>
-      <c r="O74" s="166"/>
-      <c r="P74" s="166"/>
-      <c r="Q74" s="166"/>
-      <c r="R74" s="166"/>
-      <c r="S74" s="166"/>
-      <c r="T74" s="166"/>
-      <c r="U74" s="166"/>
-      <c r="V74" s="166"/>
-      <c r="W74" s="166"/>
-      <c r="X74" s="166"/>
-      <c r="Y74" s="166"/>
-      <c r="Z74" s="166"/>
-      <c r="AA74" s="166"/>
-      <c r="AB74" s="166"/>
-      <c r="AC74" s="166"/>
-      <c r="AD74" s="166"/>
-      <c r="AE74" s="166"/>
-      <c r="AF74" s="166"/>
-      <c r="AG74" s="166"/>
-      <c r="AH74" s="166"/>
-      <c r="AI74" s="166"/>
-      <c r="AJ74" s="166"/>
-      <c r="AK74" s="166"/>
-      <c r="AL74" s="166"/>
-      <c r="AM74" s="166"/>
-      <c r="AN74" s="166"/>
-      <c r="AO74" s="166"/>
-      <c r="AP74" s="166"/>
-      <c r="AQ74" s="166"/>
-      <c r="AR74" s="166"/>
-      <c r="AS74" s="166"/>
-      <c r="AT74" s="166"/>
-      <c r="AU74" s="166"/>
-      <c r="AV74" s="166"/>
-      <c r="AW74" s="166"/>
-      <c r="AX74" s="166"/>
-      <c r="AY74" s="166"/>
-      <c r="AZ74" s="166"/>
-      <c r="BA74" s="166"/>
-      <c r="BB74" s="166"/>
-      <c r="BC74" s="166"/>
-      <c r="BD74" s="166"/>
-      <c r="BE74" s="166"/>
-      <c r="BF74" s="166"/>
-      <c r="BG74" s="166"/>
-      <c r="BH74" s="166"/>
-      <c r="BI74" s="166"/>
-      <c r="BJ74" s="166"/>
-      <c r="BK74" s="166"/>
-      <c r="BL74" s="166"/>
+      <c r="D74" s="169"/>
+      <c r="E74" s="169"/>
+      <c r="F74" s="169"/>
+      <c r="G74" s="169"/>
+      <c r="H74" s="169"/>
+      <c r="I74" s="169"/>
+      <c r="J74" s="169"/>
+      <c r="K74" s="169"/>
+      <c r="L74" s="169"/>
+      <c r="M74" s="169"/>
+      <c r="N74" s="169"/>
+      <c r="O74" s="169"/>
+      <c r="P74" s="169"/>
+      <c r="Q74" s="169"/>
+      <c r="R74" s="169"/>
+      <c r="S74" s="169"/>
+      <c r="T74" s="169"/>
+      <c r="U74" s="169"/>
+      <c r="V74" s="169"/>
+      <c r="W74" s="169"/>
+      <c r="X74" s="169"/>
+      <c r="Y74" s="169"/>
+      <c r="Z74" s="169"/>
+      <c r="AA74" s="169"/>
+      <c r="AB74" s="169"/>
+      <c r="AC74" s="169"/>
+      <c r="AD74" s="169"/>
+      <c r="AE74" s="169"/>
+      <c r="AF74" s="169"/>
+      <c r="AG74" s="169"/>
+      <c r="AH74" s="169"/>
+      <c r="AI74" s="169"/>
+      <c r="AJ74" s="169"/>
+      <c r="AK74" s="169"/>
+      <c r="AL74" s="169"/>
+      <c r="AM74" s="169"/>
+      <c r="AN74" s="169"/>
+      <c r="AO74" s="169"/>
+      <c r="AP74" s="169"/>
+      <c r="AQ74" s="169"/>
+      <c r="AR74" s="169"/>
+      <c r="AS74" s="169"/>
+      <c r="AT74" s="169"/>
+      <c r="AU74" s="169"/>
+      <c r="AV74" s="169"/>
+      <c r="AW74" s="169"/>
+      <c r="AX74" s="169"/>
+      <c r="AY74" s="169"/>
+      <c r="AZ74" s="169"/>
+      <c r="BA74" s="169"/>
+      <c r="BB74" s="169"/>
+      <c r="BC74" s="169"/>
+      <c r="BD74" s="169"/>
+      <c r="BE74" s="169"/>
+      <c r="BF74" s="169"/>
+      <c r="BG74" s="169"/>
+      <c r="BH74" s="169"/>
+      <c r="BI74" s="169"/>
+      <c r="BJ74" s="169"/>
+      <c r="BK74" s="169"/>
+      <c r="BL74" s="169"/>
     </row>
     <row r="75" spans="4:64">
-      <c r="D75" s="166"/>
-      <c r="E75" s="166"/>
-      <c r="F75" s="166"/>
-      <c r="G75" s="166"/>
-      <c r="H75" s="166"/>
-      <c r="I75" s="166"/>
-      <c r="J75" s="166"/>
-      <c r="K75" s="166"/>
-      <c r="L75" s="166"/>
-      <c r="M75" s="166"/>
-      <c r="N75" s="166"/>
-      <c r="O75" s="166"/>
-      <c r="P75" s="166"/>
-      <c r="Q75" s="166"/>
-      <c r="R75" s="166"/>
-      <c r="S75" s="166"/>
-      <c r="T75" s="166"/>
-      <c r="U75" s="166"/>
-      <c r="V75" s="166"/>
-      <c r="W75" s="166"/>
-      <c r="X75" s="166"/>
-      <c r="Y75" s="166"/>
-      <c r="Z75" s="166"/>
-      <c r="AA75" s="166"/>
-      <c r="AB75" s="166"/>
-      <c r="AC75" s="166"/>
-      <c r="AD75" s="166"/>
-      <c r="AE75" s="166"/>
-      <c r="AF75" s="166"/>
-      <c r="AG75" s="166"/>
-      <c r="AH75" s="166"/>
-      <c r="AI75" s="166"/>
-      <c r="AJ75" s="166"/>
-      <c r="AK75" s="166"/>
-      <c r="AL75" s="166"/>
-      <c r="AM75" s="166"/>
-      <c r="AN75" s="166"/>
-      <c r="AO75" s="166"/>
-      <c r="AP75" s="166"/>
-      <c r="AQ75" s="166"/>
-      <c r="AR75" s="166"/>
-      <c r="AS75" s="166"/>
-      <c r="AT75" s="166"/>
-      <c r="AU75" s="166"/>
-      <c r="AV75" s="166"/>
-      <c r="AW75" s="166"/>
-      <c r="AX75" s="166"/>
-      <c r="AY75" s="166"/>
-      <c r="AZ75" s="166"/>
-      <c r="BA75" s="166"/>
-      <c r="BB75" s="166"/>
-      <c r="BC75" s="166"/>
-      <c r="BD75" s="166"/>
-      <c r="BE75" s="166"/>
-      <c r="BF75" s="166"/>
-      <c r="BG75" s="166"/>
-      <c r="BH75" s="166"/>
-      <c r="BI75" s="166"/>
-      <c r="BJ75" s="166"/>
-      <c r="BK75" s="166"/>
-      <c r="BL75" s="166"/>
+      <c r="D75" s="169"/>
+      <c r="E75" s="169"/>
+      <c r="F75" s="169"/>
+      <c r="G75" s="169"/>
+      <c r="H75" s="169"/>
+      <c r="I75" s="169"/>
+      <c r="J75" s="169"/>
+      <c r="K75" s="169"/>
+      <c r="L75" s="169"/>
+      <c r="M75" s="169"/>
+      <c r="N75" s="169"/>
+      <c r="O75" s="169"/>
+      <c r="P75" s="169"/>
+      <c r="Q75" s="169"/>
+      <c r="R75" s="169"/>
+      <c r="S75" s="169"/>
+      <c r="T75" s="169"/>
+      <c r="U75" s="169"/>
+      <c r="V75" s="169"/>
+      <c r="W75" s="169"/>
+      <c r="X75" s="169"/>
+      <c r="Y75" s="169"/>
+      <c r="Z75" s="169"/>
+      <c r="AA75" s="169"/>
+      <c r="AB75" s="169"/>
+      <c r="AC75" s="169"/>
+      <c r="AD75" s="169"/>
+      <c r="AE75" s="169"/>
+      <c r="AF75" s="169"/>
+      <c r="AG75" s="169"/>
+      <c r="AH75" s="169"/>
+      <c r="AI75" s="169"/>
+      <c r="AJ75" s="169"/>
+      <c r="AK75" s="169"/>
+      <c r="AL75" s="169"/>
+      <c r="AM75" s="169"/>
+      <c r="AN75" s="169"/>
+      <c r="AO75" s="169"/>
+      <c r="AP75" s="169"/>
+      <c r="AQ75" s="169"/>
+      <c r="AR75" s="169"/>
+      <c r="AS75" s="169"/>
+      <c r="AT75" s="169"/>
+      <c r="AU75" s="169"/>
+      <c r="AV75" s="169"/>
+      <c r="AW75" s="169"/>
+      <c r="AX75" s="169"/>
+      <c r="AY75" s="169"/>
+      <c r="AZ75" s="169"/>
+      <c r="BA75" s="169"/>
+      <c r="BB75" s="169"/>
+      <c r="BC75" s="169"/>
+      <c r="BD75" s="169"/>
+      <c r="BE75" s="169"/>
+      <c r="BF75" s="169"/>
+      <c r="BG75" s="169"/>
+      <c r="BH75" s="169"/>
+      <c r="BI75" s="169"/>
+      <c r="BJ75" s="169"/>
+      <c r="BK75" s="169"/>
+      <c r="BL75" s="169"/>
     </row>
     <row r="77" ht="17.55" spans="4:67">
       <c r="D77" s="25" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="Z77" s="25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="AU77" s="25" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="BO77" s="25" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="2:84">
@@ -8166,9 +8169,9 @@
       <c r="CF78" s="96"/>
     </row>
     <row r="79" spans="1:84">
-      <c r="A79" s="167"/>
+      <c r="A79" s="170"/>
       <c r="B79" s="25" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D79" s="29"/>
       <c r="E79" s="34"/>
@@ -8248,26 +8251,26 @@
     <row r="80" spans="4:84">
       <c r="D80" s="29"/>
       <c r="E80" s="82" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F80" s="85"/>
       <c r="G80" s="34"/>
       <c r="H80" s="82" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I80" s="85"/>
       <c r="K80" s="82" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L80" s="85"/>
       <c r="M80" s="34"/>
       <c r="N80" s="66"/>
       <c r="O80" s="100" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
       <c r="P80" s="100"/>
       <c r="Q80" s="126" t="s">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="R80" s="126"/>
       <c r="S80" s="126"/>
@@ -8276,81 +8279,81 @@
       <c r="V80" s="97"/>
       <c r="Z80" s="29"/>
       <c r="AA80" s="82" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB80" s="85"/>
       <c r="AC80" s="34"/>
       <c r="AD80" s="82" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE80" s="85"/>
       <c r="AG80" s="82" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AH80" s="85"/>
       <c r="AI80" s="34"/>
       <c r="AJ80" s="66"/>
-      <c r="AK80" s="142" t="s">
-        <v>10</v>
-      </c>
-      <c r="AL80" s="143"/>
-      <c r="AM80" s="143"/>
-      <c r="AN80" s="143"/>
-      <c r="AO80" s="145"/>
+      <c r="AK80" s="210" t="s">
+        <v>94</v>
+      </c>
+      <c r="AL80" s="211"/>
+      <c r="AM80" s="211"/>
+      <c r="AN80" s="211"/>
+      <c r="AO80" s="212"/>
       <c r="AP80" s="101"/>
       <c r="AQ80" s="101"/>
       <c r="AR80" s="97"/>
       <c r="AU80" s="29"/>
       <c r="AV80" s="82" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW80" s="85"/>
       <c r="AX80" s="34"/>
       <c r="AY80" s="82" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ80" s="85"/>
       <c r="BB80" s="82" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BC80" s="85"/>
       <c r="BD80" s="34"/>
       <c r="BE80" s="66"/>
-      <c r="BF80" s="142" t="s">
-        <v>10</v>
-      </c>
-      <c r="BG80" s="143"/>
-      <c r="BH80" s="143"/>
-      <c r="BI80" s="143"/>
-      <c r="BJ80" s="145"/>
+      <c r="BF80" s="210" t="s">
+        <v>94</v>
+      </c>
+      <c r="BG80" s="211"/>
+      <c r="BH80" s="211"/>
+      <c r="BI80" s="211"/>
+      <c r="BJ80" s="212"/>
       <c r="BK80" s="101"/>
       <c r="BL80" s="97"/>
       <c r="BO80" s="29"/>
-      <c r="BP80" s="221"/>
-      <c r="BQ80" s="224" t="s">
-        <v>96</v>
-      </c>
-      <c r="BR80" s="224"/>
-      <c r="BS80" s="224"/>
-      <c r="BT80" s="224"/>
-      <c r="BU80" s="224"/>
-      <c r="BV80" s="224"/>
-      <c r="BW80" s="224"/>
-      <c r="BX80" s="224"/>
-      <c r="BY80" s="224"/>
-      <c r="BZ80" s="224"/>
-      <c r="CA80" s="224"/>
-      <c r="CB80" s="224"/>
-      <c r="CC80" s="224"/>
-      <c r="CD80" s="224"/>
+      <c r="BP80" s="227"/>
+      <c r="BQ80" s="230" t="s">
+        <v>95</v>
+      </c>
+      <c r="BR80" s="230"/>
+      <c r="BS80" s="230"/>
+      <c r="BT80" s="230"/>
+      <c r="BU80" s="230"/>
+      <c r="BV80" s="230"/>
+      <c r="BW80" s="230"/>
+      <c r="BX80" s="230"/>
+      <c r="BY80" s="230"/>
+      <c r="BZ80" s="230"/>
+      <c r="CA80" s="230"/>
+      <c r="CB80" s="230"/>
+      <c r="CC80" s="230"/>
+      <c r="CD80" s="230"/>
       <c r="CE80" s="87"/>
       <c r="CF80" s="97"/>
     </row>
     <row r="81" spans="1:84">
-      <c r="A81" s="168" t="s">
-        <v>97</v>
-      </c>
-      <c r="B81" s="168"/>
+      <c r="A81" s="171" t="s">
+        <v>96</v>
+      </c>
+      <c r="B81" s="171"/>
       <c r="D81" s="29"/>
       <c r="E81" s="34"/>
       <c r="F81" s="66"/>
@@ -8409,33 +8412,33 @@
       <c r="BL81" s="97"/>
       <c r="BO81" s="29"/>
       <c r="BP81" s="87"/>
-      <c r="BQ81" s="224"/>
-      <c r="BR81" s="224"/>
-      <c r="BS81" s="224"/>
-      <c r="BT81" s="224"/>
-      <c r="BU81" s="224"/>
-      <c r="BV81" s="224"/>
-      <c r="BW81" s="224"/>
-      <c r="BX81" s="224"/>
-      <c r="BY81" s="224"/>
-      <c r="BZ81" s="224"/>
-      <c r="CA81" s="224"/>
-      <c r="CB81" s="224"/>
-      <c r="CC81" s="224"/>
-      <c r="CD81" s="224"/>
+      <c r="BQ81" s="230"/>
+      <c r="BR81" s="230"/>
+      <c r="BS81" s="230"/>
+      <c r="BT81" s="230"/>
+      <c r="BU81" s="230"/>
+      <c r="BV81" s="230"/>
+      <c r="BW81" s="230"/>
+      <c r="BX81" s="230"/>
+      <c r="BY81" s="230"/>
+      <c r="BZ81" s="230"/>
+      <c r="CA81" s="230"/>
+      <c r="CB81" s="230"/>
+      <c r="CC81" s="230"/>
+      <c r="CD81" s="230"/>
       <c r="CE81" s="87"/>
       <c r="CF81" s="97"/>
     </row>
     <row r="82" spans="1:84">
-      <c r="A82" s="168"/>
-      <c r="B82" s="168"/>
+      <c r="A82" s="171"/>
+      <c r="B82" s="171"/>
       <c r="D82" s="29"/>
-      <c r="E82" s="176" t="s">
-        <v>98</v>
-      </c>
-      <c r="F82" s="177"/>
-      <c r="G82" s="177"/>
-      <c r="H82" s="177"/>
+      <c r="E82" s="179" t="s">
+        <v>97</v>
+      </c>
+      <c r="F82" s="180"/>
+      <c r="G82" s="180"/>
+      <c r="H82" s="180"/>
       <c r="I82" s="34"/>
       <c r="J82" s="34"/>
       <c r="K82" s="34"/>
@@ -8451,12 +8454,12 @@
       <c r="U82" s="34"/>
       <c r="V82" s="97"/>
       <c r="Z82" s="29"/>
-      <c r="AA82" s="176" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB82" s="177"/>
-      <c r="AC82" s="177"/>
-      <c r="AD82" s="177"/>
+      <c r="AA82" s="179" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB82" s="180"/>
+      <c r="AC82" s="180"/>
+      <c r="AD82" s="180"/>
       <c r="AE82" s="34"/>
       <c r="AF82" s="34"/>
       <c r="AG82" s="34"/>
@@ -8472,13 +8475,13 @@
       <c r="AQ82" s="34"/>
       <c r="AR82" s="97"/>
       <c r="AU82" s="29"/>
-      <c r="AV82" s="176" t="s">
-        <v>100</v>
-      </c>
-      <c r="AW82" s="176"/>
-      <c r="AX82" s="176"/>
-      <c r="AY82" s="176"/>
-      <c r="AZ82" s="176"/>
+      <c r="AV82" s="179" t="s">
+        <v>99</v>
+      </c>
+      <c r="AW82" s="179"/>
+      <c r="AX82" s="179"/>
+      <c r="AY82" s="179"/>
+      <c r="AZ82" s="179"/>
       <c r="BA82" s="34"/>
       <c r="BB82" s="34"/>
       <c r="BC82" s="34"/>
@@ -8492,27 +8495,27 @@
       <c r="BK82" s="34"/>
       <c r="BL82" s="97"/>
       <c r="BO82" s="29"/>
-      <c r="BP82" s="222"/>
-      <c r="BQ82" s="224"/>
-      <c r="BR82" s="224"/>
-      <c r="BS82" s="224"/>
-      <c r="BT82" s="224"/>
-      <c r="BU82" s="224"/>
-      <c r="BV82" s="224"/>
-      <c r="BW82" s="224"/>
-      <c r="BX82" s="224"/>
-      <c r="BY82" s="224"/>
-      <c r="BZ82" s="224"/>
-      <c r="CA82" s="224"/>
-      <c r="CB82" s="224"/>
-      <c r="CC82" s="224"/>
-      <c r="CD82" s="224"/>
+      <c r="BP82" s="228"/>
+      <c r="BQ82" s="230"/>
+      <c r="BR82" s="230"/>
+      <c r="BS82" s="230"/>
+      <c r="BT82" s="230"/>
+      <c r="BU82" s="230"/>
+      <c r="BV82" s="230"/>
+      <c r="BW82" s="230"/>
+      <c r="BX82" s="230"/>
+      <c r="BY82" s="230"/>
+      <c r="BZ82" s="230"/>
+      <c r="CA82" s="230"/>
+      <c r="CB82" s="230"/>
+      <c r="CC82" s="230"/>
+      <c r="CD82" s="230"/>
       <c r="CE82" s="87"/>
       <c r="CF82" s="97"/>
     </row>
     <row r="83" spans="1:84">
-      <c r="A83" s="168"/>
-      <c r="B83" s="168"/>
+      <c r="A83" s="171"/>
+      <c r="B83" s="171"/>
       <c r="D83" s="29"/>
       <c r="E83" s="34"/>
       <c r="F83" s="34"/>
@@ -8571,28 +8574,28 @@
       <c r="BL83" s="97"/>
       <c r="BO83" s="29"/>
       <c r="BP83" s="87"/>
-      <c r="BQ83" s="224"/>
-      <c r="BR83" s="224"/>
-      <c r="BS83" s="224"/>
-      <c r="BT83" s="224"/>
-      <c r="BU83" s="224"/>
-      <c r="BV83" s="224"/>
-      <c r="BW83" s="224"/>
-      <c r="BX83" s="224"/>
-      <c r="BY83" s="224"/>
-      <c r="BZ83" s="224"/>
-      <c r="CA83" s="224"/>
-      <c r="CB83" s="224"/>
-      <c r="CC83" s="224"/>
-      <c r="CD83" s="224"/>
+      <c r="BQ83" s="230"/>
+      <c r="BR83" s="230"/>
+      <c r="BS83" s="230"/>
+      <c r="BT83" s="230"/>
+      <c r="BU83" s="230"/>
+      <c r="BV83" s="230"/>
+      <c r="BW83" s="230"/>
+      <c r="BX83" s="230"/>
+      <c r="BY83" s="230"/>
+      <c r="BZ83" s="230"/>
+      <c r="CA83" s="230"/>
+      <c r="CB83" s="230"/>
+      <c r="CC83" s="230"/>
+      <c r="CD83" s="230"/>
       <c r="CE83" s="87"/>
       <c r="CF83" s="97"/>
     </row>
     <row r="84" ht="20.4" spans="1:84">
-      <c r="A84" s="168"/>
-      <c r="B84" s="168"/>
-      <c r="D84" s="169" t="s">
-        <v>101</v>
+      <c r="A84" s="171"/>
+      <c r="B84" s="171"/>
+      <c r="D84" s="172" t="s">
+        <v>100</v>
       </c>
       <c r="E84" s="107"/>
       <c r="F84" s="107"/>
@@ -8600,54 +8603,54 @@
       <c r="H84" s="107"/>
       <c r="I84" s="107"/>
       <c r="J84" s="107" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K84" s="107"/>
       <c r="L84" s="107"/>
       <c r="M84" s="107"/>
       <c r="N84" s="107" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O84" s="107"/>
       <c r="P84" s="107"/>
       <c r="Q84" s="78"/>
       <c r="R84" s="107" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="S84" s="107"/>
       <c r="T84" s="107"/>
       <c r="U84" s="107"/>
       <c r="V84" s="98"/>
-      <c r="Z84" s="192"/>
+      <c r="Z84" s="195"/>
       <c r="AA84" s="55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AB84" s="56"/>
       <c r="AC84" s="56"/>
       <c r="AD84" s="56"/>
       <c r="AE84" s="56" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AF84" s="56"/>
       <c r="AG84" s="56"/>
       <c r="AH84" s="56"/>
-      <c r="AI84" s="203" t="s">
+      <c r="AI84" s="206" t="s">
+        <v>106</v>
+      </c>
+      <c r="AJ84" s="206"/>
+      <c r="AK84" s="206"/>
+      <c r="AL84" s="206"/>
+      <c r="AM84" s="206"/>
+      <c r="AN84" s="206" t="s">
         <v>107</v>
       </c>
-      <c r="AJ84" s="203"/>
-      <c r="AK84" s="203"/>
-      <c r="AL84" s="203"/>
-      <c r="AM84" s="203"/>
-      <c r="AN84" s="203" t="s">
-        <v>108</v>
-      </c>
-      <c r="AO84" s="203"/>
-      <c r="AP84" s="203"/>
-      <c r="AQ84" s="207"/>
+      <c r="AO84" s="206"/>
+      <c r="AP84" s="206"/>
+      <c r="AQ84" s="213"/>
       <c r="AR84" s="98"/>
       <c r="AU84" s="29"/>
       <c r="AV84" s="93" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AW84" s="93"/>
       <c r="AX84" s="93"/>
@@ -8663,30 +8666,30 @@
       <c r="BH84" s="93"/>
       <c r="BI84" s="93"/>
       <c r="BJ84" s="93"/>
-      <c r="BK84" s="218"/>
+      <c r="BK84" s="224"/>
       <c r="BL84" s="97"/>
       <c r="BO84" s="29"/>
-      <c r="BP84" s="223"/>
-      <c r="BQ84" s="224"/>
-      <c r="BR84" s="224"/>
-      <c r="BS84" s="224"/>
-      <c r="BT84" s="224"/>
-      <c r="BU84" s="224"/>
-      <c r="BV84" s="224"/>
-      <c r="BW84" s="224"/>
-      <c r="BX84" s="224"/>
-      <c r="BY84" s="224"/>
-      <c r="BZ84" s="224"/>
-      <c r="CA84" s="224"/>
-      <c r="CB84" s="224"/>
-      <c r="CC84" s="224"/>
-      <c r="CD84" s="224"/>
-      <c r="CE84" s="226"/>
+      <c r="BP84" s="229"/>
+      <c r="BQ84" s="230"/>
+      <c r="BR84" s="230"/>
+      <c r="BS84" s="230"/>
+      <c r="BT84" s="230"/>
+      <c r="BU84" s="230"/>
+      <c r="BV84" s="230"/>
+      <c r="BW84" s="230"/>
+      <c r="BX84" s="230"/>
+      <c r="BY84" s="230"/>
+      <c r="BZ84" s="230"/>
+      <c r="CA84" s="230"/>
+      <c r="CB84" s="230"/>
+      <c r="CC84" s="230"/>
+      <c r="CD84" s="230"/>
+      <c r="CE84" s="232"/>
       <c r="CF84" s="97"/>
     </row>
     <row r="85" ht="17.6" spans="1:84">
-      <c r="A85" s="168"/>
-      <c r="B85" s="168"/>
+      <c r="A85" s="171"/>
+      <c r="B85" s="171"/>
       <c r="D85" s="31">
         <v>500</v>
       </c>
@@ -8714,36 +8717,36 @@
       <c r="T85" s="107"/>
       <c r="U85" s="107"/>
       <c r="V85" s="98"/>
-      <c r="Z85" s="193"/>
-      <c r="AA85" s="194">
+      <c r="Z85" s="196"/>
+      <c r="AA85" s="197">
         <v>40000</v>
       </c>
-      <c r="AB85" s="195"/>
-      <c r="AC85" s="195"/>
-      <c r="AD85" s="195"/>
-      <c r="AE85" s="195">
+      <c r="AB85" s="198"/>
+      <c r="AC85" s="198"/>
+      <c r="AD85" s="198"/>
+      <c r="AE85" s="198">
         <v>10000</v>
       </c>
-      <c r="AF85" s="195"/>
-      <c r="AG85" s="195"/>
-      <c r="AH85" s="195"/>
-      <c r="AI85" s="204">
+      <c r="AF85" s="198"/>
+      <c r="AG85" s="198"/>
+      <c r="AH85" s="198"/>
+      <c r="AI85" s="207">
         <v>10000</v>
       </c>
-      <c r="AJ85" s="204"/>
-      <c r="AK85" s="204"/>
-      <c r="AL85" s="204"/>
-      <c r="AM85" s="204"/>
-      <c r="AN85" s="204">
+      <c r="AJ85" s="207"/>
+      <c r="AK85" s="207"/>
+      <c r="AL85" s="207"/>
+      <c r="AM85" s="207"/>
+      <c r="AN85" s="207">
         <v>20000</v>
       </c>
-      <c r="AO85" s="204"/>
-      <c r="AP85" s="204"/>
-      <c r="AQ85" s="208"/>
+      <c r="AO85" s="207"/>
+      <c r="AP85" s="207"/>
+      <c r="AQ85" s="214"/>
       <c r="AR85" s="98"/>
       <c r="AU85" s="29"/>
       <c r="AV85" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AW85" s="16"/>
       <c r="AX85" s="16"/>
@@ -8753,42 +8756,42 @@
       </c>
       <c r="BA85" s="93"/>
       <c r="BB85" s="93"/>
-      <c r="BC85" s="216"/>
-      <c r="BD85" s="216"/>
+      <c r="BC85" s="222"/>
+      <c r="BD85" s="222"/>
       <c r="BE85" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BF85" s="16"/>
-      <c r="BG85" s="217">
+      <c r="BG85" s="223">
         <v>0.1</v>
       </c>
-      <c r="BH85" s="217"/>
-      <c r="BI85" s="217"/>
-      <c r="BJ85" s="217"/>
-      <c r="BK85" s="219"/>
+      <c r="BH85" s="223"/>
+      <c r="BI85" s="223"/>
+      <c r="BJ85" s="223"/>
+      <c r="BK85" s="225"/>
       <c r="BL85" s="97"/>
       <c r="BO85" s="29"/>
-      <c r="BP85" s="222"/>
-      <c r="BQ85" s="224"/>
-      <c r="BR85" s="224"/>
-      <c r="BS85" s="224"/>
-      <c r="BT85" s="224"/>
-      <c r="BU85" s="224"/>
-      <c r="BV85" s="224"/>
-      <c r="BW85" s="224"/>
-      <c r="BX85" s="224"/>
-      <c r="BY85" s="224"/>
-      <c r="BZ85" s="224"/>
-      <c r="CA85" s="224"/>
-      <c r="CB85" s="224"/>
-      <c r="CC85" s="224"/>
-      <c r="CD85" s="224"/>
-      <c r="CE85" s="227"/>
+      <c r="BP85" s="228"/>
+      <c r="BQ85" s="230"/>
+      <c r="BR85" s="230"/>
+      <c r="BS85" s="230"/>
+      <c r="BT85" s="230"/>
+      <c r="BU85" s="230"/>
+      <c r="BV85" s="230"/>
+      <c r="BW85" s="230"/>
+      <c r="BX85" s="230"/>
+      <c r="BY85" s="230"/>
+      <c r="BZ85" s="230"/>
+      <c r="CA85" s="230"/>
+      <c r="CB85" s="230"/>
+      <c r="CC85" s="230"/>
+      <c r="CD85" s="230"/>
+      <c r="CE85" s="233"/>
       <c r="CF85" s="97"/>
     </row>
     <row r="86" ht="17.6" spans="1:84">
-      <c r="A86" s="168"/>
-      <c r="B86" s="168"/>
+      <c r="A86" s="171"/>
+      <c r="B86" s="171"/>
       <c r="D86" s="29"/>
       <c r="E86" s="51"/>
       <c r="F86" s="51"/>
@@ -8837,36 +8840,36 @@
       </c>
       <c r="BA86" s="93"/>
       <c r="BB86" s="93"/>
-      <c r="BC86" s="216"/>
-      <c r="BD86" s="216"/>
+      <c r="BC86" s="222"/>
+      <c r="BD86" s="222"/>
       <c r="BE86" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BF86" s="16"/>
-      <c r="BG86" s="217">
+      <c r="BG86" s="223">
         <v>0.1</v>
       </c>
-      <c r="BH86" s="217"/>
-      <c r="BI86" s="217"/>
-      <c r="BJ86" s="217"/>
-      <c r="BK86" s="216"/>
+      <c r="BH86" s="223"/>
+      <c r="BI86" s="223"/>
+      <c r="BJ86" s="223"/>
+      <c r="BK86" s="222"/>
       <c r="BL86" s="97"/>
       <c r="BO86" s="29"/>
-      <c r="BP86" s="222"/>
-      <c r="BQ86" s="224"/>
-      <c r="BR86" s="224"/>
-      <c r="BS86" s="224"/>
-      <c r="BT86" s="224"/>
-      <c r="BU86" s="224"/>
-      <c r="BV86" s="224"/>
-      <c r="BW86" s="224"/>
-      <c r="BX86" s="224"/>
-      <c r="BY86" s="224"/>
-      <c r="BZ86" s="224"/>
-      <c r="CA86" s="224"/>
-      <c r="CB86" s="224"/>
-      <c r="CC86" s="224"/>
-      <c r="CD86" s="224"/>
+      <c r="BP86" s="228"/>
+      <c r="BQ86" s="230"/>
+      <c r="BR86" s="230"/>
+      <c r="BS86" s="230"/>
+      <c r="BT86" s="230"/>
+      <c r="BU86" s="230"/>
+      <c r="BV86" s="230"/>
+      <c r="BW86" s="230"/>
+      <c r="BX86" s="230"/>
+      <c r="BY86" s="230"/>
+      <c r="BZ86" s="230"/>
+      <c r="CA86" s="230"/>
+      <c r="CB86" s="230"/>
+      <c r="CC86" s="230"/>
+      <c r="CD86" s="230"/>
       <c r="CE86" s="87"/>
       <c r="CF86" s="97"/>
     </row>
@@ -8890,32 +8893,32 @@
       <c r="T87" s="34"/>
       <c r="U87" s="34"/>
       <c r="V87" s="97"/>
-      <c r="Z87" s="192"/>
+      <c r="Z87" s="195"/>
       <c r="AA87" s="55" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AB87" s="56"/>
       <c r="AC87" s="56"/>
       <c r="AD87" s="56"/>
       <c r="AE87" s="56" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AF87" s="56"/>
       <c r="AG87" s="56"/>
       <c r="AH87" s="56"/>
-      <c r="AI87" s="203" t="s">
+      <c r="AI87" s="206" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ87" s="206"/>
+      <c r="AK87" s="206"/>
+      <c r="AL87" s="206"/>
+      <c r="AM87" s="206"/>
+      <c r="AN87" s="206" t="s">
         <v>114</v>
       </c>
-      <c r="AJ87" s="203"/>
-      <c r="AK87" s="203"/>
-      <c r="AL87" s="203"/>
-      <c r="AM87" s="203"/>
-      <c r="AN87" s="203" t="s">
-        <v>115</v>
-      </c>
-      <c r="AO87" s="203"/>
-      <c r="AP87" s="203"/>
-      <c r="AQ87" s="207"/>
+      <c r="AO87" s="206"/>
+      <c r="AP87" s="206"/>
+      <c r="AQ87" s="213"/>
       <c r="AR87" s="97"/>
       <c r="AU87" s="29"/>
       <c r="AV87" s="16"/>
@@ -8927,50 +8930,50 @@
       </c>
       <c r="BA87" s="93"/>
       <c r="BB87" s="93"/>
-      <c r="BC87" s="216"/>
-      <c r="BD87" s="216"/>
+      <c r="BC87" s="222"/>
+      <c r="BD87" s="222"/>
       <c r="BE87" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BF87" s="16"/>
-      <c r="BG87" s="217">
+      <c r="BG87" s="223">
         <v>0.1</v>
       </c>
-      <c r="BH87" s="217"/>
-      <c r="BI87" s="217"/>
-      <c r="BJ87" s="217"/>
-      <c r="BK87" s="219" t="s">
-        <v>40</v>
+      <c r="BH87" s="223"/>
+      <c r="BI87" s="223"/>
+      <c r="BJ87" s="223"/>
+      <c r="BK87" s="225" t="s">
+        <v>36</v>
       </c>
       <c r="BL87" s="97"/>
       <c r="BO87" s="29"/>
-      <c r="BP87" s="222"/>
-      <c r="BQ87" s="224"/>
-      <c r="BR87" s="224"/>
-      <c r="BS87" s="224"/>
-      <c r="BT87" s="224"/>
-      <c r="BU87" s="224"/>
-      <c r="BV87" s="224"/>
-      <c r="BW87" s="224"/>
-      <c r="BX87" s="224"/>
-      <c r="BY87" s="224"/>
-      <c r="BZ87" s="224"/>
-      <c r="CA87" s="224"/>
-      <c r="CB87" s="224"/>
-      <c r="CC87" s="224"/>
-      <c r="CD87" s="224"/>
-      <c r="CE87" s="227"/>
+      <c r="BP87" s="228"/>
+      <c r="BQ87" s="230"/>
+      <c r="BR87" s="230"/>
+      <c r="BS87" s="230"/>
+      <c r="BT87" s="230"/>
+      <c r="BU87" s="230"/>
+      <c r="BV87" s="230"/>
+      <c r="BW87" s="230"/>
+      <c r="BX87" s="230"/>
+      <c r="BY87" s="230"/>
+      <c r="BZ87" s="230"/>
+      <c r="CA87" s="230"/>
+      <c r="CB87" s="230"/>
+      <c r="CC87" s="230"/>
+      <c r="CD87" s="230"/>
+      <c r="CE87" s="233"/>
       <c r="CF87" s="97"/>
     </row>
     <row r="88" ht="20.4" spans="4:84">
       <c r="D88" s="29"/>
-      <c r="E88" s="178" t="s">
-        <v>116</v>
-      </c>
-      <c r="F88" s="178"/>
-      <c r="G88" s="178"/>
-      <c r="H88" s="178"/>
-      <c r="I88" s="178"/>
+      <c r="E88" s="181" t="s">
+        <v>115</v>
+      </c>
+      <c r="F88" s="181"/>
+      <c r="G88" s="181"/>
+      <c r="H88" s="181"/>
+      <c r="I88" s="181"/>
       <c r="J88" s="52"/>
       <c r="K88" s="78"/>
       <c r="L88" s="34"/>
@@ -8985,30 +8988,30 @@
       <c r="U88" s="34"/>
       <c r="V88" s="97"/>
       <c r="Y88" s="34"/>
-      <c r="Z88" s="192"/>
-      <c r="AA88" s="196"/>
+      <c r="Z88" s="195"/>
+      <c r="AA88" s="199"/>
       <c r="AB88" s="27"/>
       <c r="AC88" s="27"/>
       <c r="AD88" s="27"/>
-      <c r="AE88" s="198">
+      <c r="AE88" s="201">
         <v>10000</v>
       </c>
-      <c r="AF88" s="198"/>
-      <c r="AG88" s="198"/>
-      <c r="AH88" s="198"/>
-      <c r="AI88" s="205">
+      <c r="AF88" s="201"/>
+      <c r="AG88" s="201"/>
+      <c r="AH88" s="201"/>
+      <c r="AI88" s="208">
         <v>10000</v>
       </c>
-      <c r="AJ88" s="205"/>
-      <c r="AK88" s="205"/>
-      <c r="AL88" s="205"/>
-      <c r="AM88" s="205"/>
-      <c r="AN88" s="205">
+      <c r="AJ88" s="208"/>
+      <c r="AK88" s="208"/>
+      <c r="AL88" s="208"/>
+      <c r="AM88" s="208"/>
+      <c r="AN88" s="208">
         <v>20000</v>
       </c>
-      <c r="AO88" s="205"/>
-      <c r="AP88" s="205"/>
-      <c r="AQ88" s="209"/>
+      <c r="AO88" s="208"/>
+      <c r="AP88" s="208"/>
+      <c r="AQ88" s="215"/>
       <c r="AR88" s="97"/>
       <c r="AU88" s="29"/>
       <c r="AV88" s="16"/>
@@ -9020,44 +9023,44 @@
       </c>
       <c r="BA88" s="93"/>
       <c r="BB88" s="93"/>
-      <c r="BC88" s="216"/>
+      <c r="BC88" s="222"/>
       <c r="BD88" s="93"/>
       <c r="BE88" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BF88" s="16"/>
-      <c r="BG88" s="217">
+      <c r="BG88" s="223">
         <v>0.1</v>
       </c>
-      <c r="BH88" s="217"/>
-      <c r="BI88" s="217"/>
-      <c r="BJ88" s="217"/>
-      <c r="BK88" s="218"/>
+      <c r="BH88" s="223"/>
+      <c r="BI88" s="223"/>
+      <c r="BJ88" s="223"/>
+      <c r="BK88" s="224"/>
       <c r="BL88" s="97"/>
       <c r="BO88" s="29"/>
-      <c r="BP88" s="222"/>
-      <c r="BQ88" s="224"/>
-      <c r="BR88" s="224"/>
-      <c r="BS88" s="224"/>
-      <c r="BT88" s="224"/>
-      <c r="BU88" s="224"/>
-      <c r="BV88" s="224"/>
-      <c r="BW88" s="224"/>
-      <c r="BX88" s="224"/>
-      <c r="BY88" s="224"/>
-      <c r="BZ88" s="224"/>
-      <c r="CA88" s="224"/>
-      <c r="CB88" s="224"/>
-      <c r="CC88" s="224"/>
-      <c r="CD88" s="224"/>
-      <c r="CE88" s="226"/>
+      <c r="BP88" s="228"/>
+      <c r="BQ88" s="230"/>
+      <c r="BR88" s="230"/>
+      <c r="BS88" s="230"/>
+      <c r="BT88" s="230"/>
+      <c r="BU88" s="230"/>
+      <c r="BV88" s="230"/>
+      <c r="BW88" s="230"/>
+      <c r="BX88" s="230"/>
+      <c r="BY88" s="230"/>
+      <c r="BZ88" s="230"/>
+      <c r="CA88" s="230"/>
+      <c r="CB88" s="230"/>
+      <c r="CC88" s="230"/>
+      <c r="CD88" s="230"/>
+      <c r="CE88" s="232"/>
       <c r="CF88" s="97"/>
     </row>
     <row r="89" ht="20.4" spans="1:84">
-      <c r="A89" s="170" t="s">
-        <v>117</v>
-      </c>
-      <c r="B89" s="171"/>
+      <c r="A89" s="173" t="s">
+        <v>116</v>
+      </c>
+      <c r="B89" s="174"/>
       <c r="D89" s="29"/>
       <c r="E89" s="107"/>
       <c r="F89" s="107"/>
@@ -9078,32 +9081,32 @@
       <c r="U89" s="34"/>
       <c r="V89" s="97"/>
       <c r="Y89" s="34"/>
-      <c r="Z89" s="193"/>
-      <c r="AA89" s="197">
+      <c r="Z89" s="196"/>
+      <c r="AA89" s="200">
         <v>40000</v>
       </c>
-      <c r="AB89" s="198"/>
-      <c r="AC89" s="198"/>
-      <c r="AD89" s="198"/>
+      <c r="AB89" s="201"/>
+      <c r="AC89" s="201"/>
+      <c r="AD89" s="201"/>
       <c r="AE89" s="107" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AF89" s="107"/>
       <c r="AG89" s="107"/>
       <c r="AH89" s="107"/>
       <c r="AI89" s="26" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AJ89" s="26"/>
       <c r="AK89" s="26"/>
       <c r="AL89" s="26"/>
       <c r="AM89" s="26"/>
       <c r="AN89" s="26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AO89" s="26"/>
       <c r="AP89" s="26"/>
-      <c r="AQ89" s="210"/>
+      <c r="AQ89" s="216"/>
       <c r="AR89" s="97"/>
       <c r="AU89" s="29"/>
       <c r="AV89" s="16"/>
@@ -9115,122 +9118,122 @@
       </c>
       <c r="BA89" s="93"/>
       <c r="BB89" s="93"/>
-      <c r="BC89" s="216"/>
+      <c r="BC89" s="222"/>
       <c r="BD89" s="93"/>
       <c r="BE89" s="16" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="BF89" s="16"/>
-      <c r="BG89" s="217">
+      <c r="BG89" s="223">
         <v>0.1</v>
       </c>
-      <c r="BH89" s="217"/>
-      <c r="BI89" s="217"/>
-      <c r="BJ89" s="217"/>
-      <c r="BK89" s="218"/>
+      <c r="BH89" s="223"/>
+      <c r="BI89" s="223"/>
+      <c r="BJ89" s="223"/>
+      <c r="BK89" s="224"/>
       <c r="BL89" s="97"/>
       <c r="BO89" s="29"/>
-      <c r="BP89" s="222"/>
-      <c r="BQ89" s="224"/>
-      <c r="BR89" s="224"/>
-      <c r="BS89" s="224"/>
-      <c r="BT89" s="224"/>
-      <c r="BU89" s="224"/>
-      <c r="BV89" s="224"/>
-      <c r="BW89" s="224"/>
-      <c r="BX89" s="224"/>
-      <c r="BY89" s="224"/>
-      <c r="BZ89" s="224"/>
-      <c r="CA89" s="224"/>
-      <c r="CB89" s="224"/>
-      <c r="CC89" s="224"/>
-      <c r="CD89" s="224"/>
-      <c r="CE89" s="226"/>
+      <c r="BP89" s="228"/>
+      <c r="BQ89" s="230"/>
+      <c r="BR89" s="230"/>
+      <c r="BS89" s="230"/>
+      <c r="BT89" s="230"/>
+      <c r="BU89" s="230"/>
+      <c r="BV89" s="230"/>
+      <c r="BW89" s="230"/>
+      <c r="BX89" s="230"/>
+      <c r="BY89" s="230"/>
+      <c r="BZ89" s="230"/>
+      <c r="CA89" s="230"/>
+      <c r="CB89" s="230"/>
+      <c r="CC89" s="230"/>
+      <c r="CD89" s="230"/>
+      <c r="CE89" s="232"/>
       <c r="CF89" s="97"/>
     </row>
     <row r="90" spans="1:84">
-      <c r="A90" s="171"/>
-      <c r="B90" s="171"/>
-      <c r="D90" s="172" t="s">
-        <v>121</v>
+      <c r="A90" s="174"/>
+      <c r="B90" s="174"/>
+      <c r="D90" s="175" t="s">
+        <v>120</v>
       </c>
       <c r="E90" s="27"/>
       <c r="F90" s="27"/>
       <c r="G90" s="148"/>
       <c r="H90" s="27" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I90" s="27"/>
       <c r="J90" s="27"/>
       <c r="K90" s="27"/>
       <c r="L90" s="148"/>
       <c r="M90" s="27" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="N90" s="27"/>
       <c r="O90" s="27"/>
-      <c r="P90" s="185"/>
+      <c r="P90" s="188"/>
       <c r="Q90" s="66" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="R90" s="66"/>
       <c r="S90" s="66"/>
       <c r="T90" s="66"/>
       <c r="U90" s="66"/>
       <c r="V90" s="97"/>
-      <c r="Z90" s="193"/>
-      <c r="AA90" s="194"/>
-      <c r="AB90" s="195"/>
-      <c r="AC90" s="195"/>
-      <c r="AD90" s="195"/>
-      <c r="AE90" s="195">
+      <c r="Z90" s="196"/>
+      <c r="AA90" s="197"/>
+      <c r="AB90" s="198"/>
+      <c r="AC90" s="198"/>
+      <c r="AD90" s="198"/>
+      <c r="AE90" s="198">
         <v>10000</v>
       </c>
-      <c r="AF90" s="195"/>
-      <c r="AG90" s="195"/>
-      <c r="AH90" s="195"/>
-      <c r="AI90" s="206">
+      <c r="AF90" s="198"/>
+      <c r="AG90" s="198"/>
+      <c r="AH90" s="198"/>
+      <c r="AI90" s="209">
         <v>3000</v>
       </c>
-      <c r="AJ90" s="206"/>
-      <c r="AK90" s="206"/>
-      <c r="AL90" s="206"/>
-      <c r="AM90" s="206"/>
-      <c r="AN90" s="204">
+      <c r="AJ90" s="209"/>
+      <c r="AK90" s="209"/>
+      <c r="AL90" s="209"/>
+      <c r="AM90" s="209"/>
+      <c r="AN90" s="207">
         <v>4000</v>
       </c>
-      <c r="AO90" s="204"/>
-      <c r="AP90" s="204"/>
-      <c r="AQ90" s="208"/>
+      <c r="AO90" s="207"/>
+      <c r="AP90" s="207"/>
+      <c r="AQ90" s="214"/>
       <c r="AR90" s="97"/>
       <c r="AU90" s="29"/>
       <c r="BL90" s="97"/>
       <c r="BO90" s="29"/>
       <c r="BP90" s="46"/>
-      <c r="BQ90" s="224"/>
-      <c r="BR90" s="224"/>
-      <c r="BS90" s="224"/>
-      <c r="BT90" s="224"/>
-      <c r="BU90" s="224"/>
-      <c r="BV90" s="224"/>
-      <c r="BW90" s="224"/>
-      <c r="BX90" s="224"/>
-      <c r="BY90" s="224"/>
-      <c r="BZ90" s="224"/>
-      <c r="CA90" s="224"/>
-      <c r="CB90" s="224"/>
-      <c r="CC90" s="224"/>
-      <c r="CD90" s="224"/>
+      <c r="BQ90" s="230"/>
+      <c r="BR90" s="230"/>
+      <c r="BS90" s="230"/>
+      <c r="BT90" s="230"/>
+      <c r="BU90" s="230"/>
+      <c r="BV90" s="230"/>
+      <c r="BW90" s="230"/>
+      <c r="BX90" s="230"/>
+      <c r="BY90" s="230"/>
+      <c r="BZ90" s="230"/>
+      <c r="CA90" s="230"/>
+      <c r="CB90" s="230"/>
+      <c r="CC90" s="230"/>
+      <c r="CD90" s="230"/>
       <c r="CE90" s="46"/>
       <c r="CF90" s="97"/>
     </row>
     <row r="91" ht="20.4" spans="1:84">
-      <c r="A91" s="171"/>
-      <c r="B91" s="171"/>
+      <c r="A91" s="174"/>
+      <c r="B91" s="174"/>
       <c r="D91" s="29">
         <v>360</v>
       </c>
-      <c r="G91" s="162"/>
+      <c r="G91" s="165"/>
       <c r="H91" s="27">
         <v>60</v>
       </c>
@@ -9243,7 +9246,7 @@
       </c>
       <c r="N91" s="27"/>
       <c r="O91" s="27"/>
-      <c r="P91" s="185"/>
+      <c r="P91" s="188"/>
       <c r="Q91" s="66">
         <v>150</v>
       </c>
@@ -9253,12 +9256,12 @@
       <c r="U91" s="66"/>
       <c r="V91" s="97"/>
       <c r="Z91" s="31"/>
-      <c r="AA91" s="199"/>
-      <c r="AB91" s="199"/>
-      <c r="AC91" s="199"/>
-      <c r="AD91" s="199"/>
-      <c r="AE91" s="199"/>
-      <c r="AF91" s="199"/>
+      <c r="AA91" s="202"/>
+      <c r="AB91" s="202"/>
+      <c r="AC91" s="202"/>
+      <c r="AD91" s="202"/>
+      <c r="AE91" s="202"/>
+      <c r="AF91" s="202"/>
       <c r="AG91" s="42"/>
       <c r="AH91" s="41"/>
       <c r="AI91" s="41"/>
@@ -9272,58 +9275,58 @@
       <c r="AQ91" s="42"/>
       <c r="AR91" s="97"/>
       <c r="AU91" s="29"/>
-      <c r="AV91" s="213" t="s">
-        <v>125</v>
-      </c>
-      <c r="AW91" s="213"/>
-      <c r="AX91" s="213"/>
-      <c r="AY91" s="213"/>
-      <c r="AZ91" s="213"/>
-      <c r="BA91" s="213"/>
-      <c r="BB91" s="213"/>
-      <c r="BC91" s="213"/>
+      <c r="AV91" s="219" t="s">
+        <v>124</v>
+      </c>
+      <c r="AW91" s="219"/>
+      <c r="AX91" s="219"/>
+      <c r="AY91" s="219"/>
+      <c r="AZ91" s="219"/>
+      <c r="BA91" s="219"/>
+      <c r="BB91" s="219"/>
+      <c r="BC91" s="219"/>
       <c r="BD91" s="93" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BE91" s="93"/>
       <c r="BF91" s="93"/>
       <c r="BG91" s="93" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BH91" s="93"/>
       <c r="BI91" s="93"/>
       <c r="BJ91" s="93"/>
-      <c r="BK91" s="218"/>
+      <c r="BK91" s="224"/>
       <c r="BL91" s="97"/>
       <c r="BO91" s="29"/>
-      <c r="BP91" s="223"/>
-      <c r="BQ91" s="224"/>
-      <c r="BR91" s="224"/>
-      <c r="BS91" s="224"/>
-      <c r="BT91" s="224"/>
-      <c r="BU91" s="224"/>
-      <c r="BV91" s="224"/>
-      <c r="BW91" s="224"/>
-      <c r="BX91" s="224"/>
-      <c r="BY91" s="224"/>
-      <c r="BZ91" s="224"/>
-      <c r="CA91" s="224"/>
-      <c r="CB91" s="224"/>
-      <c r="CC91" s="224"/>
-      <c r="CD91" s="224"/>
-      <c r="CE91" s="226"/>
+      <c r="BP91" s="229"/>
+      <c r="BQ91" s="230"/>
+      <c r="BR91" s="230"/>
+      <c r="BS91" s="230"/>
+      <c r="BT91" s="230"/>
+      <c r="BU91" s="230"/>
+      <c r="BV91" s="230"/>
+      <c r="BW91" s="230"/>
+      <c r="BX91" s="230"/>
+      <c r="BY91" s="230"/>
+      <c r="BZ91" s="230"/>
+      <c r="CA91" s="230"/>
+      <c r="CB91" s="230"/>
+      <c r="CC91" s="230"/>
+      <c r="CD91" s="230"/>
+      <c r="CE91" s="232"/>
       <c r="CF91" s="97"/>
     </row>
     <row r="92" ht="17.6" spans="1:84">
-      <c r="A92" s="171"/>
-      <c r="B92" s="171"/>
+      <c r="A92" s="174"/>
+      <c r="B92" s="174"/>
       <c r="D92" s="29"/>
       <c r="E92" s="34"/>
       <c r="F92" s="34"/>
-      <c r="G92" s="162"/>
+      <c r="G92" s="165"/>
       <c r="H92" s="34"/>
       <c r="I92" s="34"/>
-      <c r="L92" s="162"/>
+      <c r="L92" s="165"/>
       <c r="O92" s="34"/>
       <c r="P92" s="97"/>
       <c r="Q92" s="34"/>
@@ -9332,7 +9335,7 @@
       <c r="T92" s="34"/>
       <c r="U92" s="34"/>
       <c r="V92" s="97"/>
-      <c r="Z92" s="169"/>
+      <c r="Z92" s="172"/>
       <c r="AA92" s="106"/>
       <c r="AB92" s="106"/>
       <c r="AC92" s="106"/>
@@ -9353,86 +9356,86 @@
       <c r="AR92" s="97"/>
       <c r="AU92" s="29"/>
       <c r="AV92" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AW92" s="16"/>
       <c r="AX92" s="16"/>
       <c r="AY92" s="16"/>
-      <c r="AZ92" s="215" t="s">
-        <v>127</v>
-      </c>
-      <c r="BA92" s="215"/>
-      <c r="BB92" s="215"/>
-      <c r="BC92" s="216"/>
-      <c r="BD92" s="215">
+      <c r="AZ92" s="221" t="s">
+        <v>126</v>
+      </c>
+      <c r="BA92" s="221"/>
+      <c r="BB92" s="221"/>
+      <c r="BC92" s="222"/>
+      <c r="BD92" s="221">
         <v>18000</v>
       </c>
-      <c r="BE92" s="215"/>
-      <c r="BF92" s="215"/>
-      <c r="BG92" s="215">
+      <c r="BE92" s="221"/>
+      <c r="BF92" s="221"/>
+      <c r="BG92" s="221">
         <v>2000</v>
       </c>
-      <c r="BH92" s="215"/>
-      <c r="BI92" s="215"/>
-      <c r="BJ92" s="217"/>
-      <c r="BK92" s="219"/>
+      <c r="BH92" s="221"/>
+      <c r="BI92" s="221"/>
+      <c r="BJ92" s="223"/>
+      <c r="BK92" s="225"/>
       <c r="BL92" s="97"/>
       <c r="BO92" s="29"/>
-      <c r="BP92" s="222"/>
-      <c r="BQ92" s="224"/>
-      <c r="BR92" s="224"/>
-      <c r="BS92" s="224"/>
-      <c r="BT92" s="224"/>
-      <c r="BU92" s="224"/>
-      <c r="BV92" s="224"/>
-      <c r="BW92" s="224"/>
-      <c r="BX92" s="224"/>
-      <c r="BY92" s="224"/>
-      <c r="BZ92" s="224"/>
-      <c r="CA92" s="224"/>
-      <c r="CB92" s="224"/>
-      <c r="CC92" s="224"/>
-      <c r="CD92" s="224"/>
-      <c r="CE92" s="227"/>
+      <c r="BP92" s="228"/>
+      <c r="BQ92" s="230"/>
+      <c r="BR92" s="230"/>
+      <c r="BS92" s="230"/>
+      <c r="BT92" s="230"/>
+      <c r="BU92" s="230"/>
+      <c r="BV92" s="230"/>
+      <c r="BW92" s="230"/>
+      <c r="BX92" s="230"/>
+      <c r="BY92" s="230"/>
+      <c r="BZ92" s="230"/>
+      <c r="CA92" s="230"/>
+      <c r="CB92" s="230"/>
+      <c r="CC92" s="230"/>
+      <c r="CD92" s="230"/>
+      <c r="CE92" s="233"/>
       <c r="CF92" s="97"/>
     </row>
     <row r="93" ht="17.6" spans="1:85">
-      <c r="A93" s="171"/>
-      <c r="B93" s="171"/>
-      <c r="D93" s="172" t="s">
-        <v>128</v>
+      <c r="A93" s="174"/>
+      <c r="B93" s="174"/>
+      <c r="D93" s="175" t="s">
+        <v>127</v>
       </c>
       <c r="E93" s="27"/>
       <c r="F93" s="27"/>
       <c r="G93" s="148"/>
       <c r="H93" s="66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="I93" s="27"/>
       <c r="J93" s="27"/>
       <c r="K93" s="27"/>
       <c r="L93" s="148"/>
       <c r="M93" s="66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N93" s="27"/>
       <c r="O93" s="27"/>
-      <c r="P93" s="185"/>
+      <c r="P93" s="188"/>
       <c r="Q93" s="66" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="R93" s="66"/>
       <c r="S93" s="66"/>
       <c r="T93" s="66"/>
       <c r="U93" s="66"/>
       <c r="V93" s="97"/>
-      <c r="Z93" s="169"/>
-      <c r="AA93" s="176" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB93" s="177"/>
-      <c r="AC93" s="177"/>
-      <c r="AD93" s="177"/>
+      <c r="Z93" s="172"/>
+      <c r="AA93" s="179" t="s">
+        <v>128</v>
+      </c>
+      <c r="AB93" s="180"/>
+      <c r="AC93" s="180"/>
+      <c r="AD93" s="180"/>
       <c r="AE93" s="106"/>
       <c r="AF93" s="106"/>
       <c r="AG93" s="106"/>
@@ -9452,57 +9455,57 @@
       <c r="AW93" s="16"/>
       <c r="AX93" s="16"/>
       <c r="AY93" s="16"/>
-      <c r="AZ93" s="215" t="s">
-        <v>130</v>
-      </c>
-      <c r="BA93" s="215"/>
-      <c r="BB93" s="215"/>
-      <c r="BC93" s="216"/>
-      <c r="BD93" s="215">
+      <c r="AZ93" s="221" t="s">
+        <v>129</v>
+      </c>
+      <c r="BA93" s="221"/>
+      <c r="BB93" s="221"/>
+      <c r="BC93" s="222"/>
+      <c r="BD93" s="221">
         <v>30000</v>
       </c>
-      <c r="BE93" s="215"/>
-      <c r="BF93" s="215"/>
-      <c r="BG93" s="215">
+      <c r="BE93" s="221"/>
+      <c r="BF93" s="221"/>
+      <c r="BG93" s="221">
         <v>3000</v>
       </c>
-      <c r="BH93" s="215"/>
-      <c r="BI93" s="215"/>
-      <c r="BJ93" s="217"/>
-      <c r="BK93" s="216"/>
+      <c r="BH93" s="221"/>
+      <c r="BI93" s="221"/>
+      <c r="BJ93" s="223"/>
+      <c r="BK93" s="222"/>
       <c r="BL93" s="97"/>
       <c r="BM93" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BO93" s="29"/>
-      <c r="BP93" s="222"/>
-      <c r="BQ93" s="222"/>
-      <c r="BR93" s="222"/>
-      <c r="BS93" s="222"/>
-      <c r="BT93" s="225"/>
-      <c r="BU93" s="225"/>
-      <c r="BV93" s="225"/>
+      <c r="BP93" s="228"/>
+      <c r="BQ93" s="228"/>
+      <c r="BR93" s="228"/>
+      <c r="BS93" s="228"/>
+      <c r="BT93" s="231"/>
+      <c r="BU93" s="231"/>
+      <c r="BV93" s="231"/>
       <c r="BW93" s="87"/>
-      <c r="BX93" s="225"/>
-      <c r="BY93" s="225"/>
-      <c r="BZ93" s="225"/>
-      <c r="CA93" s="225"/>
-      <c r="CB93" s="225"/>
-      <c r="CC93" s="225"/>
-      <c r="CD93" s="228"/>
+      <c r="BX93" s="231"/>
+      <c r="BY93" s="231"/>
+      <c r="BZ93" s="231"/>
+      <c r="CA93" s="231"/>
+      <c r="CB93" s="231"/>
+      <c r="CC93" s="231"/>
+      <c r="CD93" s="234"/>
       <c r="CE93" s="87"/>
       <c r="CF93" s="97"/>
       <c r="CG93" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="94" ht="17.6" spans="1:84">
-      <c r="A94" s="171"/>
-      <c r="B94" s="171"/>
+      <c r="A94" s="174"/>
+      <c r="B94" s="174"/>
       <c r="D94" s="29">
         <v>130</v>
       </c>
-      <c r="G94" s="162"/>
+      <c r="G94" s="165"/>
       <c r="H94" s="27">
         <v>60</v>
       </c>
@@ -9515,7 +9518,7 @@
       </c>
       <c r="N94" s="27"/>
       <c r="O94" s="27"/>
-      <c r="P94" s="185"/>
+      <c r="P94" s="188"/>
       <c r="Q94" s="66"/>
       <c r="R94" s="66">
         <v>50</v>
@@ -9524,7 +9527,7 @@
       <c r="T94" s="66"/>
       <c r="U94" s="66"/>
       <c r="V94" s="97"/>
-      <c r="Z94" s="169"/>
+      <c r="Z94" s="172"/>
       <c r="AA94" s="106"/>
       <c r="AB94" s="106"/>
       <c r="AC94" s="106"/>
@@ -9548,52 +9551,52 @@
       <c r="AW94" s="16"/>
       <c r="AX94" s="16"/>
       <c r="AY94" s="16"/>
-      <c r="AZ94" s="215" t="s">
-        <v>132</v>
-      </c>
-      <c r="BA94" s="215"/>
-      <c r="BB94" s="215"/>
-      <c r="BC94" s="216"/>
-      <c r="BD94" s="215">
+      <c r="AZ94" s="221" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA94" s="221"/>
+      <c r="BB94" s="221"/>
+      <c r="BC94" s="222"/>
+      <c r="BD94" s="221">
         <v>25000</v>
       </c>
-      <c r="BE94" s="215"/>
-      <c r="BF94" s="215"/>
-      <c r="BG94" s="215">
+      <c r="BE94" s="221"/>
+      <c r="BF94" s="221"/>
+      <c r="BG94" s="221">
         <v>5000</v>
       </c>
-      <c r="BH94" s="215"/>
-      <c r="BI94" s="215"/>
-      <c r="BJ94" s="217"/>
-      <c r="BK94" s="219" t="s">
-        <v>40</v>
+      <c r="BH94" s="221"/>
+      <c r="BI94" s="221"/>
+      <c r="BJ94" s="223"/>
+      <c r="BK94" s="225" t="s">
+        <v>36</v>
       </c>
       <c r="BL94" s="97"/>
       <c r="BO94" s="29"/>
-      <c r="BP94" s="222"/>
-      <c r="BQ94" s="222"/>
-      <c r="BR94" s="222"/>
-      <c r="BS94" s="222"/>
-      <c r="BT94" s="225"/>
-      <c r="BU94" s="225"/>
-      <c r="BV94" s="225"/>
+      <c r="BP94" s="228"/>
+      <c r="BQ94" s="228"/>
+      <c r="BR94" s="228"/>
+      <c r="BS94" s="228"/>
+      <c r="BT94" s="231"/>
+      <c r="BU94" s="231"/>
+      <c r="BV94" s="231"/>
       <c r="BW94" s="87"/>
-      <c r="BX94" s="225"/>
-      <c r="BY94" s="225"/>
-      <c r="BZ94" s="225"/>
-      <c r="CA94" s="225"/>
-      <c r="CB94" s="225"/>
-      <c r="CC94" s="225"/>
-      <c r="CD94" s="228"/>
-      <c r="CE94" s="227"/>
+      <c r="BX94" s="231"/>
+      <c r="BY94" s="231"/>
+      <c r="BZ94" s="231"/>
+      <c r="CA94" s="231"/>
+      <c r="CB94" s="231"/>
+      <c r="CC94" s="231"/>
+      <c r="CD94" s="234"/>
+      <c r="CE94" s="233"/>
       <c r="CF94" s="97"/>
     </row>
     <row r="95" ht="20.4" spans="1:84">
-      <c r="A95" s="171"/>
-      <c r="B95" s="171"/>
+      <c r="A95" s="174"/>
+      <c r="B95" s="174"/>
       <c r="D95" s="29"/>
-      <c r="G95" s="162"/>
-      <c r="L95" s="162"/>
+      <c r="G95" s="165"/>
+      <c r="L95" s="165"/>
       <c r="P95" s="97"/>
       <c r="Q95" s="34"/>
       <c r="R95" s="34"/>
@@ -9601,101 +9604,101 @@
       <c r="T95" s="34"/>
       <c r="U95" s="34"/>
       <c r="V95" s="97"/>
-      <c r="Z95" s="169"/>
-      <c r="AA95" s="200" t="s">
-        <v>133</v>
-      </c>
-      <c r="AB95" s="201"/>
-      <c r="AC95" s="201"/>
-      <c r="AD95" s="201"/>
-      <c r="AE95" s="201"/>
-      <c r="AF95" s="201"/>
-      <c r="AG95" s="201"/>
-      <c r="AH95" s="201"/>
-      <c r="AI95" s="201"/>
-      <c r="AJ95" s="201"/>
-      <c r="AK95" s="201"/>
-      <c r="AL95" s="201"/>
-      <c r="AM95" s="201"/>
-      <c r="AN95" s="201"/>
-      <c r="AO95" s="201"/>
-      <c r="AP95" s="201"/>
-      <c r="AQ95" s="211"/>
+      <c r="Z95" s="172"/>
+      <c r="AA95" s="203" t="s">
+        <v>132</v>
+      </c>
+      <c r="AB95" s="204"/>
+      <c r="AC95" s="204"/>
+      <c r="AD95" s="204"/>
+      <c r="AE95" s="204"/>
+      <c r="AF95" s="204"/>
+      <c r="AG95" s="204"/>
+      <c r="AH95" s="204"/>
+      <c r="AI95" s="204"/>
+      <c r="AJ95" s="204"/>
+      <c r="AK95" s="204"/>
+      <c r="AL95" s="204"/>
+      <c r="AM95" s="204"/>
+      <c r="AN95" s="204"/>
+      <c r="AO95" s="204"/>
+      <c r="AP95" s="204"/>
+      <c r="AQ95" s="217"/>
       <c r="AR95" s="97"/>
       <c r="AU95" s="29"/>
       <c r="AV95" s="16"/>
       <c r="AW95" s="16"/>
       <c r="AX95" s="16"/>
       <c r="AY95" s="16"/>
-      <c r="AZ95" s="215" t="s">
-        <v>134</v>
-      </c>
-      <c r="BA95" s="215"/>
-      <c r="BB95" s="215"/>
-      <c r="BC95" s="216"/>
-      <c r="BD95" s="215">
+      <c r="AZ95" s="221" t="s">
+        <v>133</v>
+      </c>
+      <c r="BA95" s="221"/>
+      <c r="BB95" s="221"/>
+      <c r="BC95" s="222"/>
+      <c r="BD95" s="221">
         <v>3000</v>
       </c>
-      <c r="BE95" s="215"/>
-      <c r="BF95" s="215"/>
-      <c r="BG95" s="215">
+      <c r="BE95" s="221"/>
+      <c r="BF95" s="221"/>
+      <c r="BG95" s="221">
         <v>1000</v>
       </c>
-      <c r="BH95" s="215"/>
-      <c r="BI95" s="215"/>
-      <c r="BJ95" s="217"/>
-      <c r="BK95" s="218"/>
+      <c r="BH95" s="221"/>
+      <c r="BI95" s="221"/>
+      <c r="BJ95" s="223"/>
+      <c r="BK95" s="224"/>
       <c r="BL95" s="97"/>
       <c r="BO95" s="29"/>
-      <c r="BP95" s="222"/>
-      <c r="BQ95" s="222"/>
-      <c r="BR95" s="222"/>
-      <c r="BS95" s="222"/>
-      <c r="BT95" s="225"/>
-      <c r="BU95" s="225"/>
-      <c r="BV95" s="225"/>
+      <c r="BP95" s="228"/>
+      <c r="BQ95" s="228"/>
+      <c r="BR95" s="228"/>
+      <c r="BS95" s="228"/>
+      <c r="BT95" s="231"/>
+      <c r="BU95" s="231"/>
+      <c r="BV95" s="231"/>
       <c r="BW95" s="87"/>
-      <c r="BX95" s="225"/>
-      <c r="BY95" s="225"/>
-      <c r="BZ95" s="225"/>
-      <c r="CA95" s="225"/>
-      <c r="CB95" s="225"/>
-      <c r="CC95" s="225"/>
-      <c r="CD95" s="228"/>
-      <c r="CE95" s="226"/>
+      <c r="BX95" s="231"/>
+      <c r="BY95" s="231"/>
+      <c r="BZ95" s="231"/>
+      <c r="CA95" s="231"/>
+      <c r="CB95" s="231"/>
+      <c r="CC95" s="231"/>
+      <c r="CD95" s="234"/>
+      <c r="CE95" s="232"/>
       <c r="CF95" s="97"/>
     </row>
     <row r="96" ht="17.6" spans="1:84">
-      <c r="A96" s="171"/>
-      <c r="B96" s="171"/>
-      <c r="D96" s="172" t="s">
-        <v>135</v>
+      <c r="A96" s="174"/>
+      <c r="B96" s="174"/>
+      <c r="D96" s="175" t="s">
+        <v>134</v>
       </c>
       <c r="E96" s="27"/>
       <c r="F96" s="27"/>
       <c r="G96" s="148"/>
       <c r="H96" s="66" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I96" s="27"/>
       <c r="J96" s="27"/>
       <c r="K96" s="27"/>
       <c r="L96" s="148"/>
       <c r="M96" s="66" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N96" s="27"/>
       <c r="O96" s="27"/>
-      <c r="P96" s="185"/>
+      <c r="P96" s="188"/>
       <c r="Q96" s="66" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R96" s="66"/>
       <c r="S96" s="66"/>
       <c r="T96" s="66"/>
       <c r="U96" s="66"/>
       <c r="V96" s="97"/>
-      <c r="Z96" s="169"/>
+      <c r="Z96" s="172"/>
       <c r="AA96" s="106"/>
       <c r="AB96" s="106"/>
       <c r="AC96" s="106"/>
@@ -9719,51 +9722,51 @@
       <c r="AW96" s="16"/>
       <c r="AX96" s="16"/>
       <c r="AY96" s="16"/>
-      <c r="AZ96" s="215" t="s">
-        <v>136</v>
-      </c>
-      <c r="BA96" s="215"/>
-      <c r="BB96" s="215"/>
-      <c r="BC96" s="216"/>
-      <c r="BD96" s="215">
+      <c r="AZ96" s="221" t="s">
+        <v>135</v>
+      </c>
+      <c r="BA96" s="221"/>
+      <c r="BB96" s="221"/>
+      <c r="BC96" s="222"/>
+      <c r="BD96" s="221">
         <v>6000</v>
       </c>
-      <c r="BE96" s="215"/>
-      <c r="BF96" s="215"/>
-      <c r="BG96" s="215">
+      <c r="BE96" s="221"/>
+      <c r="BF96" s="221"/>
+      <c r="BG96" s="221">
         <v>1000</v>
       </c>
-      <c r="BH96" s="215"/>
-      <c r="BI96" s="215"/>
-      <c r="BJ96" s="217"/>
-      <c r="BK96" s="216"/>
+      <c r="BH96" s="221"/>
+      <c r="BI96" s="221"/>
+      <c r="BJ96" s="223"/>
+      <c r="BK96" s="222"/>
       <c r="BL96" s="97"/>
       <c r="BO96" s="29"/>
-      <c r="BP96" s="222"/>
-      <c r="BQ96" s="222"/>
-      <c r="BR96" s="222"/>
-      <c r="BS96" s="222"/>
-      <c r="BT96" s="225"/>
-      <c r="BU96" s="225"/>
-      <c r="BV96" s="225"/>
+      <c r="BP96" s="228"/>
+      <c r="BQ96" s="228"/>
+      <c r="BR96" s="228"/>
+      <c r="BS96" s="228"/>
+      <c r="BT96" s="231"/>
+      <c r="BU96" s="231"/>
+      <c r="BV96" s="231"/>
       <c r="BW96" s="87"/>
-      <c r="BX96" s="225"/>
-      <c r="BY96" s="225"/>
-      <c r="BZ96" s="225"/>
-      <c r="CA96" s="225"/>
-      <c r="CB96" s="225"/>
-      <c r="CC96" s="225"/>
-      <c r="CD96" s="228"/>
+      <c r="BX96" s="231"/>
+      <c r="BY96" s="231"/>
+      <c r="BZ96" s="231"/>
+      <c r="CA96" s="231"/>
+      <c r="CB96" s="231"/>
+      <c r="CC96" s="231"/>
+      <c r="CD96" s="234"/>
       <c r="CE96" s="87"/>
       <c r="CF96" s="97"/>
     </row>
     <row r="97" spans="1:84">
-      <c r="A97" s="171"/>
-      <c r="B97" s="171"/>
+      <c r="A97" s="174"/>
+      <c r="B97" s="174"/>
       <c r="D97" s="29">
         <v>260</v>
       </c>
-      <c r="G97" s="162"/>
+      <c r="G97" s="165"/>
       <c r="H97" s="27">
         <v>120</v>
       </c>
@@ -9776,7 +9779,7 @@
       </c>
       <c r="N97" s="27"/>
       <c r="O97" s="27"/>
-      <c r="P97" s="185"/>
+      <c r="P97" s="188"/>
       <c r="Q97" s="66"/>
       <c r="R97" s="66">
         <v>100</v>
@@ -9785,26 +9788,26 @@
       <c r="T97" s="66"/>
       <c r="U97" s="66"/>
       <c r="V97" s="97"/>
-      <c r="Z97" s="169"/>
-      <c r="AA97" s="200" t="s">
-        <v>137</v>
-      </c>
-      <c r="AB97" s="201"/>
-      <c r="AC97" s="201"/>
-      <c r="AD97" s="201"/>
-      <c r="AE97" s="201"/>
-      <c r="AF97" s="201"/>
-      <c r="AG97" s="201"/>
-      <c r="AH97" s="201"/>
-      <c r="AI97" s="201"/>
-      <c r="AJ97" s="201"/>
-      <c r="AK97" s="201"/>
-      <c r="AL97" s="201"/>
-      <c r="AM97" s="201"/>
-      <c r="AN97" s="201"/>
-      <c r="AO97" s="201"/>
-      <c r="AP97" s="201"/>
-      <c r="AQ97" s="211"/>
+      <c r="Z97" s="172"/>
+      <c r="AA97" s="203" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB97" s="204"/>
+      <c r="AC97" s="204"/>
+      <c r="AD97" s="204"/>
+      <c r="AE97" s="204"/>
+      <c r="AF97" s="204"/>
+      <c r="AG97" s="204"/>
+      <c r="AH97" s="204"/>
+      <c r="AI97" s="204"/>
+      <c r="AJ97" s="204"/>
+      <c r="AK97" s="204"/>
+      <c r="AL97" s="204"/>
+      <c r="AM97" s="204"/>
+      <c r="AN97" s="204"/>
+      <c r="AO97" s="204"/>
+      <c r="AP97" s="204"/>
+      <c r="AQ97" s="217"/>
       <c r="AR97" s="97"/>
       <c r="AU97" s="29"/>
       <c r="BL97" s="97"/>
@@ -9829,8 +9832,8 @@
     </row>
     <row r="98" ht="20.4" spans="4:84">
       <c r="D98" s="29"/>
-      <c r="G98" s="162"/>
-      <c r="L98" s="162"/>
+      <c r="G98" s="165"/>
+      <c r="L98" s="165"/>
       <c r="P98" s="97"/>
       <c r="Q98" s="34"/>
       <c r="R98" s="34"/>
@@ -9838,7 +9841,7 @@
       <c r="T98" s="34"/>
       <c r="U98" s="34"/>
       <c r="V98" s="97"/>
-      <c r="Z98" s="169"/>
+      <c r="Z98" s="172"/>
       <c r="AA98" s="106"/>
       <c r="AB98" s="106"/>
       <c r="AC98" s="106"/>
@@ -9858,128 +9861,128 @@
       <c r="AQ98" s="106"/>
       <c r="AR98" s="97"/>
       <c r="AU98" s="29"/>
-      <c r="AV98" s="213" t="s">
-        <v>138</v>
-      </c>
-      <c r="AW98" s="213"/>
-      <c r="AX98" s="213"/>
-      <c r="AY98" s="213"/>
-      <c r="AZ98" s="213"/>
-      <c r="BA98" s="213"/>
-      <c r="BB98" s="213"/>
-      <c r="BC98" s="213"/>
-      <c r="BD98" s="213"/>
+      <c r="AV98" s="219" t="s">
+        <v>137</v>
+      </c>
+      <c r="AW98" s="219"/>
+      <c r="AX98" s="219"/>
+      <c r="AY98" s="219"/>
+      <c r="AZ98" s="219"/>
+      <c r="BA98" s="219"/>
+      <c r="BB98" s="219"/>
+      <c r="BC98" s="219"/>
+      <c r="BD98" s="219"/>
       <c r="BE98" s="93"/>
       <c r="BF98" s="93"/>
       <c r="BG98" s="93"/>
       <c r="BH98" s="93"/>
       <c r="BI98" s="93"/>
       <c r="BJ98" s="93"/>
-      <c r="BK98" s="218"/>
+      <c r="BK98" s="224"/>
       <c r="BL98" s="97"/>
       <c r="BO98" s="29"/>
-      <c r="BP98" s="223"/>
-      <c r="BQ98" s="223"/>
-      <c r="BR98" s="223"/>
-      <c r="BS98" s="223"/>
-      <c r="BT98" s="223"/>
-      <c r="BU98" s="223"/>
-      <c r="BV98" s="223"/>
-      <c r="BW98" s="223"/>
-      <c r="BX98" s="223"/>
-      <c r="BY98" s="223"/>
-      <c r="BZ98" s="223"/>
-      <c r="CA98" s="223"/>
-      <c r="CB98" s="223"/>
-      <c r="CC98" s="223"/>
-      <c r="CD98" s="223"/>
-      <c r="CE98" s="226"/>
+      <c r="BP98" s="229"/>
+      <c r="BQ98" s="229"/>
+      <c r="BR98" s="229"/>
+      <c r="BS98" s="229"/>
+      <c r="BT98" s="229"/>
+      <c r="BU98" s="229"/>
+      <c r="BV98" s="229"/>
+      <c r="BW98" s="229"/>
+      <c r="BX98" s="229"/>
+      <c r="BY98" s="229"/>
+      <c r="BZ98" s="229"/>
+      <c r="CA98" s="229"/>
+      <c r="CB98" s="229"/>
+      <c r="CC98" s="229"/>
+      <c r="CD98" s="229"/>
+      <c r="CE98" s="232"/>
       <c r="CF98" s="97"/>
     </row>
     <row r="99" ht="18.35" spans="4:84">
       <c r="D99" s="29"/>
-      <c r="E99" s="179"/>
-      <c r="F99" s="179"/>
-      <c r="G99" s="179"/>
-      <c r="H99" s="179"/>
-      <c r="I99" s="179"/>
-      <c r="J99" s="179"/>
-      <c r="K99" s="181"/>
-      <c r="L99" s="182"/>
-      <c r="M99" s="182"/>
-      <c r="N99" s="182"/>
-      <c r="O99" s="182"/>
-      <c r="P99" s="182"/>
-      <c r="Q99" s="182"/>
-      <c r="R99" s="182"/>
-      <c r="S99" s="182"/>
-      <c r="T99" s="182"/>
-      <c r="U99" s="182"/>
+      <c r="E99" s="182"/>
+      <c r="F99" s="182"/>
+      <c r="G99" s="182"/>
+      <c r="H99" s="182"/>
+      <c r="I99" s="182"/>
+      <c r="J99" s="182"/>
+      <c r="K99" s="184"/>
+      <c r="L99" s="185"/>
+      <c r="M99" s="185"/>
+      <c r="N99" s="185"/>
+      <c r="O99" s="185"/>
+      <c r="P99" s="185"/>
+      <c r="Q99" s="185"/>
+      <c r="R99" s="185"/>
+      <c r="S99" s="185"/>
+      <c r="T99" s="185"/>
+      <c r="U99" s="185"/>
       <c r="V99" s="97"/>
-      <c r="Z99" s="169"/>
-      <c r="AA99" s="200" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB99" s="201"/>
-      <c r="AC99" s="201"/>
-      <c r="AD99" s="201"/>
-      <c r="AE99" s="201"/>
-      <c r="AF99" s="201"/>
-      <c r="AG99" s="201"/>
-      <c r="AH99" s="201"/>
-      <c r="AI99" s="201"/>
-      <c r="AJ99" s="201"/>
-      <c r="AK99" s="201"/>
-      <c r="AL99" s="201"/>
-      <c r="AM99" s="201"/>
-      <c r="AN99" s="201"/>
-      <c r="AO99" s="201"/>
-      <c r="AP99" s="201"/>
-      <c r="AQ99" s="211"/>
+      <c r="Z99" s="172"/>
+      <c r="AA99" s="203" t="s">
+        <v>138</v>
+      </c>
+      <c r="AB99" s="204"/>
+      <c r="AC99" s="204"/>
+      <c r="AD99" s="204"/>
+      <c r="AE99" s="204"/>
+      <c r="AF99" s="204"/>
+      <c r="AG99" s="204"/>
+      <c r="AH99" s="204"/>
+      <c r="AI99" s="204"/>
+      <c r="AJ99" s="204"/>
+      <c r="AK99" s="204"/>
+      <c r="AL99" s="204"/>
+      <c r="AM99" s="204"/>
+      <c r="AN99" s="204"/>
+      <c r="AO99" s="204"/>
+      <c r="AP99" s="204"/>
+      <c r="AQ99" s="217"/>
       <c r="AR99" s="97"/>
       <c r="AU99" s="29"/>
       <c r="AV99" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AW99" s="16"/>
       <c r="AX99" s="16"/>
       <c r="AY99" s="16"/>
-      <c r="AZ99" s="215" t="s">
-        <v>140</v>
-      </c>
-      <c r="BA99" s="215"/>
-      <c r="BB99" s="215"/>
-      <c r="BC99" s="216"/>
-      <c r="BD99" s="215">
+      <c r="AZ99" s="221" t="s">
+        <v>139</v>
+      </c>
+      <c r="BA99" s="221"/>
+      <c r="BB99" s="221"/>
+      <c r="BC99" s="222"/>
+      <c r="BD99" s="221">
         <v>18000</v>
       </c>
-      <c r="BE99" s="215"/>
-      <c r="BF99" s="215"/>
-      <c r="BG99" s="215">
+      <c r="BE99" s="221"/>
+      <c r="BF99" s="221"/>
+      <c r="BG99" s="221">
         <v>2000</v>
       </c>
-      <c r="BH99" s="215"/>
-      <c r="BI99" s="215"/>
-      <c r="BJ99" s="217"/>
-      <c r="BK99" s="219"/>
+      <c r="BH99" s="221"/>
+      <c r="BI99" s="221"/>
+      <c r="BJ99" s="223"/>
+      <c r="BK99" s="225"/>
       <c r="BL99" s="97"/>
       <c r="BO99" s="29"/>
-      <c r="BP99" s="222"/>
-      <c r="BQ99" s="222"/>
-      <c r="BR99" s="222"/>
-      <c r="BS99" s="222"/>
-      <c r="BT99" s="225"/>
-      <c r="BU99" s="225"/>
-      <c r="BV99" s="225"/>
+      <c r="BP99" s="228"/>
+      <c r="BQ99" s="228"/>
+      <c r="BR99" s="228"/>
+      <c r="BS99" s="228"/>
+      <c r="BT99" s="231"/>
+      <c r="BU99" s="231"/>
+      <c r="BV99" s="231"/>
       <c r="BW99" s="87"/>
-      <c r="BX99" s="225"/>
-      <c r="BY99" s="225"/>
-      <c r="BZ99" s="225"/>
-      <c r="CA99" s="225"/>
-      <c r="CB99" s="225"/>
-      <c r="CC99" s="225"/>
-      <c r="CD99" s="228"/>
-      <c r="CE99" s="227"/>
+      <c r="BX99" s="231"/>
+      <c r="BY99" s="231"/>
+      <c r="BZ99" s="231"/>
+      <c r="CA99" s="231"/>
+      <c r="CB99" s="231"/>
+      <c r="CC99" s="231"/>
+      <c r="CD99" s="234"/>
+      <c r="CE99" s="233"/>
       <c r="CF99" s="97"/>
     </row>
     <row r="100" ht="17.6" spans="4:85">
@@ -10002,7 +10005,7 @@
       <c r="T100" s="34"/>
       <c r="U100" s="34"/>
       <c r="V100" s="97"/>
-      <c r="Z100" s="169"/>
+      <c r="Z100" s="172"/>
       <c r="AA100" s="106"/>
       <c r="AB100" s="106"/>
       <c r="AC100" s="106"/>
@@ -10026,61 +10029,61 @@
       <c r="AW100" s="16"/>
       <c r="AX100" s="16"/>
       <c r="AY100" s="16"/>
-      <c r="AZ100" s="215" t="s">
-        <v>141</v>
-      </c>
-      <c r="BA100" s="215"/>
-      <c r="BB100" s="215"/>
-      <c r="BC100" s="216"/>
-      <c r="BD100" s="215">
+      <c r="AZ100" s="221" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA100" s="221"/>
+      <c r="BB100" s="221"/>
+      <c r="BC100" s="222"/>
+      <c r="BD100" s="221">
         <v>30000</v>
       </c>
-      <c r="BE100" s="215"/>
-      <c r="BF100" s="215"/>
-      <c r="BG100" s="215">
+      <c r="BE100" s="221"/>
+      <c r="BF100" s="221"/>
+      <c r="BG100" s="221">
         <v>3000</v>
       </c>
-      <c r="BH100" s="215"/>
-      <c r="BI100" s="215"/>
-      <c r="BJ100" s="217"/>
-      <c r="BK100" s="216"/>
+      <c r="BH100" s="221"/>
+      <c r="BI100" s="221"/>
+      <c r="BJ100" s="223"/>
+      <c r="BK100" s="222"/>
       <c r="BL100" s="97"/>
       <c r="BM100" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BO100" s="29"/>
-      <c r="BP100" s="222"/>
-      <c r="BQ100" s="222"/>
-      <c r="BR100" s="222"/>
-      <c r="BS100" s="222"/>
-      <c r="BT100" s="225"/>
-      <c r="BU100" s="225"/>
-      <c r="BV100" s="225"/>
+      <c r="BP100" s="228"/>
+      <c r="BQ100" s="228"/>
+      <c r="BR100" s="228"/>
+      <c r="BS100" s="228"/>
+      <c r="BT100" s="231"/>
+      <c r="BU100" s="231"/>
+      <c r="BV100" s="231"/>
       <c r="BW100" s="87"/>
-      <c r="BX100" s="225"/>
-      <c r="BY100" s="225"/>
-      <c r="BZ100" s="225"/>
-      <c r="CA100" s="225"/>
-      <c r="CB100" s="225"/>
-      <c r="CC100" s="225"/>
-      <c r="CD100" s="228"/>
+      <c r="BX100" s="231"/>
+      <c r="BY100" s="231"/>
+      <c r="BZ100" s="231"/>
+      <c r="CA100" s="231"/>
+      <c r="CB100" s="231"/>
+      <c r="CC100" s="231"/>
+      <c r="CD100" s="234"/>
       <c r="CE100" s="87"/>
       <c r="CF100" s="97"/>
       <c r="CG100" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="101" ht="17.6" spans="4:84">
       <c r="D101" s="29"/>
-      <c r="E101" s="178" t="s">
-        <v>142</v>
-      </c>
-      <c r="F101" s="178"/>
-      <c r="G101" s="178"/>
-      <c r="H101" s="178"/>
-      <c r="I101" s="178"/>
-      <c r="J101" s="178"/>
-      <c r="K101" s="178"/>
+      <c r="E101" s="181" t="s">
+        <v>141</v>
+      </c>
+      <c r="F101" s="181"/>
+      <c r="G101" s="181"/>
+      <c r="H101" s="181"/>
+      <c r="I101" s="181"/>
+      <c r="J101" s="181"/>
+      <c r="K101" s="181"/>
       <c r="L101" s="34"/>
       <c r="M101" s="34"/>
       <c r="N101" s="34"/>
@@ -10116,44 +10119,44 @@
       <c r="AW101" s="16"/>
       <c r="AX101" s="16"/>
       <c r="AY101" s="16"/>
-      <c r="AZ101" s="215" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA101" s="215"/>
-      <c r="BB101" s="215"/>
-      <c r="BC101" s="216"/>
-      <c r="BD101" s="215">
+      <c r="AZ101" s="221" t="s">
+        <v>142</v>
+      </c>
+      <c r="BA101" s="221"/>
+      <c r="BB101" s="221"/>
+      <c r="BC101" s="222"/>
+      <c r="BD101" s="221">
         <v>25000</v>
       </c>
-      <c r="BE101" s="215"/>
-      <c r="BF101" s="215"/>
-      <c r="BG101" s="215">
+      <c r="BE101" s="221"/>
+      <c r="BF101" s="221"/>
+      <c r="BG101" s="221">
         <v>5000</v>
       </c>
-      <c r="BH101" s="215"/>
-      <c r="BI101" s="215"/>
-      <c r="BJ101" s="217"/>
-      <c r="BK101" s="219" t="s">
-        <v>40</v>
+      <c r="BH101" s="221"/>
+      <c r="BI101" s="221"/>
+      <c r="BJ101" s="223"/>
+      <c r="BK101" s="225" t="s">
+        <v>36</v>
       </c>
       <c r="BL101" s="97"/>
       <c r="BO101" s="29"/>
-      <c r="BP101" s="222"/>
-      <c r="BQ101" s="222"/>
-      <c r="BR101" s="222"/>
-      <c r="BS101" s="222"/>
-      <c r="BT101" s="225"/>
-      <c r="BU101" s="225"/>
-      <c r="BV101" s="225"/>
+      <c r="BP101" s="228"/>
+      <c r="BQ101" s="228"/>
+      <c r="BR101" s="228"/>
+      <c r="BS101" s="228"/>
+      <c r="BT101" s="231"/>
+      <c r="BU101" s="231"/>
+      <c r="BV101" s="231"/>
       <c r="BW101" s="87"/>
-      <c r="BX101" s="225"/>
-      <c r="BY101" s="225"/>
-      <c r="BZ101" s="225"/>
-      <c r="CA101" s="225"/>
-      <c r="CB101" s="225"/>
-      <c r="CC101" s="225"/>
-      <c r="CD101" s="228"/>
-      <c r="CE101" s="227"/>
+      <c r="BX101" s="231"/>
+      <c r="BY101" s="231"/>
+      <c r="BZ101" s="231"/>
+      <c r="CA101" s="231"/>
+      <c r="CB101" s="231"/>
+      <c r="CC101" s="231"/>
+      <c r="CD101" s="234"/>
+      <c r="CE101" s="233"/>
       <c r="CF101" s="97"/>
     </row>
     <row r="102" ht="20.4" spans="4:84">
@@ -10200,65 +10203,65 @@
       <c r="AW102" s="16"/>
       <c r="AX102" s="16"/>
       <c r="AY102" s="16"/>
-      <c r="AZ102" s="215" t="s">
-        <v>144</v>
-      </c>
-      <c r="BA102" s="215"/>
-      <c r="BB102" s="215"/>
-      <c r="BC102" s="216"/>
-      <c r="BD102" s="215">
+      <c r="AZ102" s="221" t="s">
+        <v>143</v>
+      </c>
+      <c r="BA102" s="221"/>
+      <c r="BB102" s="221"/>
+      <c r="BC102" s="222"/>
+      <c r="BD102" s="221">
         <v>3000</v>
       </c>
-      <c r="BE102" s="215"/>
-      <c r="BF102" s="215"/>
-      <c r="BG102" s="215">
+      <c r="BE102" s="221"/>
+      <c r="BF102" s="221"/>
+      <c r="BG102" s="221">
         <v>1000</v>
       </c>
-      <c r="BH102" s="215"/>
-      <c r="BI102" s="215"/>
-      <c r="BJ102" s="217"/>
-      <c r="BK102" s="218"/>
+      <c r="BH102" s="221"/>
+      <c r="BI102" s="221"/>
+      <c r="BJ102" s="223"/>
+      <c r="BK102" s="224"/>
       <c r="BL102" s="97"/>
       <c r="BO102" s="29"/>
-      <c r="BP102" s="222"/>
-      <c r="BQ102" s="222"/>
-      <c r="BR102" s="222"/>
-      <c r="BS102" s="222"/>
-      <c r="BT102" s="225"/>
-      <c r="BU102" s="225"/>
-      <c r="BV102" s="225"/>
+      <c r="BP102" s="228"/>
+      <c r="BQ102" s="228"/>
+      <c r="BR102" s="228"/>
+      <c r="BS102" s="228"/>
+      <c r="BT102" s="231"/>
+      <c r="BU102" s="231"/>
+      <c r="BV102" s="231"/>
       <c r="BW102" s="87"/>
-      <c r="BX102" s="225"/>
-      <c r="BY102" s="225"/>
-      <c r="BZ102" s="225"/>
-      <c r="CA102" s="225"/>
-      <c r="CB102" s="225"/>
-      <c r="CC102" s="225"/>
-      <c r="CD102" s="228"/>
-      <c r="CE102" s="226"/>
+      <c r="BX102" s="231"/>
+      <c r="BY102" s="231"/>
+      <c r="BZ102" s="231"/>
+      <c r="CA102" s="231"/>
+      <c r="CB102" s="231"/>
+      <c r="CC102" s="231"/>
+      <c r="CD102" s="234"/>
+      <c r="CE102" s="232"/>
       <c r="CF102" s="97"/>
     </row>
     <row r="103" ht="17.6" spans="1:84">
-      <c r="A103" s="168" t="s">
+      <c r="A103" s="171" t="s">
+        <v>144</v>
+      </c>
+      <c r="B103" s="171"/>
+      <c r="D103" s="176" t="s">
         <v>145</v>
-      </c>
-      <c r="B103" s="168"/>
-      <c r="D103" s="173" t="s">
-        <v>146</v>
       </c>
       <c r="E103" s="19"/>
       <c r="F103" s="19"/>
       <c r="G103" s="19"/>
       <c r="H103" s="19"/>
       <c r="I103" s="19"/>
-      <c r="J103" s="183"/>
-      <c r="K103" s="184">
+      <c r="J103" s="186"/>
+      <c r="K103" s="187">
         <v>50</v>
       </c>
-      <c r="L103" s="184"/>
+      <c r="L103" s="187"/>
       <c r="M103" s="107"/>
       <c r="N103" s="19" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="O103" s="16"/>
       <c r="P103" s="16"/>
@@ -10269,8 +10272,8 @@
       </c>
       <c r="T103" s="107"/>
       <c r="U103" s="107"/>
-      <c r="V103" s="190"/>
-      <c r="Z103" s="169"/>
+      <c r="V103" s="193"/>
+      <c r="Z103" s="172"/>
       <c r="AA103" s="106"/>
       <c r="AB103" s="106"/>
       <c r="AC103" s="106"/>
@@ -10294,56 +10297,56 @@
       <c r="AW103" s="16"/>
       <c r="AX103" s="16"/>
       <c r="AY103" s="16"/>
-      <c r="AZ103" s="215" t="s">
-        <v>136</v>
-      </c>
-      <c r="BA103" s="215"/>
-      <c r="BB103" s="215"/>
-      <c r="BC103" s="216"/>
-      <c r="BD103" s="215">
+      <c r="AZ103" s="221" t="s">
+        <v>135</v>
+      </c>
+      <c r="BA103" s="221"/>
+      <c r="BB103" s="221"/>
+      <c r="BC103" s="222"/>
+      <c r="BD103" s="221">
         <v>6000</v>
       </c>
-      <c r="BE103" s="215"/>
-      <c r="BF103" s="215"/>
-      <c r="BG103" s="215">
+      <c r="BE103" s="221"/>
+      <c r="BF103" s="221"/>
+      <c r="BG103" s="221">
         <v>1000</v>
       </c>
-      <c r="BH103" s="215"/>
-      <c r="BI103" s="215"/>
-      <c r="BJ103" s="217"/>
-      <c r="BK103" s="216"/>
+      <c r="BH103" s="221"/>
+      <c r="BI103" s="221"/>
+      <c r="BJ103" s="223"/>
+      <c r="BK103" s="222"/>
       <c r="BL103" s="97"/>
       <c r="BO103" s="29"/>
-      <c r="BP103" s="222"/>
-      <c r="BQ103" s="222"/>
-      <c r="BR103" s="222"/>
-      <c r="BS103" s="222"/>
-      <c r="BT103" s="225"/>
-      <c r="BU103" s="225"/>
-      <c r="BV103" s="225"/>
+      <c r="BP103" s="228"/>
+      <c r="BQ103" s="228"/>
+      <c r="BR103" s="228"/>
+      <c r="BS103" s="228"/>
+      <c r="BT103" s="231"/>
+      <c r="BU103" s="231"/>
+      <c r="BV103" s="231"/>
       <c r="BW103" s="87"/>
-      <c r="BX103" s="225"/>
-      <c r="BY103" s="225"/>
-      <c r="BZ103" s="225"/>
-      <c r="CA103" s="225"/>
-      <c r="CB103" s="225"/>
-      <c r="CC103" s="225"/>
-      <c r="CD103" s="228"/>
+      <c r="BX103" s="231"/>
+      <c r="BY103" s="231"/>
+      <c r="BZ103" s="231"/>
+      <c r="CA103" s="231"/>
+      <c r="CB103" s="231"/>
+      <c r="CC103" s="231"/>
+      <c r="CD103" s="234"/>
       <c r="CE103" s="87"/>
       <c r="CF103" s="97"/>
     </row>
     <row r="104" ht="17.55" spans="1:84">
-      <c r="A104" s="168"/>
-      <c r="B104" s="168"/>
-      <c r="D104" s="173"/>
+      <c r="A104" s="171"/>
+      <c r="B104" s="171"/>
+      <c r="D104" s="176"/>
       <c r="E104" s="19"/>
       <c r="F104" s="19"/>
       <c r="G104" s="19"/>
       <c r="H104" s="19"/>
       <c r="I104" s="19"/>
-      <c r="J104" s="183"/>
-      <c r="K104" s="184"/>
-      <c r="L104" s="184"/>
+      <c r="J104" s="186"/>
+      <c r="K104" s="187"/>
+      <c r="L104" s="187"/>
       <c r="M104" s="107"/>
       <c r="N104" s="16"/>
       <c r="O104" s="16"/>
@@ -10353,26 +10356,26 @@
       <c r="S104" s="107"/>
       <c r="T104" s="107"/>
       <c r="U104" s="107"/>
-      <c r="V104" s="190"/>
-      <c r="Z104" s="202"/>
-      <c r="AA104" s="181"/>
-      <c r="AB104" s="181"/>
-      <c r="AC104" s="181"/>
-      <c r="AD104" s="181"/>
-      <c r="AE104" s="181"/>
-      <c r="AF104" s="181"/>
-      <c r="AG104" s="181"/>
-      <c r="AH104" s="181"/>
-      <c r="AI104" s="181"/>
-      <c r="AJ104" s="181"/>
-      <c r="AK104" s="181"/>
-      <c r="AL104" s="181"/>
-      <c r="AM104" s="181"/>
-      <c r="AN104" s="181"/>
-      <c r="AO104" s="181"/>
-      <c r="AP104" s="181"/>
-      <c r="AQ104" s="181"/>
-      <c r="AR104" s="212"/>
+      <c r="V104" s="193"/>
+      <c r="Z104" s="205"/>
+      <c r="AA104" s="184"/>
+      <c r="AB104" s="184"/>
+      <c r="AC104" s="184"/>
+      <c r="AD104" s="184"/>
+      <c r="AE104" s="184"/>
+      <c r="AF104" s="184"/>
+      <c r="AG104" s="184"/>
+      <c r="AH104" s="184"/>
+      <c r="AI104" s="184"/>
+      <c r="AJ104" s="184"/>
+      <c r="AK104" s="184"/>
+      <c r="AL104" s="184"/>
+      <c r="AM104" s="184"/>
+      <c r="AN104" s="184"/>
+      <c r="AO104" s="184"/>
+      <c r="AP104" s="184"/>
+      <c r="AQ104" s="184"/>
+      <c r="AR104" s="218"/>
       <c r="AU104" s="29"/>
       <c r="BL104" s="97"/>
       <c r="BO104" s="29"/>
@@ -10395,8 +10398,8 @@
       <c r="CF104" s="97"/>
     </row>
     <row r="105" ht="20.4" spans="1:84">
-      <c r="A105" s="168"/>
-      <c r="B105" s="168"/>
+      <c r="A105" s="171"/>
+      <c r="B105" s="171"/>
       <c r="D105" s="29"/>
       <c r="H105" s="27"/>
       <c r="I105" s="27"/>
@@ -10414,62 +10417,62 @@
       <c r="U105" s="27"/>
       <c r="V105" s="97"/>
       <c r="AU105" s="29"/>
-      <c r="AV105" s="213" t="s">
-        <v>148</v>
-      </c>
-      <c r="AW105" s="213"/>
-      <c r="AX105" s="213"/>
-      <c r="AY105" s="213"/>
-      <c r="AZ105" s="213"/>
-      <c r="BA105" s="213"/>
-      <c r="BB105" s="213"/>
-      <c r="BC105" s="213"/>
-      <c r="BD105" s="213"/>
+      <c r="AV105" s="219" t="s">
+        <v>147</v>
+      </c>
+      <c r="AW105" s="219"/>
+      <c r="AX105" s="219"/>
+      <c r="AY105" s="219"/>
+      <c r="AZ105" s="219"/>
+      <c r="BA105" s="219"/>
+      <c r="BB105" s="219"/>
+      <c r="BC105" s="219"/>
+      <c r="BD105" s="219"/>
       <c r="BE105" s="93"/>
       <c r="BF105" s="93"/>
       <c r="BG105" s="93"/>
       <c r="BH105" s="93"/>
       <c r="BI105" s="93"/>
       <c r="BJ105" s="93"/>
-      <c r="BK105" s="218"/>
+      <c r="BK105" s="224"/>
       <c r="BL105" s="97"/>
       <c r="BO105" s="29"/>
-      <c r="BP105" s="223"/>
-      <c r="BQ105" s="223"/>
-      <c r="BR105" s="223"/>
-      <c r="BS105" s="223"/>
-      <c r="BT105" s="223"/>
-      <c r="BU105" s="223"/>
-      <c r="BV105" s="223"/>
-      <c r="BW105" s="223"/>
-      <c r="BX105" s="223"/>
-      <c r="BY105" s="223"/>
-      <c r="BZ105" s="223"/>
-      <c r="CA105" s="223"/>
-      <c r="CB105" s="223"/>
-      <c r="CC105" s="223"/>
-      <c r="CD105" s="223"/>
-      <c r="CE105" s="226"/>
+      <c r="BP105" s="229"/>
+      <c r="BQ105" s="229"/>
+      <c r="BR105" s="229"/>
+      <c r="BS105" s="229"/>
+      <c r="BT105" s="229"/>
+      <c r="BU105" s="229"/>
+      <c r="BV105" s="229"/>
+      <c r="BW105" s="229"/>
+      <c r="BX105" s="229"/>
+      <c r="BY105" s="229"/>
+      <c r="BZ105" s="229"/>
+      <c r="CA105" s="229"/>
+      <c r="CB105" s="229"/>
+      <c r="CC105" s="229"/>
+      <c r="CD105" s="229"/>
+      <c r="CE105" s="232"/>
       <c r="CF105" s="97"/>
     </row>
     <row r="106" ht="18" customHeight="1" spans="1:84">
-      <c r="A106" s="168"/>
-      <c r="B106" s="168"/>
-      <c r="D106" s="173" t="s">
-        <v>149</v>
+      <c r="A106" s="171"/>
+      <c r="B106" s="171"/>
+      <c r="D106" s="176" t="s">
+        <v>148</v>
       </c>
       <c r="E106" s="19"/>
       <c r="F106" s="19"/>
       <c r="G106" s="19"/>
       <c r="H106" s="19"/>
       <c r="I106" s="19"/>
-      <c r="J106" s="183"/>
-      <c r="K106" s="184">
+      <c r="J106" s="186"/>
+      <c r="K106" s="187">
         <v>60</v>
       </c>
-      <c r="L106" s="184"/>
+      <c r="L106" s="187"/>
       <c r="N106" s="19" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O106" s="16"/>
       <c r="P106" s="16"/>
@@ -10480,64 +10483,64 @@
       </c>
       <c r="T106" s="107"/>
       <c r="U106" s="107"/>
-      <c r="V106" s="190"/>
+      <c r="V106" s="193"/>
       <c r="AU106" s="29"/>
       <c r="AV106" s="16" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AW106" s="16"/>
       <c r="AX106" s="16"/>
       <c r="AY106" s="16"/>
-      <c r="AZ106" s="215" t="s">
-        <v>140</v>
-      </c>
-      <c r="BA106" s="215"/>
-      <c r="BB106" s="215"/>
-      <c r="BC106" s="216"/>
-      <c r="BD106" s="215">
+      <c r="AZ106" s="221" t="s">
+        <v>139</v>
+      </c>
+      <c r="BA106" s="221"/>
+      <c r="BB106" s="221"/>
+      <c r="BC106" s="222"/>
+      <c r="BD106" s="221">
         <v>18000</v>
       </c>
-      <c r="BE106" s="215"/>
-      <c r="BF106" s="215"/>
-      <c r="BG106" s="215">
+      <c r="BE106" s="221"/>
+      <c r="BF106" s="221"/>
+      <c r="BG106" s="221">
         <v>2000</v>
       </c>
-      <c r="BH106" s="215"/>
-      <c r="BI106" s="215"/>
-      <c r="BJ106" s="217"/>
-      <c r="BK106" s="219"/>
+      <c r="BH106" s="221"/>
+      <c r="BI106" s="221"/>
+      <c r="BJ106" s="223"/>
+      <c r="BK106" s="225"/>
       <c r="BL106" s="97"/>
       <c r="BO106" s="29"/>
-      <c r="BP106" s="222"/>
-      <c r="BQ106" s="222"/>
-      <c r="BR106" s="222"/>
-      <c r="BS106" s="222"/>
-      <c r="BT106" s="225"/>
-      <c r="BU106" s="225"/>
-      <c r="BV106" s="225"/>
+      <c r="BP106" s="228"/>
+      <c r="BQ106" s="228"/>
+      <c r="BR106" s="228"/>
+      <c r="BS106" s="228"/>
+      <c r="BT106" s="231"/>
+      <c r="BU106" s="231"/>
+      <c r="BV106" s="231"/>
       <c r="BW106" s="87"/>
-      <c r="BX106" s="225"/>
-      <c r="BY106" s="225"/>
-      <c r="BZ106" s="225"/>
-      <c r="CA106" s="225"/>
-      <c r="CB106" s="225"/>
-      <c r="CC106" s="225"/>
-      <c r="CD106" s="228"/>
-      <c r="CE106" s="227"/>
+      <c r="BX106" s="231"/>
+      <c r="BY106" s="231"/>
+      <c r="BZ106" s="231"/>
+      <c r="CA106" s="231"/>
+      <c r="CB106" s="231"/>
+      <c r="CC106" s="231"/>
+      <c r="CD106" s="234"/>
+      <c r="CE106" s="233"/>
       <c r="CF106" s="97"/>
     </row>
     <row r="107" ht="17.6" spans="1:85">
-      <c r="A107" s="174"/>
-      <c r="B107" s="174"/>
-      <c r="D107" s="173"/>
+      <c r="A107" s="177"/>
+      <c r="B107" s="177"/>
+      <c r="D107" s="176"/>
       <c r="E107" s="19"/>
       <c r="F107" s="19"/>
       <c r="G107" s="19"/>
       <c r="H107" s="19"/>
       <c r="I107" s="19"/>
-      <c r="J107" s="183"/>
-      <c r="K107" s="184"/>
-      <c r="L107" s="184"/>
+      <c r="J107" s="186"/>
+      <c r="K107" s="187"/>
+      <c r="L107" s="187"/>
       <c r="N107" s="16"/>
       <c r="O107" s="16"/>
       <c r="P107" s="16"/>
@@ -10546,62 +10549,62 @@
       <c r="S107" s="107"/>
       <c r="T107" s="107"/>
       <c r="U107" s="107"/>
-      <c r="V107" s="190"/>
+      <c r="V107" s="193"/>
       <c r="AU107" s="29"/>
       <c r="AV107" s="16"/>
       <c r="AW107" s="16"/>
       <c r="AX107" s="16"/>
       <c r="AY107" s="16"/>
-      <c r="AZ107" s="215" t="s">
-        <v>141</v>
-      </c>
-      <c r="BA107" s="215"/>
-      <c r="BB107" s="215"/>
-      <c r="BC107" s="216"/>
-      <c r="BD107" s="215">
+      <c r="AZ107" s="221" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA107" s="221"/>
+      <c r="BB107" s="221"/>
+      <c r="BC107" s="222"/>
+      <c r="BD107" s="221">
         <v>30000</v>
       </c>
-      <c r="BE107" s="215"/>
-      <c r="BF107" s="215"/>
-      <c r="BG107" s="215">
+      <c r="BE107" s="221"/>
+      <c r="BF107" s="221"/>
+      <c r="BG107" s="221">
         <v>3000</v>
       </c>
-      <c r="BH107" s="215"/>
-      <c r="BI107" s="215"/>
-      <c r="BJ107" s="217"/>
-      <c r="BK107" s="216"/>
+      <c r="BH107" s="221"/>
+      <c r="BI107" s="221"/>
+      <c r="BJ107" s="223"/>
+      <c r="BK107" s="222"/>
       <c r="BL107" s="97"/>
       <c r="BM107" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="BO107" s="29"/>
-      <c r="BP107" s="222"/>
-      <c r="BQ107" s="222"/>
-      <c r="BR107" s="222"/>
-      <c r="BS107" s="222"/>
-      <c r="BT107" s="225"/>
-      <c r="BU107" s="225"/>
-      <c r="BV107" s="225"/>
+      <c r="BP107" s="228"/>
+      <c r="BQ107" s="228"/>
+      <c r="BR107" s="228"/>
+      <c r="BS107" s="228"/>
+      <c r="BT107" s="231"/>
+      <c r="BU107" s="231"/>
+      <c r="BV107" s="231"/>
       <c r="BW107" s="87"/>
-      <c r="BX107" s="225"/>
-      <c r="BY107" s="225"/>
-      <c r="BZ107" s="225"/>
-      <c r="CA107" s="225"/>
-      <c r="CB107" s="225"/>
-      <c r="CC107" s="225"/>
-      <c r="CD107" s="228"/>
+      <c r="BX107" s="231"/>
+      <c r="BY107" s="231"/>
+      <c r="BZ107" s="231"/>
+      <c r="CA107" s="231"/>
+      <c r="CB107" s="231"/>
+      <c r="CC107" s="231"/>
+      <c r="CD107" s="234"/>
       <c r="CE107" s="87"/>
       <c r="CF107" s="97"/>
       <c r="CG107" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="108" ht="17.6" spans="1:84">
-      <c r="A108" s="174" t="s">
+      <c r="A108" s="177" t="s">
+        <v>150</v>
+      </c>
+      <c r="B108" s="177" t="s">
         <v>151</v>
-      </c>
-      <c r="B108" s="174" t="s">
-        <v>152</v>
       </c>
       <c r="D108" s="29"/>
       <c r="J108" s="34"/>
@@ -10611,51 +10614,51 @@
       <c r="AW108" s="16"/>
       <c r="AX108" s="16"/>
       <c r="AY108" s="16"/>
-      <c r="AZ108" s="215" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA108" s="215"/>
-      <c r="BB108" s="215"/>
-      <c r="BC108" s="216"/>
-      <c r="BD108" s="215">
+      <c r="AZ108" s="221" t="s">
+        <v>142</v>
+      </c>
+      <c r="BA108" s="221"/>
+      <c r="BB108" s="221"/>
+      <c r="BC108" s="222"/>
+      <c r="BD108" s="221">
         <v>25000</v>
       </c>
-      <c r="BE108" s="215"/>
-      <c r="BF108" s="215"/>
-      <c r="BG108" s="215">
+      <c r="BE108" s="221"/>
+      <c r="BF108" s="221"/>
+      <c r="BG108" s="221">
         <v>5000</v>
       </c>
-      <c r="BH108" s="215"/>
-      <c r="BI108" s="215"/>
-      <c r="BJ108" s="217"/>
-      <c r="BK108" s="219" t="s">
-        <v>40</v>
+      <c r="BH108" s="221"/>
+      <c r="BI108" s="221"/>
+      <c r="BJ108" s="223"/>
+      <c r="BK108" s="225" t="s">
+        <v>36</v>
       </c>
       <c r="BL108" s="97"/>
       <c r="BO108" s="29"/>
-      <c r="BP108" s="222"/>
-      <c r="BQ108" s="222"/>
-      <c r="BR108" s="222"/>
-      <c r="BS108" s="222"/>
-      <c r="BT108" s="225"/>
-      <c r="BU108" s="225"/>
-      <c r="BV108" s="225"/>
+      <c r="BP108" s="228"/>
+      <c r="BQ108" s="228"/>
+      <c r="BR108" s="228"/>
+      <c r="BS108" s="228"/>
+      <c r="BT108" s="231"/>
+      <c r="BU108" s="231"/>
+      <c r="BV108" s="231"/>
       <c r="BW108" s="87"/>
-      <c r="BX108" s="225"/>
-      <c r="BY108" s="225"/>
-      <c r="BZ108" s="225"/>
-      <c r="CA108" s="225"/>
-      <c r="CB108" s="225"/>
-      <c r="CC108" s="225"/>
-      <c r="CD108" s="228"/>
-      <c r="CE108" s="227"/>
+      <c r="BX108" s="231"/>
+      <c r="BY108" s="231"/>
+      <c r="BZ108" s="231"/>
+      <c r="CA108" s="231"/>
+      <c r="CB108" s="231"/>
+      <c r="CC108" s="231"/>
+      <c r="CD108" s="234"/>
+      <c r="CE108" s="233"/>
       <c r="CF108" s="97"/>
     </row>
     <row r="109" ht="20.4" spans="1:84">
-      <c r="A109" s="174"/>
-      <c r="B109" s="174"/>
-      <c r="D109" s="175" t="s">
-        <v>153</v>
+      <c r="A109" s="177"/>
+      <c r="B109" s="177"/>
+      <c r="D109" s="178" t="s">
+        <v>152</v>
       </c>
       <c r="E109" s="16"/>
       <c r="F109" s="16"/>
@@ -10668,7 +10671,7 @@
       </c>
       <c r="L109" s="27"/>
       <c r="N109" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O109" s="16"/>
       <c r="P109" s="16"/>
@@ -10679,54 +10682,54 @@
       </c>
       <c r="T109" s="107"/>
       <c r="U109" s="107"/>
-      <c r="V109" s="190"/>
+      <c r="V109" s="193"/>
       <c r="AU109" s="29"/>
       <c r="AV109" s="16"/>
       <c r="AW109" s="16"/>
       <c r="AX109" s="16"/>
       <c r="AY109" s="16"/>
-      <c r="AZ109" s="215" t="s">
-        <v>144</v>
-      </c>
-      <c r="BA109" s="215"/>
-      <c r="BB109" s="215"/>
-      <c r="BC109" s="216"/>
-      <c r="BD109" s="215">
+      <c r="AZ109" s="221" t="s">
+        <v>143</v>
+      </c>
+      <c r="BA109" s="221"/>
+      <c r="BB109" s="221"/>
+      <c r="BC109" s="222"/>
+      <c r="BD109" s="221">
         <v>3000</v>
       </c>
-      <c r="BE109" s="215"/>
-      <c r="BF109" s="215"/>
-      <c r="BG109" s="215">
+      <c r="BE109" s="221"/>
+      <c r="BF109" s="221"/>
+      <c r="BG109" s="221">
         <v>1000</v>
       </c>
-      <c r="BH109" s="215"/>
-      <c r="BI109" s="215"/>
-      <c r="BJ109" s="217"/>
-      <c r="BK109" s="218"/>
+      <c r="BH109" s="221"/>
+      <c r="BI109" s="221"/>
+      <c r="BJ109" s="223"/>
+      <c r="BK109" s="224"/>
       <c r="BL109" s="97"/>
       <c r="BO109" s="29"/>
-      <c r="BP109" s="222"/>
-      <c r="BQ109" s="222"/>
-      <c r="BR109" s="222"/>
-      <c r="BS109" s="222"/>
-      <c r="BT109" s="225"/>
-      <c r="BU109" s="225"/>
-      <c r="BV109" s="225"/>
+      <c r="BP109" s="228"/>
+      <c r="BQ109" s="228"/>
+      <c r="BR109" s="228"/>
+      <c r="BS109" s="228"/>
+      <c r="BT109" s="231"/>
+      <c r="BU109" s="231"/>
+      <c r="BV109" s="231"/>
       <c r="BW109" s="87"/>
-      <c r="BX109" s="225"/>
-      <c r="BY109" s="225"/>
-      <c r="BZ109" s="225"/>
-      <c r="CA109" s="225"/>
-      <c r="CB109" s="225"/>
-      <c r="CC109" s="225"/>
-      <c r="CD109" s="228"/>
-      <c r="CE109" s="226"/>
+      <c r="BX109" s="231"/>
+      <c r="BY109" s="231"/>
+      <c r="BZ109" s="231"/>
+      <c r="CA109" s="231"/>
+      <c r="CB109" s="231"/>
+      <c r="CC109" s="231"/>
+      <c r="CD109" s="234"/>
+      <c r="CE109" s="232"/>
       <c r="CF109" s="97"/>
     </row>
     <row r="110" ht="17.6" spans="1:84">
-      <c r="A110" s="174"/>
-      <c r="B110" s="174"/>
-      <c r="D110" s="175"/>
+      <c r="A110" s="177"/>
+      <c r="B110" s="177"/>
+      <c r="D110" s="178"/>
       <c r="E110" s="16"/>
       <c r="F110" s="16"/>
       <c r="G110" s="16"/>
@@ -10743,53 +10746,53 @@
       <c r="S110" s="107"/>
       <c r="T110" s="107"/>
       <c r="U110" s="107"/>
-      <c r="V110" s="190"/>
+      <c r="V110" s="193"/>
       <c r="AU110" s="29"/>
       <c r="AV110" s="16"/>
       <c r="AW110" s="16"/>
       <c r="AX110" s="16"/>
       <c r="AY110" s="16"/>
-      <c r="AZ110" s="215" t="s">
-        <v>136</v>
-      </c>
-      <c r="BA110" s="215"/>
-      <c r="BB110" s="215"/>
-      <c r="BC110" s="216"/>
-      <c r="BD110" s="215">
+      <c r="AZ110" s="221" t="s">
+        <v>135</v>
+      </c>
+      <c r="BA110" s="221"/>
+      <c r="BB110" s="221"/>
+      <c r="BC110" s="222"/>
+      <c r="BD110" s="221">
         <v>6000</v>
       </c>
-      <c r="BE110" s="215"/>
-      <c r="BF110" s="215"/>
-      <c r="BG110" s="215">
+      <c r="BE110" s="221"/>
+      <c r="BF110" s="221"/>
+      <c r="BG110" s="221">
         <v>1000</v>
       </c>
-      <c r="BH110" s="215"/>
-      <c r="BI110" s="215"/>
-      <c r="BJ110" s="217"/>
-      <c r="BK110" s="216"/>
+      <c r="BH110" s="221"/>
+      <c r="BI110" s="221"/>
+      <c r="BJ110" s="223"/>
+      <c r="BK110" s="222"/>
       <c r="BL110" s="97"/>
       <c r="BO110" s="29"/>
-      <c r="BP110" s="222"/>
-      <c r="BQ110" s="222"/>
-      <c r="BR110" s="222"/>
-      <c r="BS110" s="222"/>
-      <c r="BT110" s="225"/>
-      <c r="BU110" s="225"/>
-      <c r="BV110" s="225"/>
+      <c r="BP110" s="228"/>
+      <c r="BQ110" s="228"/>
+      <c r="BR110" s="228"/>
+      <c r="BS110" s="228"/>
+      <c r="BT110" s="231"/>
+      <c r="BU110" s="231"/>
+      <c r="BV110" s="231"/>
       <c r="BW110" s="87"/>
-      <c r="BX110" s="225"/>
-      <c r="BY110" s="225"/>
-      <c r="BZ110" s="225"/>
-      <c r="CA110" s="225"/>
-      <c r="CB110" s="225"/>
-      <c r="CC110" s="225"/>
-      <c r="CD110" s="228"/>
+      <c r="BX110" s="231"/>
+      <c r="BY110" s="231"/>
+      <c r="BZ110" s="231"/>
+      <c r="CA110" s="231"/>
+      <c r="CB110" s="231"/>
+      <c r="CC110" s="231"/>
+      <c r="CD110" s="234"/>
       <c r="CE110" s="87"/>
       <c r="CF110" s="97"/>
     </row>
     <row r="111" spans="1:84">
-      <c r="A111" s="174"/>
-      <c r="B111" s="174"/>
+      <c r="A111" s="177"/>
+      <c r="B111" s="177"/>
       <c r="D111" s="29"/>
       <c r="J111" s="34"/>
       <c r="V111" s="97"/>
@@ -10815,8 +10818,8 @@
       <c r="CF111" s="97"/>
     </row>
     <row r="112" ht="17.55" spans="4:84">
-      <c r="D112" s="175" t="s">
-        <v>155</v>
+      <c r="D112" s="178" t="s">
+        <v>154</v>
       </c>
       <c r="E112" s="16"/>
       <c r="F112" s="16"/>
@@ -10828,7 +10831,7 @@
         <v>150</v>
       </c>
       <c r="N112" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O112" s="16"/>
       <c r="P112" s="16"/>
@@ -10839,46 +10842,46 @@
       </c>
       <c r="T112" s="107"/>
       <c r="U112" s="107"/>
-      <c r="V112" s="190"/>
-      <c r="AU112" s="214"/>
-      <c r="AV112" s="182"/>
-      <c r="AW112" s="182"/>
-      <c r="AX112" s="182"/>
-      <c r="AY112" s="182"/>
-      <c r="AZ112" s="182"/>
-      <c r="BA112" s="182"/>
-      <c r="BB112" s="182"/>
-      <c r="BC112" s="182"/>
-      <c r="BD112" s="182"/>
-      <c r="BE112" s="182"/>
-      <c r="BF112" s="182"/>
-      <c r="BG112" s="182"/>
-      <c r="BH112" s="182"/>
-      <c r="BI112" s="182"/>
-      <c r="BJ112" s="182"/>
-      <c r="BK112" s="182"/>
-      <c r="BL112" s="220"/>
-      <c r="BO112" s="214"/>
-      <c r="BP112" s="182"/>
-      <c r="BQ112" s="182"/>
-      <c r="BR112" s="182"/>
-      <c r="BS112" s="182"/>
-      <c r="BT112" s="182"/>
-      <c r="BU112" s="182"/>
-      <c r="BV112" s="182"/>
-      <c r="BW112" s="182"/>
-      <c r="BX112" s="182"/>
-      <c r="BY112" s="182"/>
-      <c r="BZ112" s="182"/>
-      <c r="CA112" s="182"/>
-      <c r="CB112" s="182"/>
-      <c r="CC112" s="182"/>
-      <c r="CD112" s="182"/>
-      <c r="CE112" s="182"/>
-      <c r="CF112" s="220"/>
+      <c r="V112" s="193"/>
+      <c r="AU112" s="220"/>
+      <c r="AV112" s="185"/>
+      <c r="AW112" s="185"/>
+      <c r="AX112" s="185"/>
+      <c r="AY112" s="185"/>
+      <c r="AZ112" s="185"/>
+      <c r="BA112" s="185"/>
+      <c r="BB112" s="185"/>
+      <c r="BC112" s="185"/>
+      <c r="BD112" s="185"/>
+      <c r="BE112" s="185"/>
+      <c r="BF112" s="185"/>
+      <c r="BG112" s="185"/>
+      <c r="BH112" s="185"/>
+      <c r="BI112" s="185"/>
+      <c r="BJ112" s="185"/>
+      <c r="BK112" s="185"/>
+      <c r="BL112" s="226"/>
+      <c r="BO112" s="220"/>
+      <c r="BP112" s="185"/>
+      <c r="BQ112" s="185"/>
+      <c r="BR112" s="185"/>
+      <c r="BS112" s="185"/>
+      <c r="BT112" s="185"/>
+      <c r="BU112" s="185"/>
+      <c r="BV112" s="185"/>
+      <c r="BW112" s="185"/>
+      <c r="BX112" s="185"/>
+      <c r="BY112" s="185"/>
+      <c r="BZ112" s="185"/>
+      <c r="CA112" s="185"/>
+      <c r="CB112" s="185"/>
+      <c r="CC112" s="185"/>
+      <c r="CD112" s="185"/>
+      <c r="CE112" s="185"/>
+      <c r="CF112" s="226"/>
     </row>
     <row r="113" ht="16" customHeight="1" spans="4:22">
-      <c r="D113" s="175"/>
+      <c r="D113" s="178"/>
       <c r="E113" s="16"/>
       <c r="F113" s="16"/>
       <c r="G113" s="16"/>
@@ -10893,7 +10896,7 @@
       <c r="S113" s="107"/>
       <c r="T113" s="107"/>
       <c r="U113" s="107"/>
-      <c r="V113" s="190"/>
+      <c r="V113" s="193"/>
     </row>
     <row r="114" ht="16" customHeight="1" spans="4:22">
       <c r="D114" s="29"/>
@@ -10901,8 +10904,8 @@
       <c r="V114" s="97"/>
     </row>
     <row r="115" spans="4:22">
-      <c r="D115" s="175" t="s">
-        <v>156</v>
+      <c r="D115" s="178" t="s">
+        <v>155</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
@@ -10914,7 +10917,7 @@
         <v>200</v>
       </c>
       <c r="N115" s="16" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="O115" s="16"/>
       <c r="P115" s="16"/>
@@ -10925,10 +10928,10 @@
       </c>
       <c r="T115" s="107"/>
       <c r="U115" s="107"/>
-      <c r="V115" s="190"/>
+      <c r="V115" s="193"/>
     </row>
     <row r="116" spans="4:22">
-      <c r="D116" s="175"/>
+      <c r="D116" s="178"/>
       <c r="E116" s="16"/>
       <c r="F116" s="16"/>
       <c r="G116" s="16"/>
@@ -10943,7 +10946,7 @@
       <c r="S116" s="107"/>
       <c r="T116" s="107"/>
       <c r="U116" s="107"/>
-      <c r="V116" s="190"/>
+      <c r="V116" s="193"/>
     </row>
     <row r="117" spans="4:22">
       <c r="D117" s="29"/>
@@ -10968,33 +10971,33 @@
     </row>
     <row r="118" spans="4:22">
       <c r="D118" s="29"/>
-      <c r="E118" s="180"/>
-      <c r="F118" s="180"/>
-      <c r="G118" s="180"/>
-      <c r="H118" s="180"/>
-      <c r="I118" s="180"/>
-      <c r="J118" s="180"/>
-      <c r="K118" s="180"/>
-      <c r="L118" s="180"/>
-      <c r="M118" s="180"/>
-      <c r="N118" s="180"/>
-      <c r="O118" s="180"/>
-      <c r="P118" s="180"/>
-      <c r="Q118" s="180"/>
-      <c r="R118" s="180"/>
-      <c r="S118" s="180"/>
+      <c r="E118" s="183"/>
+      <c r="F118" s="183"/>
+      <c r="G118" s="183"/>
+      <c r="H118" s="183"/>
+      <c r="I118" s="183"/>
+      <c r="J118" s="183"/>
+      <c r="K118" s="183"/>
+      <c r="L118" s="183"/>
+      <c r="M118" s="183"/>
+      <c r="N118" s="183"/>
+      <c r="O118" s="183"/>
+      <c r="P118" s="183"/>
+      <c r="Q118" s="183"/>
+      <c r="R118" s="183"/>
+      <c r="S118" s="183"/>
       <c r="T118" s="34"/>
       <c r="U118" s="34"/>
       <c r="V118" s="97"/>
     </row>
     <row r="119" spans="4:22">
       <c r="D119" s="29"/>
-      <c r="E119" s="176" t="s">
-        <v>157</v>
-      </c>
-      <c r="F119" s="176"/>
-      <c r="G119" s="176"/>
-      <c r="H119" s="176"/>
+      <c r="E119" s="179" t="s">
+        <v>156</v>
+      </c>
+      <c r="F119" s="179"/>
+      <c r="G119" s="179"/>
+      <c r="H119" s="179"/>
       <c r="I119" s="34"/>
       <c r="J119" s="34"/>
       <c r="K119" s="34"/>
@@ -11032,68 +11035,68 @@
       <c r="V120" s="97"/>
     </row>
     <row r="121" spans="4:22">
-      <c r="D121" s="173" t="s">
-        <v>158</v>
+      <c r="D121" s="176" t="s">
+        <v>157</v>
       </c>
       <c r="E121" s="19"/>
       <c r="F121" s="19"/>
       <c r="G121" s="19"/>
       <c r="H121" s="19"/>
       <c r="I121" s="19"/>
-      <c r="J121" s="184">
+      <c r="J121" s="187">
         <v>50</v>
       </c>
-      <c r="K121" s="184"/>
-      <c r="L121" s="184"/>
-      <c r="M121" s="186"/>
+      <c r="K121" s="187"/>
+      <c r="L121" s="187"/>
+      <c r="M121" s="189"/>
       <c r="N121" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O121" s="16"/>
       <c r="P121" s="16"/>
       <c r="Q121" s="16"/>
       <c r="R121" s="16"/>
-      <c r="S121" s="189">
+      <c r="S121" s="192">
         <f>J121*500</f>
         <v>25000</v>
       </c>
-      <c r="T121" s="189"/>
-      <c r="U121" s="189"/>
-      <c r="V121" s="191"/>
+      <c r="T121" s="192"/>
+      <c r="U121" s="192"/>
+      <c r="V121" s="194"/>
     </row>
     <row r="122" spans="4:22">
-      <c r="D122" s="173"/>
+      <c r="D122" s="176"/>
       <c r="E122" s="19"/>
       <c r="F122" s="19"/>
       <c r="G122" s="19"/>
       <c r="H122" s="19"/>
       <c r="I122" s="19"/>
-      <c r="J122" s="184"/>
-      <c r="K122" s="184"/>
-      <c r="L122" s="184"/>
-      <c r="M122" s="186"/>
+      <c r="J122" s="187"/>
+      <c r="K122" s="187"/>
+      <c r="L122" s="187"/>
+      <c r="M122" s="189"/>
       <c r="N122" s="16"/>
       <c r="O122" s="16"/>
       <c r="P122" s="16"/>
       <c r="Q122" s="16"/>
       <c r="R122" s="16"/>
-      <c r="S122" s="189"/>
-      <c r="T122" s="189"/>
-      <c r="U122" s="189"/>
-      <c r="V122" s="191"/>
+      <c r="S122" s="192"/>
+      <c r="T122" s="192"/>
+      <c r="U122" s="192"/>
+      <c r="V122" s="194"/>
     </row>
     <row r="123" spans="1:22">
-      <c r="A123" s="170" t="s">
-        <v>117</v>
-      </c>
-      <c r="B123" s="171"/>
+      <c r="A123" s="173" t="s">
+        <v>116</v>
+      </c>
+      <c r="B123" s="174"/>
       <c r="D123" s="29"/>
       <c r="H123" s="27"/>
       <c r="I123" s="27"/>
       <c r="J123" s="66"/>
       <c r="K123" s="27"/>
       <c r="L123" s="27"/>
-      <c r="M123" s="187"/>
+      <c r="M123" s="190"/>
       <c r="N123" s="27"/>
       <c r="O123" s="27"/>
       <c r="P123" s="27"/>
@@ -11105,73 +11108,73 @@
       <c r="V123" s="97"/>
     </row>
     <row r="124" spans="1:22">
-      <c r="A124" s="171"/>
-      <c r="B124" s="171"/>
-      <c r="D124" s="173" t="s">
-        <v>160</v>
+      <c r="A124" s="174"/>
+      <c r="B124" s="174"/>
+      <c r="D124" s="176" t="s">
+        <v>159</v>
       </c>
       <c r="E124" s="19"/>
       <c r="F124" s="19"/>
       <c r="G124" s="19"/>
       <c r="H124" s="19"/>
       <c r="I124" s="19"/>
-      <c r="J124" s="184">
+      <c r="J124" s="187">
         <v>20</v>
       </c>
-      <c r="K124" s="184"/>
-      <c r="L124" s="184"/>
-      <c r="M124" s="188"/>
+      <c r="K124" s="187"/>
+      <c r="L124" s="187"/>
+      <c r="M124" s="191"/>
       <c r="N124" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O124" s="16"/>
       <c r="P124" s="16"/>
       <c r="Q124" s="16"/>
       <c r="R124" s="16"/>
-      <c r="S124" s="189">
+      <c r="S124" s="192">
         <f>J124*2500</f>
         <v>50000</v>
       </c>
-      <c r="T124" s="189"/>
-      <c r="U124" s="189"/>
-      <c r="V124" s="191"/>
+      <c r="T124" s="192"/>
+      <c r="U124" s="192"/>
+      <c r="V124" s="194"/>
     </row>
     <row r="125" spans="1:22">
-      <c r="A125" s="171"/>
-      <c r="B125" s="171"/>
-      <c r="D125" s="173"/>
+      <c r="A125" s="174"/>
+      <c r="B125" s="174"/>
+      <c r="D125" s="176"/>
       <c r="E125" s="19"/>
       <c r="F125" s="19"/>
       <c r="G125" s="19"/>
       <c r="H125" s="19"/>
       <c r="I125" s="19"/>
-      <c r="J125" s="184"/>
-      <c r="K125" s="184"/>
-      <c r="L125" s="184"/>
-      <c r="M125" s="188"/>
+      <c r="J125" s="187"/>
+      <c r="K125" s="187"/>
+      <c r="L125" s="187"/>
+      <c r="M125" s="191"/>
       <c r="N125" s="16"/>
       <c r="O125" s="16"/>
       <c r="P125" s="16"/>
       <c r="Q125" s="16"/>
       <c r="R125" s="16"/>
-      <c r="S125" s="189"/>
-      <c r="T125" s="189"/>
-      <c r="U125" s="189"/>
-      <c r="V125" s="191"/>
+      <c r="S125" s="192"/>
+      <c r="T125" s="192"/>
+      <c r="U125" s="192"/>
+      <c r="V125" s="194"/>
     </row>
     <row r="126" spans="1:22">
-      <c r="A126" s="171"/>
-      <c r="B126" s="171"/>
+      <c r="A126" s="174"/>
+      <c r="B126" s="174"/>
       <c r="D126" s="29"/>
       <c r="J126" s="34"/>
-      <c r="M126" s="188"/>
+      <c r="M126" s="191"/>
       <c r="V126" s="97"/>
     </row>
     <row r="127" spans="1:22">
-      <c r="A127" s="171"/>
-      <c r="B127" s="171"/>
-      <c r="D127" s="173" t="s">
-        <v>161</v>
+      <c r="A127" s="174"/>
+      <c r="B127" s="174"/>
+      <c r="D127" s="176" t="s">
+        <v>160</v>
       </c>
       <c r="E127" s="19"/>
       <c r="F127" s="19"/>
@@ -11183,26 +11186,26 @@
       </c>
       <c r="K127" s="27"/>
       <c r="L127" s="27"/>
-      <c r="M127" s="188"/>
+      <c r="M127" s="191"/>
       <c r="N127" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O127" s="16"/>
       <c r="P127" s="16"/>
       <c r="Q127" s="16"/>
       <c r="R127" s="16"/>
-      <c r="S127" s="189">
+      <c r="S127" s="192">
         <f>J127*15000</f>
         <v>75000</v>
       </c>
-      <c r="T127" s="189"/>
-      <c r="U127" s="189"/>
-      <c r="V127" s="191"/>
+      <c r="T127" s="192"/>
+      <c r="U127" s="192"/>
+      <c r="V127" s="194"/>
     </row>
     <row r="128" spans="1:22">
-      <c r="A128" s="171"/>
-      <c r="B128" s="171"/>
-      <c r="D128" s="173"/>
+      <c r="A128" s="174"/>
+      <c r="B128" s="174"/>
+      <c r="D128" s="176"/>
       <c r="E128" s="19"/>
       <c r="F128" s="19"/>
       <c r="G128" s="19"/>
@@ -11211,30 +11214,30 @@
       <c r="J128" s="27"/>
       <c r="K128" s="27"/>
       <c r="L128" s="27"/>
-      <c r="M128" s="188"/>
+      <c r="M128" s="191"/>
       <c r="N128" s="16"/>
       <c r="O128" s="16"/>
       <c r="P128" s="16"/>
       <c r="Q128" s="16"/>
       <c r="R128" s="16"/>
-      <c r="S128" s="189"/>
-      <c r="T128" s="189"/>
-      <c r="U128" s="189"/>
-      <c r="V128" s="191"/>
+      <c r="S128" s="192"/>
+      <c r="T128" s="192"/>
+      <c r="U128" s="192"/>
+      <c r="V128" s="194"/>
     </row>
     <row r="129" spans="1:22">
-      <c r="A129" s="171"/>
-      <c r="B129" s="171"/>
+      <c r="A129" s="174"/>
+      <c r="B129" s="174"/>
       <c r="D129" s="29"/>
       <c r="J129" s="34"/>
-      <c r="M129" s="188"/>
+      <c r="M129" s="191"/>
       <c r="V129" s="97"/>
     </row>
     <row r="130" spans="1:22">
-      <c r="A130" s="171"/>
-      <c r="B130" s="171"/>
-      <c r="D130" s="173" t="s">
-        <v>162</v>
+      <c r="A130" s="174"/>
+      <c r="B130" s="174"/>
+      <c r="D130" s="176" t="s">
+        <v>161</v>
       </c>
       <c r="E130" s="19"/>
       <c r="F130" s="19"/>
@@ -11244,50 +11247,50 @@
       <c r="J130" s="25">
         <v>1</v>
       </c>
-      <c r="M130" s="188"/>
+      <c r="M130" s="191"/>
       <c r="N130" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O130" s="16"/>
       <c r="P130" s="16"/>
       <c r="Q130" s="16"/>
       <c r="R130" s="16"/>
-      <c r="S130" s="189">
+      <c r="S130" s="192">
         <v>35000</v>
       </c>
-      <c r="T130" s="189"/>
-      <c r="U130" s="189"/>
-      <c r="V130" s="191"/>
+      <c r="T130" s="192"/>
+      <c r="U130" s="192"/>
+      <c r="V130" s="194"/>
     </row>
     <row r="131" spans="1:22">
-      <c r="A131" s="171"/>
-      <c r="B131" s="171"/>
-      <c r="D131" s="173"/>
+      <c r="A131" s="174"/>
+      <c r="B131" s="174"/>
+      <c r="D131" s="176"/>
       <c r="E131" s="19"/>
       <c r="F131" s="19"/>
       <c r="G131" s="19"/>
       <c r="H131" s="19"/>
       <c r="I131" s="19"/>
-      <c r="M131" s="188"/>
+      <c r="M131" s="191"/>
       <c r="N131" s="16"/>
       <c r="O131" s="16"/>
       <c r="P131" s="16"/>
       <c r="Q131" s="16"/>
       <c r="R131" s="16"/>
-      <c r="S131" s="189"/>
-      <c r="T131" s="189"/>
-      <c r="U131" s="189"/>
-      <c r="V131" s="191"/>
+      <c r="S131" s="192"/>
+      <c r="T131" s="192"/>
+      <c r="U131" s="192"/>
+      <c r="V131" s="194"/>
     </row>
     <row r="132" spans="4:22">
       <c r="D132" s="29"/>
       <c r="J132" s="34"/>
-      <c r="M132" s="188"/>
+      <c r="M132" s="191"/>
       <c r="V132" s="97"/>
     </row>
     <row r="133" spans="4:22">
-      <c r="D133" s="173" t="s">
-        <v>163</v>
+      <c r="D133" s="176" t="s">
+        <v>162</v>
       </c>
       <c r="E133" s="19"/>
       <c r="F133" s="19"/>
@@ -11297,47 +11300,47 @@
       <c r="J133" s="25">
         <v>0</v>
       </c>
-      <c r="M133" s="188"/>
+      <c r="M133" s="191"/>
       <c r="N133" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O133" s="16"/>
       <c r="P133" s="16"/>
       <c r="Q133" s="16"/>
       <c r="R133" s="16"/>
-      <c r="S133" s="189">
+      <c r="S133" s="192">
         <v>0</v>
       </c>
-      <c r="T133" s="189"/>
-      <c r="U133" s="189"/>
-      <c r="V133" s="191"/>
+      <c r="T133" s="192"/>
+      <c r="U133" s="192"/>
+      <c r="V133" s="194"/>
     </row>
     <row r="134" spans="4:22">
-      <c r="D134" s="173"/>
+      <c r="D134" s="176"/>
       <c r="E134" s="19"/>
       <c r="F134" s="19"/>
       <c r="G134" s="19"/>
       <c r="H134" s="19"/>
       <c r="I134" s="19"/>
-      <c r="M134" s="188"/>
+      <c r="M134" s="191"/>
       <c r="N134" s="16"/>
       <c r="O134" s="16"/>
       <c r="P134" s="16"/>
       <c r="Q134" s="16"/>
       <c r="R134" s="16"/>
-      <c r="S134" s="189"/>
-      <c r="T134" s="189"/>
-      <c r="U134" s="189"/>
-      <c r="V134" s="191"/>
+      <c r="S134" s="192"/>
+      <c r="T134" s="192"/>
+      <c r="U134" s="192"/>
+      <c r="V134" s="194"/>
     </row>
     <row r="135" spans="4:22">
       <c r="D135" s="29"/>
-      <c r="M135" s="188"/>
+      <c r="M135" s="191"/>
       <c r="V135" s="97"/>
     </row>
     <row r="136" spans="4:22">
-      <c r="D136" s="173" t="s">
-        <v>164</v>
+      <c r="D136" s="176" t="s">
+        <v>163</v>
       </c>
       <c r="E136" s="19"/>
       <c r="F136" s="19"/>
@@ -11347,38 +11350,38 @@
       <c r="J136" s="25">
         <v>0</v>
       </c>
-      <c r="M136" s="188"/>
+      <c r="M136" s="191"/>
       <c r="N136" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="O136" s="16"/>
       <c r="P136" s="16"/>
       <c r="Q136" s="16"/>
       <c r="R136" s="16"/>
-      <c r="S136" s="189">
+      <c r="S136" s="192">
         <v>0</v>
       </c>
-      <c r="T136" s="189"/>
-      <c r="U136" s="189"/>
-      <c r="V136" s="191"/>
+      <c r="T136" s="192"/>
+      <c r="U136" s="192"/>
+      <c r="V136" s="194"/>
     </row>
     <row r="137" spans="4:22">
-      <c r="D137" s="173"/>
+      <c r="D137" s="176"/>
       <c r="E137" s="19"/>
       <c r="F137" s="19"/>
       <c r="G137" s="19"/>
       <c r="H137" s="19"/>
       <c r="I137" s="19"/>
-      <c r="M137" s="188"/>
+      <c r="M137" s="191"/>
       <c r="N137" s="16"/>
       <c r="O137" s="16"/>
       <c r="P137" s="16"/>
       <c r="Q137" s="16"/>
       <c r="R137" s="16"/>
-      <c r="S137" s="189"/>
-      <c r="T137" s="189"/>
-      <c r="U137" s="189"/>
-      <c r="V137" s="191"/>
+      <c r="S137" s="192"/>
+      <c r="T137" s="192"/>
+      <c r="U137" s="192"/>
+      <c r="V137" s="194"/>
     </row>
     <row r="138" spans="4:22">
       <c r="D138" s="29"/>
@@ -11402,101 +11405,101 @@
       <c r="V138" s="97"/>
     </row>
     <row r="139" ht="16.5" customHeight="1" spans="4:22">
-      <c r="D139" s="229" t="s">
-        <v>165</v>
-      </c>
-      <c r="E139" s="231"/>
-      <c r="F139" s="231"/>
-      <c r="G139" s="231"/>
-      <c r="H139" s="231"/>
-      <c r="I139" s="231"/>
-      <c r="J139" s="231"/>
-      <c r="K139" s="231"/>
-      <c r="L139" s="231"/>
-      <c r="M139" s="231"/>
-      <c r="N139" s="232">
+      <c r="D139" s="235" t="s">
+        <v>164</v>
+      </c>
+      <c r="E139" s="237"/>
+      <c r="F139" s="237"/>
+      <c r="G139" s="237"/>
+      <c r="H139" s="237"/>
+      <c r="I139" s="237"/>
+      <c r="J139" s="237"/>
+      <c r="K139" s="237"/>
+      <c r="L139" s="237"/>
+      <c r="M139" s="237"/>
+      <c r="N139" s="238">
         <f>(S121+S124+S127+S130+S133+S136)/76</f>
         <v>2434.21052631579</v>
       </c>
-      <c r="O139" s="232"/>
-      <c r="P139" s="232"/>
-      <c r="Q139" s="232"/>
-      <c r="R139" s="232"/>
-      <c r="S139" s="231"/>
-      <c r="T139" s="231"/>
-      <c r="U139" s="231"/>
-      <c r="V139" s="235"/>
+      <c r="O139" s="238"/>
+      <c r="P139" s="238"/>
+      <c r="Q139" s="238"/>
+      <c r="R139" s="238"/>
+      <c r="S139" s="237"/>
+      <c r="T139" s="237"/>
+      <c r="U139" s="237"/>
+      <c r="V139" s="241"/>
     </row>
     <row r="140" ht="16.5" customHeight="1" spans="4:22">
-      <c r="D140" s="229"/>
-      <c r="E140" s="231"/>
-      <c r="F140" s="231"/>
-      <c r="G140" s="231"/>
-      <c r="H140" s="231"/>
-      <c r="I140" s="231"/>
-      <c r="J140" s="231"/>
-      <c r="K140" s="231"/>
-      <c r="L140" s="231"/>
-      <c r="M140" s="231"/>
-      <c r="N140" s="232"/>
-      <c r="O140" s="232"/>
-      <c r="P140" s="232"/>
-      <c r="Q140" s="232"/>
-      <c r="R140" s="232"/>
-      <c r="S140" s="231"/>
-      <c r="T140" s="231"/>
-      <c r="U140" s="231"/>
-      <c r="V140" s="235"/>
+      <c r="D140" s="235"/>
+      <c r="E140" s="237"/>
+      <c r="F140" s="237"/>
+      <c r="G140" s="237"/>
+      <c r="H140" s="237"/>
+      <c r="I140" s="237"/>
+      <c r="J140" s="237"/>
+      <c r="K140" s="237"/>
+      <c r="L140" s="237"/>
+      <c r="M140" s="237"/>
+      <c r="N140" s="238"/>
+      <c r="O140" s="238"/>
+      <c r="P140" s="238"/>
+      <c r="Q140" s="238"/>
+      <c r="R140" s="238"/>
+      <c r="S140" s="237"/>
+      <c r="T140" s="237"/>
+      <c r="U140" s="237"/>
+      <c r="V140" s="241"/>
     </row>
     <row r="141" spans="1:22">
-      <c r="A141" s="170" t="s">
-        <v>166</v>
-      </c>
-      <c r="B141" s="171"/>
+      <c r="A141" s="173" t="s">
+        <v>165</v>
+      </c>
+      <c r="B141" s="174"/>
       <c r="D141" s="29"/>
-      <c r="E141" s="180"/>
-      <c r="F141" s="180"/>
-      <c r="G141" s="180"/>
-      <c r="H141" s="180"/>
-      <c r="I141" s="180"/>
-      <c r="J141" s="180"/>
-      <c r="K141" s="180"/>
-      <c r="L141" s="180"/>
-      <c r="M141" s="180"/>
-      <c r="N141" s="180"/>
-      <c r="O141" s="180"/>
-      <c r="P141" s="180"/>
-      <c r="Q141" s="180"/>
-      <c r="R141" s="180"/>
-      <c r="S141" s="180"/>
+      <c r="E141" s="183"/>
+      <c r="F141" s="183"/>
+      <c r="G141" s="183"/>
+      <c r="H141" s="183"/>
+      <c r="I141" s="183"/>
+      <c r="J141" s="183"/>
+      <c r="K141" s="183"/>
+      <c r="L141" s="183"/>
+      <c r="M141" s="183"/>
+      <c r="N141" s="183"/>
+      <c r="O141" s="183"/>
+      <c r="P141" s="183"/>
+      <c r="Q141" s="183"/>
+      <c r="R141" s="183"/>
+      <c r="S141" s="183"/>
       <c r="T141" s="34"/>
       <c r="U141" s="34"/>
       <c r="V141" s="97"/>
     </row>
     <row r="142" spans="1:22">
-      <c r="A142" s="171"/>
-      <c r="B142" s="171"/>
-      <c r="D142" s="230" t="s">
-        <v>167</v>
-      </c>
-      <c r="E142" s="177"/>
-      <c r="F142" s="177"/>
-      <c r="G142" s="177"/>
-      <c r="H142" s="177"/>
-      <c r="I142" s="177"/>
+      <c r="A142" s="174"/>
+      <c r="B142" s="174"/>
+      <c r="D142" s="236" t="s">
+        <v>166</v>
+      </c>
+      <c r="E142" s="180"/>
+      <c r="F142" s="180"/>
+      <c r="G142" s="180"/>
+      <c r="H142" s="180"/>
+      <c r="I142" s="180"/>
       <c r="V142" s="97"/>
     </row>
     <row r="143" spans="1:22">
-      <c r="A143" s="171"/>
-      <c r="B143" s="171"/>
+      <c r="A143" s="174"/>
+      <c r="B143" s="174"/>
       <c r="D143" s="29"/>
       <c r="V143" s="97"/>
     </row>
     <row r="144" spans="1:22">
-      <c r="A144" s="171"/>
-      <c r="B144" s="171"/>
-      <c r="D144" s="173" t="s">
-        <v>168</v>
+      <c r="A144" s="174"/>
+      <c r="B144" s="174"/>
+      <c r="D144" s="176" t="s">
+        <v>167</v>
       </c>
       <c r="E144" s="19"/>
       <c r="F144" s="19"/>
@@ -11506,8 +11509,8 @@
       <c r="J144" s="25">
         <v>10</v>
       </c>
-      <c r="M144" s="233" t="s">
-        <v>169</v>
+      <c r="M144" s="239" t="s">
+        <v>168</v>
       </c>
       <c r="N144" s="19"/>
       <c r="O144" s="19"/>
@@ -11520,15 +11523,15 @@
       <c r="V144" s="97"/>
     </row>
     <row r="145" spans="1:22">
-      <c r="A145" s="171"/>
-      <c r="B145" s="171"/>
-      <c r="D145" s="173"/>
+      <c r="A145" s="174"/>
+      <c r="B145" s="174"/>
+      <c r="D145" s="176"/>
       <c r="E145" s="19"/>
       <c r="F145" s="19"/>
       <c r="G145" s="19"/>
       <c r="H145" s="19"/>
       <c r="I145" s="19"/>
-      <c r="M145" s="233"/>
+      <c r="M145" s="239"/>
       <c r="N145" s="19"/>
       <c r="O145" s="19"/>
       <c r="P145" s="19"/>
@@ -11537,16 +11540,16 @@
       <c r="V145" s="97"/>
     </row>
     <row r="146" spans="1:22">
-      <c r="A146" s="171"/>
-      <c r="B146" s="171"/>
+      <c r="A146" s="174"/>
+      <c r="B146" s="174"/>
       <c r="D146" s="29"/>
       <c r="V146" s="97"/>
     </row>
     <row r="147" spans="1:22">
-      <c r="A147" s="171"/>
-      <c r="B147" s="171"/>
-      <c r="D147" s="173" t="s">
-        <v>170</v>
+      <c r="A147" s="174"/>
+      <c r="B147" s="174"/>
+      <c r="D147" s="176" t="s">
+        <v>169</v>
       </c>
       <c r="E147" s="19"/>
       <c r="F147" s="19"/>
@@ -11557,64 +11560,64 @@
         <f>S144/J144</f>
         <v>3000</v>
       </c>
-      <c r="M147" s="233" t="s">
-        <v>171</v>
+      <c r="M147" s="239" t="s">
+        <v>170</v>
       </c>
       <c r="N147" s="19"/>
       <c r="O147" s="19"/>
       <c r="P147" s="19"/>
       <c r="Q147" s="19"/>
       <c r="R147" s="19"/>
-      <c r="S147" s="234">
+      <c r="S147" s="240">
         <f>J144/(H94+M94)</f>
         <v>0.125</v>
       </c>
-      <c r="T147" s="234"/>
-      <c r="U147" s="234"/>
-      <c r="V147" s="236"/>
+      <c r="T147" s="240"/>
+      <c r="U147" s="240"/>
+      <c r="V147" s="242"/>
     </row>
     <row r="148" spans="1:22">
-      <c r="A148" s="171"/>
-      <c r="B148" s="171"/>
-      <c r="D148" s="173"/>
+      <c r="A148" s="174"/>
+      <c r="B148" s="174"/>
+      <c r="D148" s="176"/>
       <c r="E148" s="19"/>
       <c r="F148" s="19"/>
       <c r="G148" s="19"/>
       <c r="H148" s="19"/>
       <c r="I148" s="19"/>
-      <c r="M148" s="233"/>
+      <c r="M148" s="239"/>
       <c r="N148" s="19"/>
       <c r="O148" s="19"/>
       <c r="P148" s="19"/>
       <c r="Q148" s="19"/>
       <c r="R148" s="19"/>
-      <c r="S148" s="234"/>
-      <c r="T148" s="234"/>
-      <c r="U148" s="234"/>
-      <c r="V148" s="236"/>
+      <c r="S148" s="240"/>
+      <c r="T148" s="240"/>
+      <c r="U148" s="240"/>
+      <c r="V148" s="242"/>
     </row>
     <row r="149" ht="17.55" spans="1:22">
-      <c r="A149" s="171"/>
-      <c r="B149" s="171"/>
-      <c r="D149" s="202"/>
-      <c r="E149" s="181"/>
-      <c r="F149" s="181"/>
-      <c r="G149" s="181"/>
-      <c r="H149" s="181"/>
-      <c r="I149" s="181"/>
-      <c r="J149" s="181"/>
-      <c r="K149" s="181"/>
-      <c r="L149" s="181"/>
-      <c r="M149" s="181"/>
-      <c r="N149" s="181"/>
-      <c r="O149" s="181"/>
-      <c r="P149" s="181"/>
-      <c r="Q149" s="181"/>
-      <c r="R149" s="181"/>
-      <c r="S149" s="181"/>
-      <c r="T149" s="181"/>
-      <c r="U149" s="181"/>
-      <c r="V149" s="212"/>
+      <c r="A149" s="174"/>
+      <c r="B149" s="174"/>
+      <c r="D149" s="205"/>
+      <c r="E149" s="184"/>
+      <c r="F149" s="184"/>
+      <c r="G149" s="184"/>
+      <c r="H149" s="184"/>
+      <c r="I149" s="184"/>
+      <c r="J149" s="184"/>
+      <c r="K149" s="184"/>
+      <c r="L149" s="184"/>
+      <c r="M149" s="184"/>
+      <c r="N149" s="184"/>
+      <c r="O149" s="184"/>
+      <c r="P149" s="184"/>
+      <c r="Q149" s="184"/>
+      <c r="R149" s="184"/>
+      <c r="S149" s="184"/>
+      <c r="T149" s="184"/>
+      <c r="U149" s="184"/>
+      <c r="V149" s="218"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -12115,21 +12118,21 @@
     <row r="3" ht="23.2" spans="2:23">
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H3" s="14"/>
       <c r="J3" s="4"/>
       <c r="K3" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="N3" s="14"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="T3" s="14"/>
       <c r="W3" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" ht="5.15" customHeight="1" spans="2:20">
@@ -12143,33 +12146,33 @@
     <row r="5" ht="38.25" customHeight="1" spans="2:25">
       <c r="B5" s="4"/>
       <c r="C5" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="H5" s="14"/>
       <c r="J5" s="4"/>
       <c r="K5" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="N5" s="14"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="S5" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="S5" s="6" t="s">
-        <v>177</v>
       </c>
       <c r="T5" s="14"/>
       <c r="W5" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="Y5" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="Y5" s="6" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="6" ht="6" customHeight="1" spans="2:20">
@@ -12183,41 +12186,41 @@
     <row r="7" ht="109.35" customHeight="1" spans="2:27">
       <c r="B7" s="4"/>
       <c r="C7" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="G7" s="7" t="s">
         <v>179</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>180</v>
       </c>
       <c r="H7" s="14"/>
       <c r="J7" s="4"/>
       <c r="K7" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="M7" s="7" t="s">
         <v>181</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>182</v>
       </c>
       <c r="N7" s="14"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="S7" s="7" t="s">
         <v>183</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>184</v>
       </c>
       <c r="T7" s="14"/>
       <c r="U7" s="20"/>
       <c r="V7" s="20"/>
       <c r="W7" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="Y7" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="Y7" s="18" t="s">
+      <c r="AA7" s="18" t="s">
         <v>186</v>
-      </c>
-      <c r="AA7" s="18" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="8" ht="6.85" customHeight="1" spans="2:20">
@@ -12231,33 +12234,33 @@
     <row r="9" ht="84" spans="2:27">
       <c r="B9" s="4"/>
       <c r="C9" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="G9" s="15" t="s">
         <v>189</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>190</v>
       </c>
       <c r="H9" s="14"/>
       <c r="J9" s="4"/>
       <c r="K9" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="M9" s="18" t="s">
         <v>191</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>192</v>
       </c>
       <c r="N9" s="14"/>
       <c r="P9" s="4"/>
       <c r="T9" s="14"/>
       <c r="W9" s="18" t="s">
+        <v>192</v>
+      </c>
+      <c r="Y9" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="Y9" s="18" t="s">
+      <c r="AA9" s="18" t="s">
         <v>194</v>
-      </c>
-      <c r="AA9" s="18" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="10" ht="6.85" customHeight="1" spans="2:20">
@@ -12271,25 +12274,25 @@
     <row r="11" ht="72" spans="2:23">
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="G11" s="7" t="s">
         <v>197</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>198</v>
       </c>
       <c r="H11" s="14"/>
       <c r="J11" s="4"/>
       <c r="K11" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N11" s="14"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="19"/>
       <c r="T11" s="14"/>
       <c r="W11" s="21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12" ht="17.6" spans="2:29">
@@ -12302,13 +12305,13 @@
       <c r="P12" s="4"/>
       <c r="T12" s="14"/>
       <c r="W12" s="22" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="X12" s="23"/>
       <c r="Y12" s="22"/>
       <c r="Z12" s="23"/>
       <c r="AA12" s="24" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AB12" s="23"/>
       <c r="AC12" s="16"/>
@@ -12316,61 +12319,61 @@
     <row r="13" spans="2:30">
       <c r="B13" s="4"/>
       <c r="C13" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H13" s="14"/>
       <c r="J13" s="4"/>
       <c r="K13" s="10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N13" s="14"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="T13" s="14"/>
       <c r="W13" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="X13" s="22" t="s">
         <v>203</v>
       </c>
-      <c r="X13" s="22" t="s">
+      <c r="Y13" s="22" t="s">
         <v>204</v>
-      </c>
-      <c r="Y13" s="22" t="s">
-        <v>205</v>
       </c>
       <c r="Z13" s="23"/>
       <c r="AA13" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="AB13" s="16" t="s">
         <v>206</v>
       </c>
-      <c r="AB13" s="16" t="s">
+      <c r="AC13" s="22" t="s">
         <v>207</v>
       </c>
-      <c r="AC13" s="22" t="s">
+      <c r="AD13" s="16" t="s">
         <v>208</v>
-      </c>
-      <c r="AD13" s="16" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="14" spans="2:28">
       <c r="B14" s="4"/>
       <c r="C14" s="10" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E14" s="16"/>
       <c r="H14" s="14"/>
       <c r="J14" s="4"/>
       <c r="K14" s="10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N14" s="14"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="10" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="T14" s="14"/>
       <c r="W14" s="22" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="X14" s="23"/>
       <c r="Y14" s="23"/>
@@ -12397,7 +12400,7 @@
       <c r="S15" s="12"/>
       <c r="T15" s="17"/>
       <c r="W15" s="22" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="X15" s="23"/>
       <c r="Y15" s="23"/>
@@ -12407,7 +12410,7 @@
     </row>
     <row r="16" spans="23:28">
       <c r="W16" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="X16" s="23"/>
       <c r="Y16" s="23"/>
@@ -12417,7 +12420,7 @@
     </row>
     <row r="17" spans="23:28">
       <c r="W17" s="22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="X17" s="23"/>
       <c r="Y17" s="23"/>
@@ -12427,7 +12430,7 @@
     </row>
     <row r="18" spans="23:28">
       <c r="W18" s="22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="X18" s="23"/>
       <c r="Y18" s="23"/>

--- a/notes/meetings/meeting-20260417/美丫丫手机页面2.0.xlsx
+++ b/notes/meetings/meeting-20260417/美丫丫手机页面2.0.xlsx
@@ -259,7 +259,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="214">
   <si>
     <t>排行榜</t>
   </si>
@@ -537,15 +537,6 @@
   </si>
   <si>
     <t>以下数据默认按月</t>
-  </si>
-  <si>
-    <t>日期</t>
-  </si>
-  <si>
-    <t>2026.4.24</t>
-  </si>
-  <si>
-    <t>禁止自定义</t>
   </si>
   <si>
     <t>和员工端相同即可</t>
@@ -2908,7 +2899,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="246">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3395,6 +3386,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="17" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3404,6 +3407,12 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3537,15 +3546,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4403,7 +4403,7 @@
       <c r="BL7" s="161"/>
       <c r="BM7" s="101"/>
       <c r="BN7" s="101"/>
-      <c r="BO7" s="164"/>
+      <c r="BO7" s="168"/>
     </row>
     <row r="8" spans="1:67">
       <c r="A8" s="30" t="s">
@@ -4558,13 +4558,13 @@
       <c r="AT10" s="152"/>
       <c r="AU10" s="152"/>
       <c r="AW10" s="29"/>
-      <c r="AX10" s="108" t="s">
+      <c r="AX10" s="102" t="s">
         <v>16</v>
       </c>
-      <c r="AY10" s="109"/>
-      <c r="AZ10" s="109"/>
-      <c r="BA10" s="109"/>
-      <c r="BB10" s="131"/>
+      <c r="AY10" s="103"/>
+      <c r="AZ10" s="103"/>
+      <c r="BA10" s="103"/>
+      <c r="BB10" s="128"/>
       <c r="BD10" s="108" t="s">
         <v>17</v>
       </c>
@@ -4625,11 +4625,11 @@
       <c r="AT11" s="152"/>
       <c r="AU11" s="152"/>
       <c r="AW11" s="31"/>
-      <c r="AX11" s="110"/>
-      <c r="AY11" s="111"/>
-      <c r="AZ11" s="111"/>
-      <c r="BA11" s="111"/>
-      <c r="BB11" s="132"/>
+      <c r="AX11" s="104"/>
+      <c r="AY11" s="105"/>
+      <c r="AZ11" s="105"/>
+      <c r="BA11" s="105"/>
+      <c r="BB11" s="129"/>
       <c r="BD11" s="110"/>
       <c r="BE11" s="111"/>
       <c r="BF11" s="111"/>
@@ -4779,13 +4779,13 @@
       <c r="BG13" s="109"/>
       <c r="BH13" s="131"/>
       <c r="BI13" s="107"/>
-      <c r="BJ13" s="102" t="s">
+      <c r="BJ13" s="162" t="s">
         <v>24</v>
       </c>
-      <c r="BK13" s="103"/>
-      <c r="BL13" s="103"/>
-      <c r="BM13" s="103"/>
-      <c r="BN13" s="128"/>
+      <c r="BK13" s="163"/>
+      <c r="BL13" s="163"/>
+      <c r="BM13" s="163"/>
+      <c r="BN13" s="169"/>
       <c r="BO13" s="97"/>
       <c r="BP13" s="152"/>
       <c r="BQ13" s="152"/>
@@ -4853,11 +4853,11 @@
       <c r="BG14" s="111"/>
       <c r="BH14" s="132"/>
       <c r="BI14" s="107"/>
-      <c r="BJ14" s="104"/>
-      <c r="BK14" s="105"/>
-      <c r="BL14" s="105"/>
-      <c r="BM14" s="105"/>
-      <c r="BN14" s="129"/>
+      <c r="BJ14" s="164"/>
+      <c r="BK14" s="165"/>
+      <c r="BL14" s="165"/>
+      <c r="BM14" s="165"/>
+      <c r="BN14" s="170"/>
       <c r="BO14" s="97"/>
       <c r="BQ14" s="153"/>
       <c r="BR14" s="153"/>
@@ -5215,12 +5215,12 @@
       <c r="BI19" s="34"/>
       <c r="BJ19" s="34"/>
       <c r="BK19" s="34"/>
-      <c r="BL19" s="162">
+      <c r="BL19" s="166">
         <v>16800</v>
       </c>
-      <c r="BM19" s="162"/>
-      <c r="BN19" s="162"/>
-      <c r="BO19" s="165"/>
+      <c r="BM19" s="166"/>
+      <c r="BN19" s="166"/>
+      <c r="BO19" s="171"/>
       <c r="BP19" s="152" t="s">
         <v>34</v>
       </c>
@@ -5283,9 +5283,9 @@
       <c r="BI20" s="34"/>
       <c r="BJ20" s="34"/>
       <c r="BK20" s="34"/>
-      <c r="BL20" s="162"/>
-      <c r="BM20" s="162"/>
-      <c r="BN20" s="162"/>
+      <c r="BL20" s="166"/>
+      <c r="BM20" s="166"/>
+      <c r="BN20" s="166"/>
       <c r="BO20" s="148" t="s">
         <v>36</v>
       </c>
@@ -5365,12 +5365,12 @@
       <c r="BI21" s="156"/>
       <c r="BJ21" s="156"/>
       <c r="BK21" s="156"/>
-      <c r="BL21" s="163" t="s">
+      <c r="BL21" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="BM21" s="163"/>
+      <c r="BM21" s="167"/>
       <c r="BN21" s="159"/>
-      <c r="BO21" s="166"/>
+      <c r="BO21" s="172"/>
       <c r="BP21" s="152"/>
       <c r="BQ21" s="152"/>
       <c r="BR21" s="152"/>
@@ -5442,12 +5442,12 @@
       <c r="BI22" s="34"/>
       <c r="BJ22" s="34"/>
       <c r="BK22" s="34"/>
-      <c r="BL22" s="162">
+      <c r="BL22" s="166">
         <v>15500</v>
       </c>
-      <c r="BM22" s="162"/>
-      <c r="BN22" s="162"/>
-      <c r="BO22" s="165"/>
+      <c r="BM22" s="166"/>
+      <c r="BN22" s="166"/>
+      <c r="BO22" s="171"/>
       <c r="BP22" s="152"/>
       <c r="BQ22" s="152"/>
       <c r="BR22" s="152"/>
@@ -5503,9 +5503,9 @@
       <c r="BI23" s="34"/>
       <c r="BJ23" s="34"/>
       <c r="BK23" s="34"/>
-      <c r="BL23" s="162"/>
-      <c r="BM23" s="162"/>
-      <c r="BN23" s="162"/>
+      <c r="BL23" s="166"/>
+      <c r="BM23" s="166"/>
+      <c r="BN23" s="166"/>
       <c r="BO23" s="148" t="s">
         <v>36</v>
       </c>
@@ -5583,12 +5583,12 @@
       <c r="BI24" s="156"/>
       <c r="BJ24" s="156"/>
       <c r="BK24" s="156"/>
-      <c r="BL24" s="163" t="s">
+      <c r="BL24" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="BM24" s="163"/>
+      <c r="BM24" s="167"/>
       <c r="BN24" s="159"/>
-      <c r="BO24" s="166"/>
+      <c r="BO24" s="172"/>
       <c r="BP24" s="152"/>
       <c r="BQ24" s="152"/>
       <c r="BR24" s="152"/>
@@ -5659,12 +5659,12 @@
       <c r="BI25" s="34"/>
       <c r="BJ25" s="34"/>
       <c r="BK25" s="34"/>
-      <c r="BL25" s="162">
+      <c r="BL25" s="166">
         <v>14900</v>
       </c>
-      <c r="BM25" s="162"/>
-      <c r="BN25" s="162"/>
-      <c r="BO25" s="165"/>
+      <c r="BM25" s="166"/>
+      <c r="BN25" s="166"/>
+      <c r="BO25" s="171"/>
       <c r="BP25" s="152"/>
       <c r="BQ25" s="152"/>
       <c r="BR25" s="152"/>
@@ -5733,9 +5733,9 @@
       <c r="BI26" s="34"/>
       <c r="BJ26" s="34"/>
       <c r="BK26" s="34"/>
-      <c r="BL26" s="162"/>
-      <c r="BM26" s="162"/>
-      <c r="BN26" s="162"/>
+      <c r="BL26" s="166"/>
+      <c r="BM26" s="166"/>
+      <c r="BN26" s="166"/>
       <c r="BO26" s="148" t="s">
         <v>36</v>
       </c>
@@ -5805,12 +5805,12 @@
       <c r="BI27" s="156"/>
       <c r="BJ27" s="156"/>
       <c r="BK27" s="156"/>
-      <c r="BL27" s="163" t="s">
+      <c r="BL27" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="BM27" s="163"/>
+      <c r="BM27" s="167"/>
       <c r="BN27" s="159"/>
-      <c r="BO27" s="166"/>
+      <c r="BO27" s="172"/>
       <c r="BP27" s="152"/>
       <c r="BQ27" s="152"/>
       <c r="BR27" s="152"/>
@@ -5889,12 +5889,12 @@
       <c r="BI28" s="34"/>
       <c r="BJ28" s="34"/>
       <c r="BK28" s="34"/>
-      <c r="BL28" s="162">
+      <c r="BL28" s="166">
         <v>12800</v>
       </c>
-      <c r="BM28" s="162"/>
-      <c r="BN28" s="162"/>
-      <c r="BO28" s="165"/>
+      <c r="BM28" s="166"/>
+      <c r="BN28" s="166"/>
+      <c r="BO28" s="171"/>
       <c r="BP28" s="152"/>
       <c r="BQ28" s="152"/>
       <c r="BR28" s="152"/>
@@ -5956,9 +5956,9 @@
       <c r="BI29" s="34"/>
       <c r="BJ29" s="34"/>
       <c r="BK29" s="34"/>
-      <c r="BL29" s="162"/>
-      <c r="BM29" s="162"/>
-      <c r="BN29" s="162"/>
+      <c r="BL29" s="166"/>
+      <c r="BM29" s="166"/>
+      <c r="BN29" s="166"/>
       <c r="BO29" s="148" t="s">
         <v>36</v>
       </c>
@@ -6029,12 +6029,12 @@
       <c r="BI30" s="159"/>
       <c r="BJ30" s="159"/>
       <c r="BK30" s="159"/>
-      <c r="BL30" s="163" t="s">
+      <c r="BL30" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="BM30" s="163"/>
+      <c r="BM30" s="167"/>
       <c r="BN30" s="159"/>
-      <c r="BO30" s="166"/>
+      <c r="BO30" s="172"/>
       <c r="BP30" s="152"/>
       <c r="BQ30" s="152"/>
       <c r="BR30" s="152"/>
@@ -6106,12 +6106,12 @@
       <c r="BI31" s="34"/>
       <c r="BJ31" s="34"/>
       <c r="BK31" s="34"/>
-      <c r="BL31" s="162">
+      <c r="BL31" s="166">
         <v>11300</v>
       </c>
-      <c r="BM31" s="162"/>
-      <c r="BN31" s="162"/>
-      <c r="BO31" s="165"/>
+      <c r="BM31" s="166"/>
+      <c r="BN31" s="166"/>
+      <c r="BO31" s="171"/>
       <c r="BP31" s="152"/>
       <c r="BQ31" s="152"/>
       <c r="BR31" s="152"/>
@@ -6175,9 +6175,9 @@
       <c r="BI32" s="34"/>
       <c r="BJ32" s="34"/>
       <c r="BK32" s="34"/>
-      <c r="BL32" s="162"/>
-      <c r="BM32" s="162"/>
-      <c r="BN32" s="162"/>
+      <c r="BL32" s="166"/>
+      <c r="BM32" s="166"/>
+      <c r="BN32" s="166"/>
       <c r="BO32" s="148" t="s">
         <v>36</v>
       </c>
@@ -6261,12 +6261,12 @@
       <c r="BI33" s="159"/>
       <c r="BJ33" s="159"/>
       <c r="BK33" s="159"/>
-      <c r="BL33" s="163" t="s">
+      <c r="BL33" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="BM33" s="163"/>
+      <c r="BM33" s="167"/>
       <c r="BN33" s="159"/>
-      <c r="BO33" s="166"/>
+      <c r="BO33" s="172"/>
       <c r="BP33" s="152"/>
       <c r="BQ33" s="152"/>
       <c r="BR33" s="152"/>
@@ -6338,12 +6338,12 @@
       <c r="BI34" s="34"/>
       <c r="BJ34" s="34"/>
       <c r="BK34" s="34"/>
-      <c r="BL34" s="162">
+      <c r="BL34" s="166">
         <v>10200</v>
       </c>
-      <c r="BM34" s="162"/>
-      <c r="BN34" s="162"/>
-      <c r="BO34" s="165"/>
+      <c r="BM34" s="166"/>
+      <c r="BN34" s="166"/>
+      <c r="BO34" s="171"/>
       <c r="BP34" s="152"/>
       <c r="BQ34" s="152"/>
       <c r="BR34" s="152"/>
@@ -6395,9 +6395,9 @@
       <c r="BI35" s="34"/>
       <c r="BJ35" s="34"/>
       <c r="BK35" s="34"/>
-      <c r="BL35" s="162"/>
-      <c r="BM35" s="162"/>
-      <c r="BN35" s="162"/>
+      <c r="BL35" s="166"/>
+      <c r="BM35" s="166"/>
+      <c r="BN35" s="166"/>
       <c r="BO35" s="148" t="s">
         <v>36</v>
       </c>
@@ -6476,12 +6476,12 @@
       <c r="BI36" s="159"/>
       <c r="BJ36" s="159"/>
       <c r="BK36" s="159"/>
-      <c r="BL36" s="163" t="s">
+      <c r="BL36" s="167" t="s">
         <v>40</v>
       </c>
-      <c r="BM36" s="163"/>
+      <c r="BM36" s="167"/>
       <c r="BN36" s="159"/>
-      <c r="BO36" s="166"/>
+      <c r="BO36" s="172"/>
       <c r="BP36" s="152"/>
       <c r="BQ36" s="152"/>
       <c r="BR36" s="152"/>
@@ -7772,7 +7772,7 @@
       <c r="V65" s="97"/>
     </row>
     <row r="66" spans="4:22">
-      <c r="D66" s="167" t="s">
+      <c r="D66" s="173" t="s">
         <v>79</v>
       </c>
       <c r="E66" s="135"/>
@@ -7801,7 +7801,7 @@
       <c r="V66" s="134"/>
     </row>
     <row r="67" ht="17.55" spans="4:22">
-      <c r="D67" s="168"/>
+      <c r="D67" s="174"/>
       <c r="E67" s="137"/>
       <c r="F67" s="137"/>
       <c r="G67" s="137"/>
@@ -7822,258 +7822,258 @@
       <c r="V67" s="136"/>
     </row>
     <row r="72" spans="4:64">
-      <c r="D72" s="169" t="s">
+      <c r="D72" s="175" t="s">
         <v>91</v>
       </c>
-      <c r="E72" s="169"/>
-      <c r="F72" s="169"/>
-      <c r="G72" s="169"/>
-      <c r="H72" s="169"/>
-      <c r="I72" s="169"/>
-      <c r="J72" s="169"/>
-      <c r="K72" s="169"/>
-      <c r="L72" s="169"/>
-      <c r="M72" s="169"/>
-      <c r="N72" s="169"/>
-      <c r="O72" s="169"/>
-      <c r="P72" s="169"/>
-      <c r="Q72" s="169"/>
-      <c r="R72" s="169"/>
-      <c r="S72" s="169"/>
-      <c r="T72" s="169"/>
-      <c r="U72" s="169"/>
-      <c r="V72" s="169"/>
-      <c r="W72" s="169"/>
-      <c r="X72" s="169"/>
-      <c r="Y72" s="169"/>
-      <c r="Z72" s="169"/>
-      <c r="AA72" s="169"/>
-      <c r="AB72" s="169"/>
-      <c r="AC72" s="169"/>
-      <c r="AD72" s="169"/>
-      <c r="AE72" s="169"/>
-      <c r="AF72" s="169"/>
-      <c r="AG72" s="169"/>
-      <c r="AH72" s="169"/>
-      <c r="AI72" s="169"/>
-      <c r="AJ72" s="169"/>
-      <c r="AK72" s="169"/>
-      <c r="AL72" s="169"/>
-      <c r="AM72" s="169"/>
-      <c r="AN72" s="169"/>
-      <c r="AO72" s="169"/>
-      <c r="AP72" s="169"/>
-      <c r="AQ72" s="169"/>
-      <c r="AR72" s="169"/>
-      <c r="AS72" s="169"/>
-      <c r="AT72" s="169"/>
-      <c r="AU72" s="169"/>
-      <c r="AV72" s="169"/>
-      <c r="AW72" s="169"/>
-      <c r="AX72" s="169"/>
-      <c r="AY72" s="169"/>
-      <c r="AZ72" s="169"/>
-      <c r="BA72" s="169"/>
-      <c r="BB72" s="169"/>
-      <c r="BC72" s="169"/>
-      <c r="BD72" s="169"/>
-      <c r="BE72" s="169"/>
-      <c r="BF72" s="169"/>
-      <c r="BG72" s="169"/>
-      <c r="BH72" s="169"/>
-      <c r="BI72" s="169"/>
-      <c r="BJ72" s="169"/>
-      <c r="BK72" s="169"/>
-      <c r="BL72" s="169"/>
+      <c r="E72" s="175"/>
+      <c r="F72" s="175"/>
+      <c r="G72" s="175"/>
+      <c r="H72" s="175"/>
+      <c r="I72" s="175"/>
+      <c r="J72" s="175"/>
+      <c r="K72" s="175"/>
+      <c r="L72" s="175"/>
+      <c r="M72" s="175"/>
+      <c r="N72" s="175"/>
+      <c r="O72" s="175"/>
+      <c r="P72" s="175"/>
+      <c r="Q72" s="175"/>
+      <c r="R72" s="175"/>
+      <c r="S72" s="175"/>
+      <c r="T72" s="175"/>
+      <c r="U72" s="175"/>
+      <c r="V72" s="175"/>
+      <c r="W72" s="175"/>
+      <c r="X72" s="175"/>
+      <c r="Y72" s="175"/>
+      <c r="Z72" s="175"/>
+      <c r="AA72" s="175"/>
+      <c r="AB72" s="175"/>
+      <c r="AC72" s="175"/>
+      <c r="AD72" s="175"/>
+      <c r="AE72" s="175"/>
+      <c r="AF72" s="175"/>
+      <c r="AG72" s="175"/>
+      <c r="AH72" s="175"/>
+      <c r="AI72" s="175"/>
+      <c r="AJ72" s="175"/>
+      <c r="AK72" s="175"/>
+      <c r="AL72" s="175"/>
+      <c r="AM72" s="175"/>
+      <c r="AN72" s="175"/>
+      <c r="AO72" s="175"/>
+      <c r="AP72" s="175"/>
+      <c r="AQ72" s="175"/>
+      <c r="AR72" s="175"/>
+      <c r="AS72" s="175"/>
+      <c r="AT72" s="175"/>
+      <c r="AU72" s="175"/>
+      <c r="AV72" s="175"/>
+      <c r="AW72" s="175"/>
+      <c r="AX72" s="175"/>
+      <c r="AY72" s="175"/>
+      <c r="AZ72" s="175"/>
+      <c r="BA72" s="175"/>
+      <c r="BB72" s="175"/>
+      <c r="BC72" s="175"/>
+      <c r="BD72" s="175"/>
+      <c r="BE72" s="175"/>
+      <c r="BF72" s="175"/>
+      <c r="BG72" s="175"/>
+      <c r="BH72" s="175"/>
+      <c r="BI72" s="175"/>
+      <c r="BJ72" s="175"/>
+      <c r="BK72" s="175"/>
+      <c r="BL72" s="175"/>
     </row>
     <row r="73" spans="4:64">
-      <c r="D73" s="169"/>
-      <c r="E73" s="169"/>
-      <c r="F73" s="169"/>
-      <c r="G73" s="169"/>
-      <c r="H73" s="169"/>
-      <c r="I73" s="169"/>
-      <c r="J73" s="169"/>
-      <c r="K73" s="169"/>
-      <c r="L73" s="169"/>
-      <c r="M73" s="169"/>
-      <c r="N73" s="169"/>
-      <c r="O73" s="169"/>
-      <c r="P73" s="169"/>
-      <c r="Q73" s="169"/>
-      <c r="R73" s="169"/>
-      <c r="S73" s="169"/>
-      <c r="T73" s="169"/>
-      <c r="U73" s="169"/>
-      <c r="V73" s="169"/>
-      <c r="W73" s="169"/>
-      <c r="X73" s="169"/>
-      <c r="Y73" s="169"/>
-      <c r="Z73" s="169"/>
-      <c r="AA73" s="169"/>
-      <c r="AB73" s="169"/>
-      <c r="AC73" s="169"/>
-      <c r="AD73" s="169"/>
-      <c r="AE73" s="169"/>
-      <c r="AF73" s="169"/>
-      <c r="AG73" s="169"/>
-      <c r="AH73" s="169"/>
-      <c r="AI73" s="169"/>
-      <c r="AJ73" s="169"/>
-      <c r="AK73" s="169"/>
-      <c r="AL73" s="169"/>
-      <c r="AM73" s="169"/>
-      <c r="AN73" s="169"/>
-      <c r="AO73" s="169"/>
-      <c r="AP73" s="169"/>
-      <c r="AQ73" s="169"/>
-      <c r="AR73" s="169"/>
-      <c r="AS73" s="169"/>
-      <c r="AT73" s="169"/>
-      <c r="AU73" s="169"/>
-      <c r="AV73" s="169"/>
-      <c r="AW73" s="169"/>
-      <c r="AX73" s="169"/>
-      <c r="AY73" s="169"/>
-      <c r="AZ73" s="169"/>
-      <c r="BA73" s="169"/>
-      <c r="BB73" s="169"/>
-      <c r="BC73" s="169"/>
-      <c r="BD73" s="169"/>
-      <c r="BE73" s="169"/>
-      <c r="BF73" s="169"/>
-      <c r="BG73" s="169"/>
-      <c r="BH73" s="169"/>
-      <c r="BI73" s="169"/>
-      <c r="BJ73" s="169"/>
-      <c r="BK73" s="169"/>
-      <c r="BL73" s="169"/>
+      <c r="D73" s="175"/>
+      <c r="E73" s="175"/>
+      <c r="F73" s="175"/>
+      <c r="G73" s="175"/>
+      <c r="H73" s="175"/>
+      <c r="I73" s="175"/>
+      <c r="J73" s="175"/>
+      <c r="K73" s="175"/>
+      <c r="L73" s="175"/>
+      <c r="M73" s="175"/>
+      <c r="N73" s="175"/>
+      <c r="O73" s="175"/>
+      <c r="P73" s="175"/>
+      <c r="Q73" s="175"/>
+      <c r="R73" s="175"/>
+      <c r="S73" s="175"/>
+      <c r="T73" s="175"/>
+      <c r="U73" s="175"/>
+      <c r="V73" s="175"/>
+      <c r="W73" s="175"/>
+      <c r="X73" s="175"/>
+      <c r="Y73" s="175"/>
+      <c r="Z73" s="175"/>
+      <c r="AA73" s="175"/>
+      <c r="AB73" s="175"/>
+      <c r="AC73" s="175"/>
+      <c r="AD73" s="175"/>
+      <c r="AE73" s="175"/>
+      <c r="AF73" s="175"/>
+      <c r="AG73" s="175"/>
+      <c r="AH73" s="175"/>
+      <c r="AI73" s="175"/>
+      <c r="AJ73" s="175"/>
+      <c r="AK73" s="175"/>
+      <c r="AL73" s="175"/>
+      <c r="AM73" s="175"/>
+      <c r="AN73" s="175"/>
+      <c r="AO73" s="175"/>
+      <c r="AP73" s="175"/>
+      <c r="AQ73" s="175"/>
+      <c r="AR73" s="175"/>
+      <c r="AS73" s="175"/>
+      <c r="AT73" s="175"/>
+      <c r="AU73" s="175"/>
+      <c r="AV73" s="175"/>
+      <c r="AW73" s="175"/>
+      <c r="AX73" s="175"/>
+      <c r="AY73" s="175"/>
+      <c r="AZ73" s="175"/>
+      <c r="BA73" s="175"/>
+      <c r="BB73" s="175"/>
+      <c r="BC73" s="175"/>
+      <c r="BD73" s="175"/>
+      <c r="BE73" s="175"/>
+      <c r="BF73" s="175"/>
+      <c r="BG73" s="175"/>
+      <c r="BH73" s="175"/>
+      <c r="BI73" s="175"/>
+      <c r="BJ73" s="175"/>
+      <c r="BK73" s="175"/>
+      <c r="BL73" s="175"/>
     </row>
     <row r="74" spans="4:64">
-      <c r="D74" s="169"/>
-      <c r="E74" s="169"/>
-      <c r="F74" s="169"/>
-      <c r="G74" s="169"/>
-      <c r="H74" s="169"/>
-      <c r="I74" s="169"/>
-      <c r="J74" s="169"/>
-      <c r="K74" s="169"/>
-      <c r="L74" s="169"/>
-      <c r="M74" s="169"/>
-      <c r="N74" s="169"/>
-      <c r="O74" s="169"/>
-      <c r="P74" s="169"/>
-      <c r="Q74" s="169"/>
-      <c r="R74" s="169"/>
-      <c r="S74" s="169"/>
-      <c r="T74" s="169"/>
-      <c r="U74" s="169"/>
-      <c r="V74" s="169"/>
-      <c r="W74" s="169"/>
-      <c r="X74" s="169"/>
-      <c r="Y74" s="169"/>
-      <c r="Z74" s="169"/>
-      <c r="AA74" s="169"/>
-      <c r="AB74" s="169"/>
-      <c r="AC74" s="169"/>
-      <c r="AD74" s="169"/>
-      <c r="AE74" s="169"/>
-      <c r="AF74" s="169"/>
-      <c r="AG74" s="169"/>
-      <c r="AH74" s="169"/>
-      <c r="AI74" s="169"/>
-      <c r="AJ74" s="169"/>
-      <c r="AK74" s="169"/>
-      <c r="AL74" s="169"/>
-      <c r="AM74" s="169"/>
-      <c r="AN74" s="169"/>
-      <c r="AO74" s="169"/>
-      <c r="AP74" s="169"/>
-      <c r="AQ74" s="169"/>
-      <c r="AR74" s="169"/>
-      <c r="AS74" s="169"/>
-      <c r="AT74" s="169"/>
-      <c r="AU74" s="169"/>
-      <c r="AV74" s="169"/>
-      <c r="AW74" s="169"/>
-      <c r="AX74" s="169"/>
-      <c r="AY74" s="169"/>
-      <c r="AZ74" s="169"/>
-      <c r="BA74" s="169"/>
-      <c r="BB74" s="169"/>
-      <c r="BC74" s="169"/>
-      <c r="BD74" s="169"/>
-      <c r="BE74" s="169"/>
-      <c r="BF74" s="169"/>
-      <c r="BG74" s="169"/>
-      <c r="BH74" s="169"/>
-      <c r="BI74" s="169"/>
-      <c r="BJ74" s="169"/>
-      <c r="BK74" s="169"/>
-      <c r="BL74" s="169"/>
+      <c r="D74" s="175"/>
+      <c r="E74" s="175"/>
+      <c r="F74" s="175"/>
+      <c r="G74" s="175"/>
+      <c r="H74" s="175"/>
+      <c r="I74" s="175"/>
+      <c r="J74" s="175"/>
+      <c r="K74" s="175"/>
+      <c r="L74" s="175"/>
+      <c r="M74" s="175"/>
+      <c r="N74" s="175"/>
+      <c r="O74" s="175"/>
+      <c r="P74" s="175"/>
+      <c r="Q74" s="175"/>
+      <c r="R74" s="175"/>
+      <c r="S74" s="175"/>
+      <c r="T74" s="175"/>
+      <c r="U74" s="175"/>
+      <c r="V74" s="175"/>
+      <c r="W74" s="175"/>
+      <c r="X74" s="175"/>
+      <c r="Y74" s="175"/>
+      <c r="Z74" s="175"/>
+      <c r="AA74" s="175"/>
+      <c r="AB74" s="175"/>
+      <c r="AC74" s="175"/>
+      <c r="AD74" s="175"/>
+      <c r="AE74" s="175"/>
+      <c r="AF74" s="175"/>
+      <c r="AG74" s="175"/>
+      <c r="AH74" s="175"/>
+      <c r="AI74" s="175"/>
+      <c r="AJ74" s="175"/>
+      <c r="AK74" s="175"/>
+      <c r="AL74" s="175"/>
+      <c r="AM74" s="175"/>
+      <c r="AN74" s="175"/>
+      <c r="AO74" s="175"/>
+      <c r="AP74" s="175"/>
+      <c r="AQ74" s="175"/>
+      <c r="AR74" s="175"/>
+      <c r="AS74" s="175"/>
+      <c r="AT74" s="175"/>
+      <c r="AU74" s="175"/>
+      <c r="AV74" s="175"/>
+      <c r="AW74" s="175"/>
+      <c r="AX74" s="175"/>
+      <c r="AY74" s="175"/>
+      <c r="AZ74" s="175"/>
+      <c r="BA74" s="175"/>
+      <c r="BB74" s="175"/>
+      <c r="BC74" s="175"/>
+      <c r="BD74" s="175"/>
+      <c r="BE74" s="175"/>
+      <c r="BF74" s="175"/>
+      <c r="BG74" s="175"/>
+      <c r="BH74" s="175"/>
+      <c r="BI74" s="175"/>
+      <c r="BJ74" s="175"/>
+      <c r="BK74" s="175"/>
+      <c r="BL74" s="175"/>
     </row>
     <row r="75" spans="4:64">
-      <c r="D75" s="169"/>
-      <c r="E75" s="169"/>
-      <c r="F75" s="169"/>
-      <c r="G75" s="169"/>
-      <c r="H75" s="169"/>
-      <c r="I75" s="169"/>
-      <c r="J75" s="169"/>
-      <c r="K75" s="169"/>
-      <c r="L75" s="169"/>
-      <c r="M75" s="169"/>
-      <c r="N75" s="169"/>
-      <c r="O75" s="169"/>
-      <c r="P75" s="169"/>
-      <c r="Q75" s="169"/>
-      <c r="R75" s="169"/>
-      <c r="S75" s="169"/>
-      <c r="T75" s="169"/>
-      <c r="U75" s="169"/>
-      <c r="V75" s="169"/>
-      <c r="W75" s="169"/>
-      <c r="X75" s="169"/>
-      <c r="Y75" s="169"/>
-      <c r="Z75" s="169"/>
-      <c r="AA75" s="169"/>
-      <c r="AB75" s="169"/>
-      <c r="AC75" s="169"/>
-      <c r="AD75" s="169"/>
-      <c r="AE75" s="169"/>
-      <c r="AF75" s="169"/>
-      <c r="AG75" s="169"/>
-      <c r="AH75" s="169"/>
-      <c r="AI75" s="169"/>
-      <c r="AJ75" s="169"/>
-      <c r="AK75" s="169"/>
-      <c r="AL75" s="169"/>
-      <c r="AM75" s="169"/>
-      <c r="AN75" s="169"/>
-      <c r="AO75" s="169"/>
-      <c r="AP75" s="169"/>
-      <c r="AQ75" s="169"/>
-      <c r="AR75" s="169"/>
-      <c r="AS75" s="169"/>
-      <c r="AT75" s="169"/>
-      <c r="AU75" s="169"/>
-      <c r="AV75" s="169"/>
-      <c r="AW75" s="169"/>
-      <c r="AX75" s="169"/>
-      <c r="AY75" s="169"/>
-      <c r="AZ75" s="169"/>
-      <c r="BA75" s="169"/>
-      <c r="BB75" s="169"/>
-      <c r="BC75" s="169"/>
-      <c r="BD75" s="169"/>
-      <c r="BE75" s="169"/>
-      <c r="BF75" s="169"/>
-      <c r="BG75" s="169"/>
-      <c r="BH75" s="169"/>
-      <c r="BI75" s="169"/>
-      <c r="BJ75" s="169"/>
-      <c r="BK75" s="169"/>
-      <c r="BL75" s="169"/>
+      <c r="D75" s="175"/>
+      <c r="E75" s="175"/>
+      <c r="F75" s="175"/>
+      <c r="G75" s="175"/>
+      <c r="H75" s="175"/>
+      <c r="I75" s="175"/>
+      <c r="J75" s="175"/>
+      <c r="K75" s="175"/>
+      <c r="L75" s="175"/>
+      <c r="M75" s="175"/>
+      <c r="N75" s="175"/>
+      <c r="O75" s="175"/>
+      <c r="P75" s="175"/>
+      <c r="Q75" s="175"/>
+      <c r="R75" s="175"/>
+      <c r="S75" s="175"/>
+      <c r="T75" s="175"/>
+      <c r="U75" s="175"/>
+      <c r="V75" s="175"/>
+      <c r="W75" s="175"/>
+      <c r="X75" s="175"/>
+      <c r="Y75" s="175"/>
+      <c r="Z75" s="175"/>
+      <c r="AA75" s="175"/>
+      <c r="AB75" s="175"/>
+      <c r="AC75" s="175"/>
+      <c r="AD75" s="175"/>
+      <c r="AE75" s="175"/>
+      <c r="AF75" s="175"/>
+      <c r="AG75" s="175"/>
+      <c r="AH75" s="175"/>
+      <c r="AI75" s="175"/>
+      <c r="AJ75" s="175"/>
+      <c r="AK75" s="175"/>
+      <c r="AL75" s="175"/>
+      <c r="AM75" s="175"/>
+      <c r="AN75" s="175"/>
+      <c r="AO75" s="175"/>
+      <c r="AP75" s="175"/>
+      <c r="AQ75" s="175"/>
+      <c r="AR75" s="175"/>
+      <c r="AS75" s="175"/>
+      <c r="AT75" s="175"/>
+      <c r="AU75" s="175"/>
+      <c r="AV75" s="175"/>
+      <c r="AW75" s="175"/>
+      <c r="AX75" s="175"/>
+      <c r="AY75" s="175"/>
+      <c r="AZ75" s="175"/>
+      <c r="BA75" s="175"/>
+      <c r="BB75" s="175"/>
+      <c r="BC75" s="175"/>
+      <c r="BD75" s="175"/>
+      <c r="BE75" s="175"/>
+      <c r="BF75" s="175"/>
+      <c r="BG75" s="175"/>
+      <c r="BH75" s="175"/>
+      <c r="BI75" s="175"/>
+      <c r="BJ75" s="175"/>
+      <c r="BK75" s="175"/>
+      <c r="BL75" s="175"/>
     </row>
     <row r="77" ht="17.55" spans="4:67">
       <c r="D77" s="25" t="s">
@@ -8169,7 +8169,7 @@
       <c r="CF78" s="96"/>
     </row>
     <row r="79" spans="1:84">
-      <c r="A79" s="170"/>
+      <c r="A79" s="176"/>
       <c r="B79" s="25" t="s">
         <v>3</v>
       </c>
@@ -8265,13 +8265,9 @@
       <c r="L80" s="85"/>
       <c r="M80" s="34"/>
       <c r="N80" s="66"/>
-      <c r="O80" s="100" t="s">
-        <v>92</v>
-      </c>
+      <c r="O80" s="100"/>
       <c r="P80" s="100"/>
-      <c r="Q80" s="126" t="s">
-        <v>93</v>
-      </c>
+      <c r="Q80" s="126"/>
       <c r="R80" s="126"/>
       <c r="S80" s="126"/>
       <c r="T80" s="101"/>
@@ -8293,13 +8289,11 @@
       <c r="AH80" s="85"/>
       <c r="AI80" s="34"/>
       <c r="AJ80" s="66"/>
-      <c r="AK80" s="210" t="s">
-        <v>94</v>
-      </c>
-      <c r="AL80" s="211"/>
-      <c r="AM80" s="211"/>
-      <c r="AN80" s="211"/>
-      <c r="AO80" s="212"/>
+      <c r="AK80" s="158"/>
+      <c r="AL80" s="160"/>
+      <c r="AM80" s="160"/>
+      <c r="AN80" s="160"/>
+      <c r="AO80" s="161"/>
       <c r="AP80" s="101"/>
       <c r="AQ80" s="101"/>
       <c r="AR80" s="97"/>
@@ -8319,41 +8313,39 @@
       <c r="BC80" s="85"/>
       <c r="BD80" s="34"/>
       <c r="BE80" s="66"/>
-      <c r="BF80" s="210" t="s">
-        <v>94</v>
-      </c>
-      <c r="BG80" s="211"/>
-      <c r="BH80" s="211"/>
-      <c r="BI80" s="211"/>
-      <c r="BJ80" s="212"/>
+      <c r="BF80" s="158"/>
+      <c r="BG80" s="160"/>
+      <c r="BH80" s="160"/>
+      <c r="BI80" s="160"/>
+      <c r="BJ80" s="161"/>
       <c r="BK80" s="101"/>
       <c r="BL80" s="97"/>
       <c r="BO80" s="29"/>
-      <c r="BP80" s="227"/>
-      <c r="BQ80" s="230" t="s">
-        <v>95</v>
-      </c>
-      <c r="BR80" s="230"/>
-      <c r="BS80" s="230"/>
-      <c r="BT80" s="230"/>
-      <c r="BU80" s="230"/>
-      <c r="BV80" s="230"/>
-      <c r="BW80" s="230"/>
-      <c r="BX80" s="230"/>
-      <c r="BY80" s="230"/>
-      <c r="BZ80" s="230"/>
-      <c r="CA80" s="230"/>
-      <c r="CB80" s="230"/>
-      <c r="CC80" s="230"/>
-      <c r="CD80" s="230"/>
+      <c r="BP80" s="230"/>
+      <c r="BQ80" s="233" t="s">
+        <v>92</v>
+      </c>
+      <c r="BR80" s="233"/>
+      <c r="BS80" s="233"/>
+      <c r="BT80" s="233"/>
+      <c r="BU80" s="233"/>
+      <c r="BV80" s="233"/>
+      <c r="BW80" s="233"/>
+      <c r="BX80" s="233"/>
+      <c r="BY80" s="233"/>
+      <c r="BZ80" s="233"/>
+      <c r="CA80" s="233"/>
+      <c r="CB80" s="233"/>
+      <c r="CC80" s="233"/>
+      <c r="CD80" s="233"/>
       <c r="CE80" s="87"/>
       <c r="CF80" s="97"/>
     </row>
     <row r="81" spans="1:84">
-      <c r="A81" s="171" t="s">
-        <v>96</v>
-      </c>
-      <c r="B81" s="171"/>
+      <c r="A81" s="177" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" s="177"/>
       <c r="D81" s="29"/>
       <c r="E81" s="34"/>
       <c r="F81" s="66"/>
@@ -8412,33 +8404,33 @@
       <c r="BL81" s="97"/>
       <c r="BO81" s="29"/>
       <c r="BP81" s="87"/>
-      <c r="BQ81" s="230"/>
-      <c r="BR81" s="230"/>
-      <c r="BS81" s="230"/>
-      <c r="BT81" s="230"/>
-      <c r="BU81" s="230"/>
-      <c r="BV81" s="230"/>
-      <c r="BW81" s="230"/>
-      <c r="BX81" s="230"/>
-      <c r="BY81" s="230"/>
-      <c r="BZ81" s="230"/>
-      <c r="CA81" s="230"/>
-      <c r="CB81" s="230"/>
-      <c r="CC81" s="230"/>
-      <c r="CD81" s="230"/>
+      <c r="BQ81" s="233"/>
+      <c r="BR81" s="233"/>
+      <c r="BS81" s="233"/>
+      <c r="BT81" s="233"/>
+      <c r="BU81" s="233"/>
+      <c r="BV81" s="233"/>
+      <c r="BW81" s="233"/>
+      <c r="BX81" s="233"/>
+      <c r="BY81" s="233"/>
+      <c r="BZ81" s="233"/>
+      <c r="CA81" s="233"/>
+      <c r="CB81" s="233"/>
+      <c r="CC81" s="233"/>
+      <c r="CD81" s="233"/>
       <c r="CE81" s="87"/>
       <c r="CF81" s="97"/>
     </row>
     <row r="82" spans="1:84">
-      <c r="A82" s="171"/>
-      <c r="B82" s="171"/>
+      <c r="A82" s="177"/>
+      <c r="B82" s="177"/>
       <c r="D82" s="29"/>
-      <c r="E82" s="179" t="s">
-        <v>97</v>
-      </c>
-      <c r="F82" s="180"/>
-      <c r="G82" s="180"/>
-      <c r="H82" s="180"/>
+      <c r="E82" s="185" t="s">
+        <v>94</v>
+      </c>
+      <c r="F82" s="186"/>
+      <c r="G82" s="186"/>
+      <c r="H82" s="186"/>
       <c r="I82" s="34"/>
       <c r="J82" s="34"/>
       <c r="K82" s="34"/>
@@ -8454,12 +8446,12 @@
       <c r="U82" s="34"/>
       <c r="V82" s="97"/>
       <c r="Z82" s="29"/>
-      <c r="AA82" s="179" t="s">
-        <v>98</v>
-      </c>
-      <c r="AB82" s="180"/>
-      <c r="AC82" s="180"/>
-      <c r="AD82" s="180"/>
+      <c r="AA82" s="185" t="s">
+        <v>95</v>
+      </c>
+      <c r="AB82" s="186"/>
+      <c r="AC82" s="186"/>
+      <c r="AD82" s="186"/>
       <c r="AE82" s="34"/>
       <c r="AF82" s="34"/>
       <c r="AG82" s="34"/>
@@ -8475,13 +8467,13 @@
       <c r="AQ82" s="34"/>
       <c r="AR82" s="97"/>
       <c r="AU82" s="29"/>
-      <c r="AV82" s="179" t="s">
-        <v>99</v>
-      </c>
-      <c r="AW82" s="179"/>
-      <c r="AX82" s="179"/>
-      <c r="AY82" s="179"/>
-      <c r="AZ82" s="179"/>
+      <c r="AV82" s="185" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW82" s="185"/>
+      <c r="AX82" s="185"/>
+      <c r="AY82" s="185"/>
+      <c r="AZ82" s="185"/>
       <c r="BA82" s="34"/>
       <c r="BB82" s="34"/>
       <c r="BC82" s="34"/>
@@ -8495,27 +8487,27 @@
       <c r="BK82" s="34"/>
       <c r="BL82" s="97"/>
       <c r="BO82" s="29"/>
-      <c r="BP82" s="228"/>
-      <c r="BQ82" s="230"/>
-      <c r="BR82" s="230"/>
-      <c r="BS82" s="230"/>
-      <c r="BT82" s="230"/>
-      <c r="BU82" s="230"/>
-      <c r="BV82" s="230"/>
-      <c r="BW82" s="230"/>
-      <c r="BX82" s="230"/>
-      <c r="BY82" s="230"/>
-      <c r="BZ82" s="230"/>
-      <c r="CA82" s="230"/>
-      <c r="CB82" s="230"/>
-      <c r="CC82" s="230"/>
-      <c r="CD82" s="230"/>
+      <c r="BP82" s="231"/>
+      <c r="BQ82" s="233"/>
+      <c r="BR82" s="233"/>
+      <c r="BS82" s="233"/>
+      <c r="BT82" s="233"/>
+      <c r="BU82" s="233"/>
+      <c r="BV82" s="233"/>
+      <c r="BW82" s="233"/>
+      <c r="BX82" s="233"/>
+      <c r="BY82" s="233"/>
+      <c r="BZ82" s="233"/>
+      <c r="CA82" s="233"/>
+      <c r="CB82" s="233"/>
+      <c r="CC82" s="233"/>
+      <c r="CD82" s="233"/>
       <c r="CE82" s="87"/>
       <c r="CF82" s="97"/>
     </row>
     <row r="83" spans="1:84">
-      <c r="A83" s="171"/>
-      <c r="B83" s="171"/>
+      <c r="A83" s="177"/>
+      <c r="B83" s="177"/>
       <c r="D83" s="29"/>
       <c r="E83" s="34"/>
       <c r="F83" s="34"/>
@@ -8574,28 +8566,28 @@
       <c r="BL83" s="97"/>
       <c r="BO83" s="29"/>
       <c r="BP83" s="87"/>
-      <c r="BQ83" s="230"/>
-      <c r="BR83" s="230"/>
-      <c r="BS83" s="230"/>
-      <c r="BT83" s="230"/>
-      <c r="BU83" s="230"/>
-      <c r="BV83" s="230"/>
-      <c r="BW83" s="230"/>
-      <c r="BX83" s="230"/>
-      <c r="BY83" s="230"/>
-      <c r="BZ83" s="230"/>
-      <c r="CA83" s="230"/>
-      <c r="CB83" s="230"/>
-      <c r="CC83" s="230"/>
-      <c r="CD83" s="230"/>
+      <c r="BQ83" s="233"/>
+      <c r="BR83" s="233"/>
+      <c r="BS83" s="233"/>
+      <c r="BT83" s="233"/>
+      <c r="BU83" s="233"/>
+      <c r="BV83" s="233"/>
+      <c r="BW83" s="233"/>
+      <c r="BX83" s="233"/>
+      <c r="BY83" s="233"/>
+      <c r="BZ83" s="233"/>
+      <c r="CA83" s="233"/>
+      <c r="CB83" s="233"/>
+      <c r="CC83" s="233"/>
+      <c r="CD83" s="233"/>
       <c r="CE83" s="87"/>
       <c r="CF83" s="97"/>
     </row>
     <row r="84" ht="20.4" spans="1:84">
-      <c r="A84" s="171"/>
-      <c r="B84" s="171"/>
-      <c r="D84" s="172" t="s">
-        <v>100</v>
+      <c r="A84" s="177"/>
+      <c r="B84" s="177"/>
+      <c r="D84" s="178" t="s">
+        <v>97</v>
       </c>
       <c r="E84" s="107"/>
       <c r="F84" s="107"/>
@@ -8603,54 +8595,54 @@
       <c r="H84" s="107"/>
       <c r="I84" s="107"/>
       <c r="J84" s="107" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K84" s="107"/>
       <c r="L84" s="107"/>
       <c r="M84" s="107"/>
       <c r="N84" s="107" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="O84" s="107"/>
       <c r="P84" s="107"/>
       <c r="Q84" s="78"/>
       <c r="R84" s="107" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="S84" s="107"/>
       <c r="T84" s="107"/>
       <c r="U84" s="107"/>
       <c r="V84" s="98"/>
-      <c r="Z84" s="195"/>
+      <c r="Z84" s="201"/>
       <c r="AA84" s="55" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="AB84" s="56"/>
       <c r="AC84" s="56"/>
       <c r="AD84" s="56"/>
       <c r="AE84" s="56" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="AF84" s="56"/>
       <c r="AG84" s="56"/>
       <c r="AH84" s="56"/>
-      <c r="AI84" s="206" t="s">
-        <v>106</v>
-      </c>
-      <c r="AJ84" s="206"/>
-      <c r="AK84" s="206"/>
-      <c r="AL84" s="206"/>
-      <c r="AM84" s="206"/>
-      <c r="AN84" s="206" t="s">
-        <v>107</v>
-      </c>
-      <c r="AO84" s="206"/>
-      <c r="AP84" s="206"/>
-      <c r="AQ84" s="213"/>
+      <c r="AI84" s="212" t="s">
+        <v>103</v>
+      </c>
+      <c r="AJ84" s="212"/>
+      <c r="AK84" s="212"/>
+      <c r="AL84" s="212"/>
+      <c r="AM84" s="212"/>
+      <c r="AN84" s="212" t="s">
+        <v>104</v>
+      </c>
+      <c r="AO84" s="212"/>
+      <c r="AP84" s="212"/>
+      <c r="AQ84" s="216"/>
       <c r="AR84" s="98"/>
       <c r="AU84" s="29"/>
       <c r="AV84" s="93" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="AW84" s="93"/>
       <c r="AX84" s="93"/>
@@ -8666,30 +8658,30 @@
       <c r="BH84" s="93"/>
       <c r="BI84" s="93"/>
       <c r="BJ84" s="93"/>
-      <c r="BK84" s="224"/>
+      <c r="BK84" s="227"/>
       <c r="BL84" s="97"/>
       <c r="BO84" s="29"/>
-      <c r="BP84" s="229"/>
-      <c r="BQ84" s="230"/>
-      <c r="BR84" s="230"/>
-      <c r="BS84" s="230"/>
-      <c r="BT84" s="230"/>
-      <c r="BU84" s="230"/>
-      <c r="BV84" s="230"/>
-      <c r="BW84" s="230"/>
-      <c r="BX84" s="230"/>
-      <c r="BY84" s="230"/>
-      <c r="BZ84" s="230"/>
-      <c r="CA84" s="230"/>
-      <c r="CB84" s="230"/>
-      <c r="CC84" s="230"/>
-      <c r="CD84" s="230"/>
-      <c r="CE84" s="232"/>
+      <c r="BP84" s="232"/>
+      <c r="BQ84" s="233"/>
+      <c r="BR84" s="233"/>
+      <c r="BS84" s="233"/>
+      <c r="BT84" s="233"/>
+      <c r="BU84" s="233"/>
+      <c r="BV84" s="233"/>
+      <c r="BW84" s="233"/>
+      <c r="BX84" s="233"/>
+      <c r="BY84" s="233"/>
+      <c r="BZ84" s="233"/>
+      <c r="CA84" s="233"/>
+      <c r="CB84" s="233"/>
+      <c r="CC84" s="233"/>
+      <c r="CD84" s="233"/>
+      <c r="CE84" s="235"/>
       <c r="CF84" s="97"/>
     </row>
     <row r="85" ht="17.6" spans="1:84">
-      <c r="A85" s="171"/>
-      <c r="B85" s="171"/>
+      <c r="A85" s="177"/>
+      <c r="B85" s="177"/>
       <c r="D85" s="31">
         <v>500</v>
       </c>
@@ -8717,36 +8709,36 @@
       <c r="T85" s="107"/>
       <c r="U85" s="107"/>
       <c r="V85" s="98"/>
-      <c r="Z85" s="196"/>
-      <c r="AA85" s="197">
+      <c r="Z85" s="202"/>
+      <c r="AA85" s="203">
         <v>40000</v>
       </c>
-      <c r="AB85" s="198"/>
-      <c r="AC85" s="198"/>
-      <c r="AD85" s="198"/>
-      <c r="AE85" s="198">
+      <c r="AB85" s="204"/>
+      <c r="AC85" s="204"/>
+      <c r="AD85" s="204"/>
+      <c r="AE85" s="204">
         <v>10000</v>
       </c>
-      <c r="AF85" s="198"/>
-      <c r="AG85" s="198"/>
-      <c r="AH85" s="198"/>
-      <c r="AI85" s="207">
+      <c r="AF85" s="204"/>
+      <c r="AG85" s="204"/>
+      <c r="AH85" s="204"/>
+      <c r="AI85" s="213">
         <v>10000</v>
       </c>
-      <c r="AJ85" s="207"/>
-      <c r="AK85" s="207"/>
-      <c r="AL85" s="207"/>
-      <c r="AM85" s="207"/>
-      <c r="AN85" s="207">
+      <c r="AJ85" s="213"/>
+      <c r="AK85" s="213"/>
+      <c r="AL85" s="213"/>
+      <c r="AM85" s="213"/>
+      <c r="AN85" s="213">
         <v>20000</v>
       </c>
-      <c r="AO85" s="207"/>
-      <c r="AP85" s="207"/>
-      <c r="AQ85" s="214"/>
+      <c r="AO85" s="213"/>
+      <c r="AP85" s="213"/>
+      <c r="AQ85" s="217"/>
       <c r="AR85" s="98"/>
       <c r="AU85" s="29"/>
       <c r="AV85" s="16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AW85" s="16"/>
       <c r="AX85" s="16"/>
@@ -8756,42 +8748,42 @@
       </c>
       <c r="BA85" s="93"/>
       <c r="BB85" s="93"/>
-      <c r="BC85" s="222"/>
-      <c r="BD85" s="222"/>
+      <c r="BC85" s="225"/>
+      <c r="BD85" s="225"/>
       <c r="BE85" s="16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="BF85" s="16"/>
-      <c r="BG85" s="223">
+      <c r="BG85" s="226">
         <v>0.1</v>
       </c>
-      <c r="BH85" s="223"/>
-      <c r="BI85" s="223"/>
-      <c r="BJ85" s="223"/>
-      <c r="BK85" s="225"/>
+      <c r="BH85" s="226"/>
+      <c r="BI85" s="226"/>
+      <c r="BJ85" s="226"/>
+      <c r="BK85" s="228"/>
       <c r="BL85" s="97"/>
       <c r="BO85" s="29"/>
-      <c r="BP85" s="228"/>
-      <c r="BQ85" s="230"/>
-      <c r="BR85" s="230"/>
-      <c r="BS85" s="230"/>
-      <c r="BT85" s="230"/>
-      <c r="BU85" s="230"/>
-      <c r="BV85" s="230"/>
-      <c r="BW85" s="230"/>
-      <c r="BX85" s="230"/>
-      <c r="BY85" s="230"/>
-      <c r="BZ85" s="230"/>
-      <c r="CA85" s="230"/>
-      <c r="CB85" s="230"/>
-      <c r="CC85" s="230"/>
-      <c r="CD85" s="230"/>
-      <c r="CE85" s="233"/>
+      <c r="BP85" s="231"/>
+      <c r="BQ85" s="233"/>
+      <c r="BR85" s="233"/>
+      <c r="BS85" s="233"/>
+      <c r="BT85" s="233"/>
+      <c r="BU85" s="233"/>
+      <c r="BV85" s="233"/>
+      <c r="BW85" s="233"/>
+      <c r="BX85" s="233"/>
+      <c r="BY85" s="233"/>
+      <c r="BZ85" s="233"/>
+      <c r="CA85" s="233"/>
+      <c r="CB85" s="233"/>
+      <c r="CC85" s="233"/>
+      <c r="CD85" s="233"/>
+      <c r="CE85" s="236"/>
       <c r="CF85" s="97"/>
     </row>
     <row r="86" ht="17.6" spans="1:84">
-      <c r="A86" s="171"/>
-      <c r="B86" s="171"/>
+      <c r="A86" s="177"/>
+      <c r="B86" s="177"/>
       <c r="D86" s="29"/>
       <c r="E86" s="51"/>
       <c r="F86" s="51"/>
@@ -8840,36 +8832,36 @@
       </c>
       <c r="BA86" s="93"/>
       <c r="BB86" s="93"/>
-      <c r="BC86" s="222"/>
-      <c r="BD86" s="222"/>
+      <c r="BC86" s="225"/>
+      <c r="BD86" s="225"/>
       <c r="BE86" s="16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="BF86" s="16"/>
-      <c r="BG86" s="223">
+      <c r="BG86" s="226">
         <v>0.1</v>
       </c>
-      <c r="BH86" s="223"/>
-      <c r="BI86" s="223"/>
-      <c r="BJ86" s="223"/>
-      <c r="BK86" s="222"/>
+      <c r="BH86" s="226"/>
+      <c r="BI86" s="226"/>
+      <c r="BJ86" s="226"/>
+      <c r="BK86" s="225"/>
       <c r="BL86" s="97"/>
       <c r="BO86" s="29"/>
-      <c r="BP86" s="228"/>
-      <c r="BQ86" s="230"/>
-      <c r="BR86" s="230"/>
-      <c r="BS86" s="230"/>
-      <c r="BT86" s="230"/>
-      <c r="BU86" s="230"/>
-      <c r="BV86" s="230"/>
-      <c r="BW86" s="230"/>
-      <c r="BX86" s="230"/>
-      <c r="BY86" s="230"/>
-      <c r="BZ86" s="230"/>
-      <c r="CA86" s="230"/>
-      <c r="CB86" s="230"/>
-      <c r="CC86" s="230"/>
-      <c r="CD86" s="230"/>
+      <c r="BP86" s="231"/>
+      <c r="BQ86" s="233"/>
+      <c r="BR86" s="233"/>
+      <c r="BS86" s="233"/>
+      <c r="BT86" s="233"/>
+      <c r="BU86" s="233"/>
+      <c r="BV86" s="233"/>
+      <c r="BW86" s="233"/>
+      <c r="BX86" s="233"/>
+      <c r="BY86" s="233"/>
+      <c r="BZ86" s="233"/>
+      <c r="CA86" s="233"/>
+      <c r="CB86" s="233"/>
+      <c r="CC86" s="233"/>
+      <c r="CD86" s="233"/>
       <c r="CE86" s="87"/>
       <c r="CF86" s="97"/>
     </row>
@@ -8893,32 +8885,32 @@
       <c r="T87" s="34"/>
       <c r="U87" s="34"/>
       <c r="V87" s="97"/>
-      <c r="Z87" s="195"/>
+      <c r="Z87" s="201"/>
       <c r="AA87" s="55" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="AB87" s="56"/>
       <c r="AC87" s="56"/>
       <c r="AD87" s="56"/>
       <c r="AE87" s="56" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AF87" s="56"/>
       <c r="AG87" s="56"/>
       <c r="AH87" s="56"/>
-      <c r="AI87" s="206" t="s">
-        <v>113</v>
-      </c>
-      <c r="AJ87" s="206"/>
-      <c r="AK87" s="206"/>
-      <c r="AL87" s="206"/>
-      <c r="AM87" s="206"/>
-      <c r="AN87" s="206" t="s">
-        <v>114</v>
-      </c>
-      <c r="AO87" s="206"/>
-      <c r="AP87" s="206"/>
-      <c r="AQ87" s="213"/>
+      <c r="AI87" s="212" t="s">
+        <v>110</v>
+      </c>
+      <c r="AJ87" s="212"/>
+      <c r="AK87" s="212"/>
+      <c r="AL87" s="212"/>
+      <c r="AM87" s="212"/>
+      <c r="AN87" s="212" t="s">
+        <v>111</v>
+      </c>
+      <c r="AO87" s="212"/>
+      <c r="AP87" s="212"/>
+      <c r="AQ87" s="216"/>
       <c r="AR87" s="97"/>
       <c r="AU87" s="29"/>
       <c r="AV87" s="16"/>
@@ -8930,50 +8922,50 @@
       </c>
       <c r="BA87" s="93"/>
       <c r="BB87" s="93"/>
-      <c r="BC87" s="222"/>
-      <c r="BD87" s="222"/>
+      <c r="BC87" s="225"/>
+      <c r="BD87" s="225"/>
       <c r="BE87" s="16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="BF87" s="16"/>
-      <c r="BG87" s="223">
+      <c r="BG87" s="226">
         <v>0.1</v>
       </c>
-      <c r="BH87" s="223"/>
-      <c r="BI87" s="223"/>
-      <c r="BJ87" s="223"/>
-      <c r="BK87" s="225" t="s">
+      <c r="BH87" s="226"/>
+      <c r="BI87" s="226"/>
+      <c r="BJ87" s="226"/>
+      <c r="BK87" s="228" t="s">
         <v>36</v>
       </c>
       <c r="BL87" s="97"/>
       <c r="BO87" s="29"/>
-      <c r="BP87" s="228"/>
-      <c r="BQ87" s="230"/>
-      <c r="BR87" s="230"/>
-      <c r="BS87" s="230"/>
-      <c r="BT87" s="230"/>
-      <c r="BU87" s="230"/>
-      <c r="BV87" s="230"/>
-      <c r="BW87" s="230"/>
-      <c r="BX87" s="230"/>
-      <c r="BY87" s="230"/>
-      <c r="BZ87" s="230"/>
-      <c r="CA87" s="230"/>
-      <c r="CB87" s="230"/>
-      <c r="CC87" s="230"/>
-      <c r="CD87" s="230"/>
-      <c r="CE87" s="233"/>
+      <c r="BP87" s="231"/>
+      <c r="BQ87" s="233"/>
+      <c r="BR87" s="233"/>
+      <c r="BS87" s="233"/>
+      <c r="BT87" s="233"/>
+      <c r="BU87" s="233"/>
+      <c r="BV87" s="233"/>
+      <c r="BW87" s="233"/>
+      <c r="BX87" s="233"/>
+      <c r="BY87" s="233"/>
+      <c r="BZ87" s="233"/>
+      <c r="CA87" s="233"/>
+      <c r="CB87" s="233"/>
+      <c r="CC87" s="233"/>
+      <c r="CD87" s="233"/>
+      <c r="CE87" s="236"/>
       <c r="CF87" s="97"/>
     </row>
     <row r="88" ht="20.4" spans="4:84">
       <c r="D88" s="29"/>
-      <c r="E88" s="181" t="s">
-        <v>115</v>
-      </c>
-      <c r="F88" s="181"/>
-      <c r="G88" s="181"/>
-      <c r="H88" s="181"/>
-      <c r="I88" s="181"/>
+      <c r="E88" s="187" t="s">
+        <v>112</v>
+      </c>
+      <c r="F88" s="187"/>
+      <c r="G88" s="187"/>
+      <c r="H88" s="187"/>
+      <c r="I88" s="187"/>
       <c r="J88" s="52"/>
       <c r="K88" s="78"/>
       <c r="L88" s="34"/>
@@ -8988,30 +8980,30 @@
       <c r="U88" s="34"/>
       <c r="V88" s="97"/>
       <c r="Y88" s="34"/>
-      <c r="Z88" s="195"/>
-      <c r="AA88" s="199"/>
+      <c r="Z88" s="201"/>
+      <c r="AA88" s="205"/>
       <c r="AB88" s="27"/>
       <c r="AC88" s="27"/>
       <c r="AD88" s="27"/>
-      <c r="AE88" s="201">
+      <c r="AE88" s="207">
         <v>10000</v>
       </c>
-      <c r="AF88" s="201"/>
-      <c r="AG88" s="201"/>
-      <c r="AH88" s="201"/>
-      <c r="AI88" s="208">
+      <c r="AF88" s="207"/>
+      <c r="AG88" s="207"/>
+      <c r="AH88" s="207"/>
+      <c r="AI88" s="214">
         <v>10000</v>
       </c>
-      <c r="AJ88" s="208"/>
-      <c r="AK88" s="208"/>
-      <c r="AL88" s="208"/>
-      <c r="AM88" s="208"/>
-      <c r="AN88" s="208">
+      <c r="AJ88" s="214"/>
+      <c r="AK88" s="214"/>
+      <c r="AL88" s="214"/>
+      <c r="AM88" s="214"/>
+      <c r="AN88" s="214">
         <v>20000</v>
       </c>
-      <c r="AO88" s="208"/>
-      <c r="AP88" s="208"/>
-      <c r="AQ88" s="215"/>
+      <c r="AO88" s="214"/>
+      <c r="AP88" s="214"/>
+      <c r="AQ88" s="218"/>
       <c r="AR88" s="97"/>
       <c r="AU88" s="29"/>
       <c r="AV88" s="16"/>
@@ -9023,44 +9015,44 @@
       </c>
       <c r="BA88" s="93"/>
       <c r="BB88" s="93"/>
-      <c r="BC88" s="222"/>
+      <c r="BC88" s="225"/>
       <c r="BD88" s="93"/>
       <c r="BE88" s="16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="BF88" s="16"/>
-      <c r="BG88" s="223">
+      <c r="BG88" s="226">
         <v>0.1</v>
       </c>
-      <c r="BH88" s="223"/>
-      <c r="BI88" s="223"/>
-      <c r="BJ88" s="223"/>
-      <c r="BK88" s="224"/>
+      <c r="BH88" s="226"/>
+      <c r="BI88" s="226"/>
+      <c r="BJ88" s="226"/>
+      <c r="BK88" s="227"/>
       <c r="BL88" s="97"/>
       <c r="BO88" s="29"/>
-      <c r="BP88" s="228"/>
-      <c r="BQ88" s="230"/>
-      <c r="BR88" s="230"/>
-      <c r="BS88" s="230"/>
-      <c r="BT88" s="230"/>
-      <c r="BU88" s="230"/>
-      <c r="BV88" s="230"/>
-      <c r="BW88" s="230"/>
-      <c r="BX88" s="230"/>
-      <c r="BY88" s="230"/>
-      <c r="BZ88" s="230"/>
-      <c r="CA88" s="230"/>
-      <c r="CB88" s="230"/>
-      <c r="CC88" s="230"/>
-      <c r="CD88" s="230"/>
-      <c r="CE88" s="232"/>
+      <c r="BP88" s="231"/>
+      <c r="BQ88" s="233"/>
+      <c r="BR88" s="233"/>
+      <c r="BS88" s="233"/>
+      <c r="BT88" s="233"/>
+      <c r="BU88" s="233"/>
+      <c r="BV88" s="233"/>
+      <c r="BW88" s="233"/>
+      <c r="BX88" s="233"/>
+      <c r="BY88" s="233"/>
+      <c r="BZ88" s="233"/>
+      <c r="CA88" s="233"/>
+      <c r="CB88" s="233"/>
+      <c r="CC88" s="233"/>
+      <c r="CD88" s="233"/>
+      <c r="CE88" s="235"/>
       <c r="CF88" s="97"/>
     </row>
     <row r="89" ht="20.4" spans="1:84">
-      <c r="A89" s="173" t="s">
-        <v>116</v>
-      </c>
-      <c r="B89" s="174"/>
+      <c r="A89" s="179" t="s">
+        <v>113</v>
+      </c>
+      <c r="B89" s="180"/>
       <c r="D89" s="29"/>
       <c r="E89" s="107"/>
       <c r="F89" s="107"/>
@@ -9081,32 +9073,32 @@
       <c r="U89" s="34"/>
       <c r="V89" s="97"/>
       <c r="Y89" s="34"/>
-      <c r="Z89" s="196"/>
-      <c r="AA89" s="200">
+      <c r="Z89" s="202"/>
+      <c r="AA89" s="206">
         <v>40000</v>
       </c>
-      <c r="AB89" s="201"/>
-      <c r="AC89" s="201"/>
-      <c r="AD89" s="201"/>
+      <c r="AB89" s="207"/>
+      <c r="AC89" s="207"/>
+      <c r="AD89" s="207"/>
       <c r="AE89" s="107" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="AF89" s="107"/>
       <c r="AG89" s="107"/>
       <c r="AH89" s="107"/>
       <c r="AI89" s="26" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="AJ89" s="26"/>
       <c r="AK89" s="26"/>
       <c r="AL89" s="26"/>
       <c r="AM89" s="26"/>
       <c r="AN89" s="26" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="AO89" s="26"/>
       <c r="AP89" s="26"/>
-      <c r="AQ89" s="216"/>
+      <c r="AQ89" s="219"/>
       <c r="AR89" s="97"/>
       <c r="AU89" s="29"/>
       <c r="AV89" s="16"/>
@@ -9118,122 +9110,122 @@
       </c>
       <c r="BA89" s="93"/>
       <c r="BB89" s="93"/>
-      <c r="BC89" s="222"/>
+      <c r="BC89" s="225"/>
       <c r="BD89" s="93"/>
       <c r="BE89" s="16" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="BF89" s="16"/>
-      <c r="BG89" s="223">
+      <c r="BG89" s="226">
         <v>0.1</v>
       </c>
-      <c r="BH89" s="223"/>
-      <c r="BI89" s="223"/>
-      <c r="BJ89" s="223"/>
-      <c r="BK89" s="224"/>
+      <c r="BH89" s="226"/>
+      <c r="BI89" s="226"/>
+      <c r="BJ89" s="226"/>
+      <c r="BK89" s="227"/>
       <c r="BL89" s="97"/>
       <c r="BO89" s="29"/>
-      <c r="BP89" s="228"/>
-      <c r="BQ89" s="230"/>
-      <c r="BR89" s="230"/>
-      <c r="BS89" s="230"/>
-      <c r="BT89" s="230"/>
-      <c r="BU89" s="230"/>
-      <c r="BV89" s="230"/>
-      <c r="BW89" s="230"/>
-      <c r="BX89" s="230"/>
-      <c r="BY89" s="230"/>
-      <c r="BZ89" s="230"/>
-      <c r="CA89" s="230"/>
-      <c r="CB89" s="230"/>
-      <c r="CC89" s="230"/>
-      <c r="CD89" s="230"/>
-      <c r="CE89" s="232"/>
+      <c r="BP89" s="231"/>
+      <c r="BQ89" s="233"/>
+      <c r="BR89" s="233"/>
+      <c r="BS89" s="233"/>
+      <c r="BT89" s="233"/>
+      <c r="BU89" s="233"/>
+      <c r="BV89" s="233"/>
+      <c r="BW89" s="233"/>
+      <c r="BX89" s="233"/>
+      <c r="BY89" s="233"/>
+      <c r="BZ89" s="233"/>
+      <c r="CA89" s="233"/>
+      <c r="CB89" s="233"/>
+      <c r="CC89" s="233"/>
+      <c r="CD89" s="233"/>
+      <c r="CE89" s="235"/>
       <c r="CF89" s="97"/>
     </row>
     <row r="90" spans="1:84">
-      <c r="A90" s="174"/>
-      <c r="B90" s="174"/>
-      <c r="D90" s="175" t="s">
-        <v>120</v>
+      <c r="A90" s="180"/>
+      <c r="B90" s="180"/>
+      <c r="D90" s="181" t="s">
+        <v>117</v>
       </c>
       <c r="E90" s="27"/>
       <c r="F90" s="27"/>
       <c r="G90" s="148"/>
       <c r="H90" s="27" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="I90" s="27"/>
       <c r="J90" s="27"/>
       <c r="K90" s="27"/>
       <c r="L90" s="148"/>
       <c r="M90" s="27" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="N90" s="27"/>
       <c r="O90" s="27"/>
-      <c r="P90" s="188"/>
+      <c r="P90" s="194"/>
       <c r="Q90" s="66" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="R90" s="66"/>
       <c r="S90" s="66"/>
       <c r="T90" s="66"/>
       <c r="U90" s="66"/>
       <c r="V90" s="97"/>
-      <c r="Z90" s="196"/>
-      <c r="AA90" s="197"/>
-      <c r="AB90" s="198"/>
-      <c r="AC90" s="198"/>
-      <c r="AD90" s="198"/>
-      <c r="AE90" s="198">
+      <c r="Z90" s="202"/>
+      <c r="AA90" s="203"/>
+      <c r="AB90" s="204"/>
+      <c r="AC90" s="204"/>
+      <c r="AD90" s="204"/>
+      <c r="AE90" s="204">
         <v>10000</v>
       </c>
-      <c r="AF90" s="198"/>
-      <c r="AG90" s="198"/>
-      <c r="AH90" s="198"/>
-      <c r="AI90" s="209">
+      <c r="AF90" s="204"/>
+      <c r="AG90" s="204"/>
+      <c r="AH90" s="204"/>
+      <c r="AI90" s="215">
         <v>3000</v>
       </c>
-      <c r="AJ90" s="209"/>
-      <c r="AK90" s="209"/>
-      <c r="AL90" s="209"/>
-      <c r="AM90" s="209"/>
-      <c r="AN90" s="207">
+      <c r="AJ90" s="215"/>
+      <c r="AK90" s="215"/>
+      <c r="AL90" s="215"/>
+      <c r="AM90" s="215"/>
+      <c r="AN90" s="213">
         <v>4000</v>
       </c>
-      <c r="AO90" s="207"/>
-      <c r="AP90" s="207"/>
-      <c r="AQ90" s="214"/>
+      <c r="AO90" s="213"/>
+      <c r="AP90" s="213"/>
+      <c r="AQ90" s="217"/>
       <c r="AR90" s="97"/>
       <c r="AU90" s="29"/>
       <c r="BL90" s="97"/>
       <c r="BO90" s="29"/>
       <c r="BP90" s="46"/>
-      <c r="BQ90" s="230"/>
-      <c r="BR90" s="230"/>
-      <c r="BS90" s="230"/>
-      <c r="BT90" s="230"/>
-      <c r="BU90" s="230"/>
-      <c r="BV90" s="230"/>
-      <c r="BW90" s="230"/>
-      <c r="BX90" s="230"/>
-      <c r="BY90" s="230"/>
-      <c r="BZ90" s="230"/>
-      <c r="CA90" s="230"/>
-      <c r="CB90" s="230"/>
-      <c r="CC90" s="230"/>
-      <c r="CD90" s="230"/>
+      <c r="BQ90" s="233"/>
+      <c r="BR90" s="233"/>
+      <c r="BS90" s="233"/>
+      <c r="BT90" s="233"/>
+      <c r="BU90" s="233"/>
+      <c r="BV90" s="233"/>
+      <c r="BW90" s="233"/>
+      <c r="BX90" s="233"/>
+      <c r="BY90" s="233"/>
+      <c r="BZ90" s="233"/>
+      <c r="CA90" s="233"/>
+      <c r="CB90" s="233"/>
+      <c r="CC90" s="233"/>
+      <c r="CD90" s="233"/>
       <c r="CE90" s="46"/>
       <c r="CF90" s="97"/>
     </row>
     <row r="91" ht="20.4" spans="1:84">
-      <c r="A91" s="174"/>
-      <c r="B91" s="174"/>
+      <c r="A91" s="180"/>
+      <c r="B91" s="180"/>
       <c r="D91" s="29">
         <v>360</v>
       </c>
-      <c r="G91" s="165"/>
+      <c r="G91" s="171"/>
       <c r="H91" s="27">
         <v>60</v>
       </c>
@@ -9246,7 +9238,7 @@
       </c>
       <c r="N91" s="27"/>
       <c r="O91" s="27"/>
-      <c r="P91" s="188"/>
+      <c r="P91" s="194"/>
       <c r="Q91" s="66">
         <v>150</v>
       </c>
@@ -9256,12 +9248,12 @@
       <c r="U91" s="66"/>
       <c r="V91" s="97"/>
       <c r="Z91" s="31"/>
-      <c r="AA91" s="202"/>
-      <c r="AB91" s="202"/>
-      <c r="AC91" s="202"/>
-      <c r="AD91" s="202"/>
-      <c r="AE91" s="202"/>
-      <c r="AF91" s="202"/>
+      <c r="AA91" s="208"/>
+      <c r="AB91" s="208"/>
+      <c r="AC91" s="208"/>
+      <c r="AD91" s="208"/>
+      <c r="AE91" s="208"/>
+      <c r="AF91" s="208"/>
       <c r="AG91" s="42"/>
       <c r="AH91" s="41"/>
       <c r="AI91" s="41"/>
@@ -9275,58 +9267,58 @@
       <c r="AQ91" s="42"/>
       <c r="AR91" s="97"/>
       <c r="AU91" s="29"/>
-      <c r="AV91" s="219" t="s">
-        <v>124</v>
-      </c>
-      <c r="AW91" s="219"/>
-      <c r="AX91" s="219"/>
-      <c r="AY91" s="219"/>
-      <c r="AZ91" s="219"/>
-      <c r="BA91" s="219"/>
-      <c r="BB91" s="219"/>
-      <c r="BC91" s="219"/>
+      <c r="AV91" s="222" t="s">
+        <v>121</v>
+      </c>
+      <c r="AW91" s="222"/>
+      <c r="AX91" s="222"/>
+      <c r="AY91" s="222"/>
+      <c r="AZ91" s="222"/>
+      <c r="BA91" s="222"/>
+      <c r="BB91" s="222"/>
+      <c r="BC91" s="222"/>
       <c r="BD91" s="93" t="s">
         <v>38</v>
       </c>
       <c r="BE91" s="93"/>
       <c r="BF91" s="93"/>
       <c r="BG91" s="93" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="BH91" s="93"/>
       <c r="BI91" s="93"/>
       <c r="BJ91" s="93"/>
-      <c r="BK91" s="224"/>
+      <c r="BK91" s="227"/>
       <c r="BL91" s="97"/>
       <c r="BO91" s="29"/>
-      <c r="BP91" s="229"/>
-      <c r="BQ91" s="230"/>
-      <c r="BR91" s="230"/>
-      <c r="BS91" s="230"/>
-      <c r="BT91" s="230"/>
-      <c r="BU91" s="230"/>
-      <c r="BV91" s="230"/>
-      <c r="BW91" s="230"/>
-      <c r="BX91" s="230"/>
-      <c r="BY91" s="230"/>
-      <c r="BZ91" s="230"/>
-      <c r="CA91" s="230"/>
-      <c r="CB91" s="230"/>
-      <c r="CC91" s="230"/>
-      <c r="CD91" s="230"/>
-      <c r="CE91" s="232"/>
+      <c r="BP91" s="232"/>
+      <c r="BQ91" s="233"/>
+      <c r="BR91" s="233"/>
+      <c r="BS91" s="233"/>
+      <c r="BT91" s="233"/>
+      <c r="BU91" s="233"/>
+      <c r="BV91" s="233"/>
+      <c r="BW91" s="233"/>
+      <c r="BX91" s="233"/>
+      <c r="BY91" s="233"/>
+      <c r="BZ91" s="233"/>
+      <c r="CA91" s="233"/>
+      <c r="CB91" s="233"/>
+      <c r="CC91" s="233"/>
+      <c r="CD91" s="233"/>
+      <c r="CE91" s="235"/>
       <c r="CF91" s="97"/>
     </row>
     <row r="92" ht="17.6" spans="1:84">
-      <c r="A92" s="174"/>
-      <c r="B92" s="174"/>
+      <c r="A92" s="180"/>
+      <c r="B92" s="180"/>
       <c r="D92" s="29"/>
       <c r="E92" s="34"/>
       <c r="F92" s="34"/>
-      <c r="G92" s="165"/>
+      <c r="G92" s="171"/>
       <c r="H92" s="34"/>
       <c r="I92" s="34"/>
-      <c r="L92" s="165"/>
+      <c r="L92" s="171"/>
       <c r="O92" s="34"/>
       <c r="P92" s="97"/>
       <c r="Q92" s="34"/>
@@ -9335,7 +9327,7 @@
       <c r="T92" s="34"/>
       <c r="U92" s="34"/>
       <c r="V92" s="97"/>
-      <c r="Z92" s="172"/>
+      <c r="Z92" s="178"/>
       <c r="AA92" s="106"/>
       <c r="AB92" s="106"/>
       <c r="AC92" s="106"/>
@@ -9356,86 +9348,86 @@
       <c r="AR92" s="97"/>
       <c r="AU92" s="29"/>
       <c r="AV92" s="16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AW92" s="16"/>
       <c r="AX92" s="16"/>
       <c r="AY92" s="16"/>
-      <c r="AZ92" s="221" t="s">
-        <v>126</v>
-      </c>
-      <c r="BA92" s="221"/>
-      <c r="BB92" s="221"/>
-      <c r="BC92" s="222"/>
-      <c r="BD92" s="221">
+      <c r="AZ92" s="224" t="s">
+        <v>123</v>
+      </c>
+      <c r="BA92" s="224"/>
+      <c r="BB92" s="224"/>
+      <c r="BC92" s="225"/>
+      <c r="BD92" s="224">
         <v>18000</v>
       </c>
-      <c r="BE92" s="221"/>
-      <c r="BF92" s="221"/>
-      <c r="BG92" s="221">
+      <c r="BE92" s="224"/>
+      <c r="BF92" s="224"/>
+      <c r="BG92" s="224">
         <v>2000</v>
       </c>
-      <c r="BH92" s="221"/>
-      <c r="BI92" s="221"/>
-      <c r="BJ92" s="223"/>
-      <c r="BK92" s="225"/>
+      <c r="BH92" s="224"/>
+      <c r="BI92" s="224"/>
+      <c r="BJ92" s="226"/>
+      <c r="BK92" s="228"/>
       <c r="BL92" s="97"/>
       <c r="BO92" s="29"/>
-      <c r="BP92" s="228"/>
-      <c r="BQ92" s="230"/>
-      <c r="BR92" s="230"/>
-      <c r="BS92" s="230"/>
-      <c r="BT92" s="230"/>
-      <c r="BU92" s="230"/>
-      <c r="BV92" s="230"/>
-      <c r="BW92" s="230"/>
-      <c r="BX92" s="230"/>
-      <c r="BY92" s="230"/>
-      <c r="BZ92" s="230"/>
-      <c r="CA92" s="230"/>
-      <c r="CB92" s="230"/>
-      <c r="CC92" s="230"/>
-      <c r="CD92" s="230"/>
-      <c r="CE92" s="233"/>
+      <c r="BP92" s="231"/>
+      <c r="BQ92" s="233"/>
+      <c r="BR92" s="233"/>
+      <c r="BS92" s="233"/>
+      <c r="BT92" s="233"/>
+      <c r="BU92" s="233"/>
+      <c r="BV92" s="233"/>
+      <c r="BW92" s="233"/>
+      <c r="BX92" s="233"/>
+      <c r="BY92" s="233"/>
+      <c r="BZ92" s="233"/>
+      <c r="CA92" s="233"/>
+      <c r="CB92" s="233"/>
+      <c r="CC92" s="233"/>
+      <c r="CD92" s="233"/>
+      <c r="CE92" s="236"/>
       <c r="CF92" s="97"/>
     </row>
     <row r="93" ht="17.6" spans="1:85">
-      <c r="A93" s="174"/>
-      <c r="B93" s="174"/>
-      <c r="D93" s="175" t="s">
-        <v>127</v>
+      <c r="A93" s="180"/>
+      <c r="B93" s="180"/>
+      <c r="D93" s="181" t="s">
+        <v>124</v>
       </c>
       <c r="E93" s="27"/>
       <c r="F93" s="27"/>
       <c r="G93" s="148"/>
       <c r="H93" s="66" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="I93" s="27"/>
       <c r="J93" s="27"/>
       <c r="K93" s="27"/>
       <c r="L93" s="148"/>
       <c r="M93" s="66" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N93" s="27"/>
       <c r="O93" s="27"/>
-      <c r="P93" s="188"/>
+      <c r="P93" s="194"/>
       <c r="Q93" s="66" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="R93" s="66"/>
       <c r="S93" s="66"/>
       <c r="T93" s="66"/>
       <c r="U93" s="66"/>
       <c r="V93" s="97"/>
-      <c r="Z93" s="172"/>
-      <c r="AA93" s="179" t="s">
-        <v>128</v>
-      </c>
-      <c r="AB93" s="180"/>
-      <c r="AC93" s="180"/>
-      <c r="AD93" s="180"/>
+      <c r="Z93" s="178"/>
+      <c r="AA93" s="185" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB93" s="186"/>
+      <c r="AC93" s="186"/>
+      <c r="AD93" s="186"/>
       <c r="AE93" s="106"/>
       <c r="AF93" s="106"/>
       <c r="AG93" s="106"/>
@@ -9455,57 +9447,57 @@
       <c r="AW93" s="16"/>
       <c r="AX93" s="16"/>
       <c r="AY93" s="16"/>
-      <c r="AZ93" s="221" t="s">
-        <v>129</v>
-      </c>
-      <c r="BA93" s="221"/>
-      <c r="BB93" s="221"/>
-      <c r="BC93" s="222"/>
-      <c r="BD93" s="221">
+      <c r="AZ93" s="224" t="s">
+        <v>126</v>
+      </c>
+      <c r="BA93" s="224"/>
+      <c r="BB93" s="224"/>
+      <c r="BC93" s="225"/>
+      <c r="BD93" s="224">
         <v>30000</v>
       </c>
-      <c r="BE93" s="221"/>
-      <c r="BF93" s="221"/>
-      <c r="BG93" s="221">
+      <c r="BE93" s="224"/>
+      <c r="BF93" s="224"/>
+      <c r="BG93" s="224">
         <v>3000</v>
       </c>
-      <c r="BH93" s="221"/>
-      <c r="BI93" s="221"/>
-      <c r="BJ93" s="223"/>
-      <c r="BK93" s="222"/>
+      <c r="BH93" s="224"/>
+      <c r="BI93" s="224"/>
+      <c r="BJ93" s="226"/>
+      <c r="BK93" s="225"/>
       <c r="BL93" s="97"/>
       <c r="BM93" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BO93" s="29"/>
-      <c r="BP93" s="228"/>
-      <c r="BQ93" s="228"/>
-      <c r="BR93" s="228"/>
-      <c r="BS93" s="228"/>
-      <c r="BT93" s="231"/>
-      <c r="BU93" s="231"/>
-      <c r="BV93" s="231"/>
+      <c r="BP93" s="231"/>
+      <c r="BQ93" s="231"/>
+      <c r="BR93" s="231"/>
+      <c r="BS93" s="231"/>
+      <c r="BT93" s="234"/>
+      <c r="BU93" s="234"/>
+      <c r="BV93" s="234"/>
       <c r="BW93" s="87"/>
-      <c r="BX93" s="231"/>
-      <c r="BY93" s="231"/>
-      <c r="BZ93" s="231"/>
-      <c r="CA93" s="231"/>
-      <c r="CB93" s="231"/>
-      <c r="CC93" s="231"/>
-      <c r="CD93" s="234"/>
+      <c r="BX93" s="234"/>
+      <c r="BY93" s="234"/>
+      <c r="BZ93" s="234"/>
+      <c r="CA93" s="234"/>
+      <c r="CB93" s="234"/>
+      <c r="CC93" s="234"/>
+      <c r="CD93" s="237"/>
       <c r="CE93" s="87"/>
       <c r="CF93" s="97"/>
       <c r="CG93" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="94" ht="17.6" spans="1:84">
-      <c r="A94" s="174"/>
-      <c r="B94" s="174"/>
+      <c r="A94" s="180"/>
+      <c r="B94" s="180"/>
       <c r="D94" s="29">
         <v>130</v>
       </c>
-      <c r="G94" s="165"/>
+      <c r="G94" s="171"/>
       <c r="H94" s="27">
         <v>60</v>
       </c>
@@ -9518,7 +9510,7 @@
       </c>
       <c r="N94" s="27"/>
       <c r="O94" s="27"/>
-      <c r="P94" s="188"/>
+      <c r="P94" s="194"/>
       <c r="Q94" s="66"/>
       <c r="R94" s="66">
         <v>50</v>
@@ -9527,7 +9519,7 @@
       <c r="T94" s="66"/>
       <c r="U94" s="66"/>
       <c r="V94" s="97"/>
-      <c r="Z94" s="172"/>
+      <c r="Z94" s="178"/>
       <c r="AA94" s="106"/>
       <c r="AB94" s="106"/>
       <c r="AC94" s="106"/>
@@ -9551,52 +9543,52 @@
       <c r="AW94" s="16"/>
       <c r="AX94" s="16"/>
       <c r="AY94" s="16"/>
-      <c r="AZ94" s="221" t="s">
-        <v>131</v>
-      </c>
-      <c r="BA94" s="221"/>
-      <c r="BB94" s="221"/>
-      <c r="BC94" s="222"/>
-      <c r="BD94" s="221">
+      <c r="AZ94" s="224" t="s">
+        <v>128</v>
+      </c>
+      <c r="BA94" s="224"/>
+      <c r="BB94" s="224"/>
+      <c r="BC94" s="225"/>
+      <c r="BD94" s="224">
         <v>25000</v>
       </c>
-      <c r="BE94" s="221"/>
-      <c r="BF94" s="221"/>
-      <c r="BG94" s="221">
+      <c r="BE94" s="224"/>
+      <c r="BF94" s="224"/>
+      <c r="BG94" s="224">
         <v>5000</v>
       </c>
-      <c r="BH94" s="221"/>
-      <c r="BI94" s="221"/>
-      <c r="BJ94" s="223"/>
-      <c r="BK94" s="225" t="s">
+      <c r="BH94" s="224"/>
+      <c r="BI94" s="224"/>
+      <c r="BJ94" s="226"/>
+      <c r="BK94" s="228" t="s">
         <v>36</v>
       </c>
       <c r="BL94" s="97"/>
       <c r="BO94" s="29"/>
-      <c r="BP94" s="228"/>
-      <c r="BQ94" s="228"/>
-      <c r="BR94" s="228"/>
-      <c r="BS94" s="228"/>
-      <c r="BT94" s="231"/>
-      <c r="BU94" s="231"/>
-      <c r="BV94" s="231"/>
+      <c r="BP94" s="231"/>
+      <c r="BQ94" s="231"/>
+      <c r="BR94" s="231"/>
+      <c r="BS94" s="231"/>
+      <c r="BT94" s="234"/>
+      <c r="BU94" s="234"/>
+      <c r="BV94" s="234"/>
       <c r="BW94" s="87"/>
-      <c r="BX94" s="231"/>
-      <c r="BY94" s="231"/>
-      <c r="BZ94" s="231"/>
-      <c r="CA94" s="231"/>
-      <c r="CB94" s="231"/>
-      <c r="CC94" s="231"/>
-      <c r="CD94" s="234"/>
-      <c r="CE94" s="233"/>
+      <c r="BX94" s="234"/>
+      <c r="BY94" s="234"/>
+      <c r="BZ94" s="234"/>
+      <c r="CA94" s="234"/>
+      <c r="CB94" s="234"/>
+      <c r="CC94" s="234"/>
+      <c r="CD94" s="237"/>
+      <c r="CE94" s="236"/>
       <c r="CF94" s="97"/>
     </row>
     <row r="95" ht="20.4" spans="1:84">
-      <c r="A95" s="174"/>
-      <c r="B95" s="174"/>
+      <c r="A95" s="180"/>
+      <c r="B95" s="180"/>
       <c r="D95" s="29"/>
-      <c r="G95" s="165"/>
-      <c r="L95" s="165"/>
+      <c r="G95" s="171"/>
+      <c r="L95" s="171"/>
       <c r="P95" s="97"/>
       <c r="Q95" s="34"/>
       <c r="R95" s="34"/>
@@ -9604,101 +9596,101 @@
       <c r="T95" s="34"/>
       <c r="U95" s="34"/>
       <c r="V95" s="97"/>
-      <c r="Z95" s="172"/>
-      <c r="AA95" s="203" t="s">
-        <v>132</v>
-      </c>
-      <c r="AB95" s="204"/>
-      <c r="AC95" s="204"/>
-      <c r="AD95" s="204"/>
-      <c r="AE95" s="204"/>
-      <c r="AF95" s="204"/>
-      <c r="AG95" s="204"/>
-      <c r="AH95" s="204"/>
-      <c r="AI95" s="204"/>
-      <c r="AJ95" s="204"/>
-      <c r="AK95" s="204"/>
-      <c r="AL95" s="204"/>
-      <c r="AM95" s="204"/>
-      <c r="AN95" s="204"/>
-      <c r="AO95" s="204"/>
-      <c r="AP95" s="204"/>
-      <c r="AQ95" s="217"/>
+      <c r="Z95" s="178"/>
+      <c r="AA95" s="209" t="s">
+        <v>129</v>
+      </c>
+      <c r="AB95" s="210"/>
+      <c r="AC95" s="210"/>
+      <c r="AD95" s="210"/>
+      <c r="AE95" s="210"/>
+      <c r="AF95" s="210"/>
+      <c r="AG95" s="210"/>
+      <c r="AH95" s="210"/>
+      <c r="AI95" s="210"/>
+      <c r="AJ95" s="210"/>
+      <c r="AK95" s="210"/>
+      <c r="AL95" s="210"/>
+      <c r="AM95" s="210"/>
+      <c r="AN95" s="210"/>
+      <c r="AO95" s="210"/>
+      <c r="AP95" s="210"/>
+      <c r="AQ95" s="220"/>
       <c r="AR95" s="97"/>
       <c r="AU95" s="29"/>
       <c r="AV95" s="16"/>
       <c r="AW95" s="16"/>
       <c r="AX95" s="16"/>
       <c r="AY95" s="16"/>
-      <c r="AZ95" s="221" t="s">
-        <v>133</v>
-      </c>
-      <c r="BA95" s="221"/>
-      <c r="BB95" s="221"/>
-      <c r="BC95" s="222"/>
-      <c r="BD95" s="221">
+      <c r="AZ95" s="224" t="s">
+        <v>130</v>
+      </c>
+      <c r="BA95" s="224"/>
+      <c r="BB95" s="224"/>
+      <c r="BC95" s="225"/>
+      <c r="BD95" s="224">
         <v>3000</v>
       </c>
-      <c r="BE95" s="221"/>
-      <c r="BF95" s="221"/>
-      <c r="BG95" s="221">
+      <c r="BE95" s="224"/>
+      <c r="BF95" s="224"/>
+      <c r="BG95" s="224">
         <v>1000</v>
       </c>
-      <c r="BH95" s="221"/>
-      <c r="BI95" s="221"/>
-      <c r="BJ95" s="223"/>
-      <c r="BK95" s="224"/>
+      <c r="BH95" s="224"/>
+      <c r="BI95" s="224"/>
+      <c r="BJ95" s="226"/>
+      <c r="BK95" s="227"/>
       <c r="BL95" s="97"/>
       <c r="BO95" s="29"/>
-      <c r="BP95" s="228"/>
-      <c r="BQ95" s="228"/>
-      <c r="BR95" s="228"/>
-      <c r="BS95" s="228"/>
-      <c r="BT95" s="231"/>
-      <c r="BU95" s="231"/>
-      <c r="BV95" s="231"/>
+      <c r="BP95" s="231"/>
+      <c r="BQ95" s="231"/>
+      <c r="BR95" s="231"/>
+      <c r="BS95" s="231"/>
+      <c r="BT95" s="234"/>
+      <c r="BU95" s="234"/>
+      <c r="BV95" s="234"/>
       <c r="BW95" s="87"/>
-      <c r="BX95" s="231"/>
-      <c r="BY95" s="231"/>
-      <c r="BZ95" s="231"/>
-      <c r="CA95" s="231"/>
-      <c r="CB95" s="231"/>
-      <c r="CC95" s="231"/>
-      <c r="CD95" s="234"/>
-      <c r="CE95" s="232"/>
+      <c r="BX95" s="234"/>
+      <c r="BY95" s="234"/>
+      <c r="BZ95" s="234"/>
+      <c r="CA95" s="234"/>
+      <c r="CB95" s="234"/>
+      <c r="CC95" s="234"/>
+      <c r="CD95" s="237"/>
+      <c r="CE95" s="235"/>
       <c r="CF95" s="97"/>
     </row>
     <row r="96" ht="17.6" spans="1:84">
-      <c r="A96" s="174"/>
-      <c r="B96" s="174"/>
-      <c r="D96" s="175" t="s">
-        <v>134</v>
+      <c r="A96" s="180"/>
+      <c r="B96" s="180"/>
+      <c r="D96" s="181" t="s">
+        <v>131</v>
       </c>
       <c r="E96" s="27"/>
       <c r="F96" s="27"/>
       <c r="G96" s="148"/>
       <c r="H96" s="66" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="I96" s="27"/>
       <c r="J96" s="27"/>
       <c r="K96" s="27"/>
       <c r="L96" s="148"/>
       <c r="M96" s="66" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="N96" s="27"/>
       <c r="O96" s="27"/>
-      <c r="P96" s="188"/>
+      <c r="P96" s="194"/>
       <c r="Q96" s="66" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="R96" s="66"/>
       <c r="S96" s="66"/>
       <c r="T96" s="66"/>
       <c r="U96" s="66"/>
       <c r="V96" s="97"/>
-      <c r="Z96" s="172"/>
+      <c r="Z96" s="178"/>
       <c r="AA96" s="106"/>
       <c r="AB96" s="106"/>
       <c r="AC96" s="106"/>
@@ -9722,51 +9714,51 @@
       <c r="AW96" s="16"/>
       <c r="AX96" s="16"/>
       <c r="AY96" s="16"/>
-      <c r="AZ96" s="221" t="s">
-        <v>135</v>
-      </c>
-      <c r="BA96" s="221"/>
-      <c r="BB96" s="221"/>
-      <c r="BC96" s="222"/>
-      <c r="BD96" s="221">
+      <c r="AZ96" s="224" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA96" s="224"/>
+      <c r="BB96" s="224"/>
+      <c r="BC96" s="225"/>
+      <c r="BD96" s="224">
         <v>6000</v>
       </c>
-      <c r="BE96" s="221"/>
-      <c r="BF96" s="221"/>
-      <c r="BG96" s="221">
+      <c r="BE96" s="224"/>
+      <c r="BF96" s="224"/>
+      <c r="BG96" s="224">
         <v>1000</v>
       </c>
-      <c r="BH96" s="221"/>
-      <c r="BI96" s="221"/>
-      <c r="BJ96" s="223"/>
-      <c r="BK96" s="222"/>
+      <c r="BH96" s="224"/>
+      <c r="BI96" s="224"/>
+      <c r="BJ96" s="226"/>
+      <c r="BK96" s="225"/>
       <c r="BL96" s="97"/>
       <c r="BO96" s="29"/>
-      <c r="BP96" s="228"/>
-      <c r="BQ96" s="228"/>
-      <c r="BR96" s="228"/>
-      <c r="BS96" s="228"/>
-      <c r="BT96" s="231"/>
-      <c r="BU96" s="231"/>
-      <c r="BV96" s="231"/>
+      <c r="BP96" s="231"/>
+      <c r="BQ96" s="231"/>
+      <c r="BR96" s="231"/>
+      <c r="BS96" s="231"/>
+      <c r="BT96" s="234"/>
+      <c r="BU96" s="234"/>
+      <c r="BV96" s="234"/>
       <c r="BW96" s="87"/>
-      <c r="BX96" s="231"/>
-      <c r="BY96" s="231"/>
-      <c r="BZ96" s="231"/>
-      <c r="CA96" s="231"/>
-      <c r="CB96" s="231"/>
-      <c r="CC96" s="231"/>
-      <c r="CD96" s="234"/>
+      <c r="BX96" s="234"/>
+      <c r="BY96" s="234"/>
+      <c r="BZ96" s="234"/>
+      <c r="CA96" s="234"/>
+      <c r="CB96" s="234"/>
+      <c r="CC96" s="234"/>
+      <c r="CD96" s="237"/>
       <c r="CE96" s="87"/>
       <c r="CF96" s="97"/>
     </row>
     <row r="97" spans="1:84">
-      <c r="A97" s="174"/>
-      <c r="B97" s="174"/>
+      <c r="A97" s="180"/>
+      <c r="B97" s="180"/>
       <c r="D97" s="29">
         <v>260</v>
       </c>
-      <c r="G97" s="165"/>
+      <c r="G97" s="171"/>
       <c r="H97" s="27">
         <v>120</v>
       </c>
@@ -9779,7 +9771,7 @@
       </c>
       <c r="N97" s="27"/>
       <c r="O97" s="27"/>
-      <c r="P97" s="188"/>
+      <c r="P97" s="194"/>
       <c r="Q97" s="66"/>
       <c r="R97" s="66">
         <v>100</v>
@@ -9788,26 +9780,26 @@
       <c r="T97" s="66"/>
       <c r="U97" s="66"/>
       <c r="V97" s="97"/>
-      <c r="Z97" s="172"/>
-      <c r="AA97" s="203" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB97" s="204"/>
-      <c r="AC97" s="204"/>
-      <c r="AD97" s="204"/>
-      <c r="AE97" s="204"/>
-      <c r="AF97" s="204"/>
-      <c r="AG97" s="204"/>
-      <c r="AH97" s="204"/>
-      <c r="AI97" s="204"/>
-      <c r="AJ97" s="204"/>
-      <c r="AK97" s="204"/>
-      <c r="AL97" s="204"/>
-      <c r="AM97" s="204"/>
-      <c r="AN97" s="204"/>
-      <c r="AO97" s="204"/>
-      <c r="AP97" s="204"/>
-      <c r="AQ97" s="217"/>
+      <c r="Z97" s="178"/>
+      <c r="AA97" s="209" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB97" s="210"/>
+      <c r="AC97" s="210"/>
+      <c r="AD97" s="210"/>
+      <c r="AE97" s="210"/>
+      <c r="AF97" s="210"/>
+      <c r="AG97" s="210"/>
+      <c r="AH97" s="210"/>
+      <c r="AI97" s="210"/>
+      <c r="AJ97" s="210"/>
+      <c r="AK97" s="210"/>
+      <c r="AL97" s="210"/>
+      <c r="AM97" s="210"/>
+      <c r="AN97" s="210"/>
+      <c r="AO97" s="210"/>
+      <c r="AP97" s="210"/>
+      <c r="AQ97" s="220"/>
       <c r="AR97" s="97"/>
       <c r="AU97" s="29"/>
       <c r="BL97" s="97"/>
@@ -9832,8 +9824,8 @@
     </row>
     <row r="98" ht="20.4" spans="4:84">
       <c r="D98" s="29"/>
-      <c r="G98" s="165"/>
-      <c r="L98" s="165"/>
+      <c r="G98" s="171"/>
+      <c r="L98" s="171"/>
       <c r="P98" s="97"/>
       <c r="Q98" s="34"/>
       <c r="R98" s="34"/>
@@ -9841,7 +9833,7 @@
       <c r="T98" s="34"/>
       <c r="U98" s="34"/>
       <c r="V98" s="97"/>
-      <c r="Z98" s="172"/>
+      <c r="Z98" s="178"/>
       <c r="AA98" s="106"/>
       <c r="AB98" s="106"/>
       <c r="AC98" s="106"/>
@@ -9861,128 +9853,128 @@
       <c r="AQ98" s="106"/>
       <c r="AR98" s="97"/>
       <c r="AU98" s="29"/>
-      <c r="AV98" s="219" t="s">
-        <v>137</v>
-      </c>
-      <c r="AW98" s="219"/>
-      <c r="AX98" s="219"/>
-      <c r="AY98" s="219"/>
-      <c r="AZ98" s="219"/>
-      <c r="BA98" s="219"/>
-      <c r="BB98" s="219"/>
-      <c r="BC98" s="219"/>
-      <c r="BD98" s="219"/>
+      <c r="AV98" s="222" t="s">
+        <v>134</v>
+      </c>
+      <c r="AW98" s="222"/>
+      <c r="AX98" s="222"/>
+      <c r="AY98" s="222"/>
+      <c r="AZ98" s="222"/>
+      <c r="BA98" s="222"/>
+      <c r="BB98" s="222"/>
+      <c r="BC98" s="222"/>
+      <c r="BD98" s="222"/>
       <c r="BE98" s="93"/>
       <c r="BF98" s="93"/>
       <c r="BG98" s="93"/>
       <c r="BH98" s="93"/>
       <c r="BI98" s="93"/>
       <c r="BJ98" s="93"/>
-      <c r="BK98" s="224"/>
+      <c r="BK98" s="227"/>
       <c r="BL98" s="97"/>
       <c r="BO98" s="29"/>
-      <c r="BP98" s="229"/>
-      <c r="BQ98" s="229"/>
-      <c r="BR98" s="229"/>
-      <c r="BS98" s="229"/>
-      <c r="BT98" s="229"/>
-      <c r="BU98" s="229"/>
-      <c r="BV98" s="229"/>
-      <c r="BW98" s="229"/>
-      <c r="BX98" s="229"/>
-      <c r="BY98" s="229"/>
-      <c r="BZ98" s="229"/>
-      <c r="CA98" s="229"/>
-      <c r="CB98" s="229"/>
-      <c r="CC98" s="229"/>
-      <c r="CD98" s="229"/>
-      <c r="CE98" s="232"/>
+      <c r="BP98" s="232"/>
+      <c r="BQ98" s="232"/>
+      <c r="BR98" s="232"/>
+      <c r="BS98" s="232"/>
+      <c r="BT98" s="232"/>
+      <c r="BU98" s="232"/>
+      <c r="BV98" s="232"/>
+      <c r="BW98" s="232"/>
+      <c r="BX98" s="232"/>
+      <c r="BY98" s="232"/>
+      <c r="BZ98" s="232"/>
+      <c r="CA98" s="232"/>
+      <c r="CB98" s="232"/>
+      <c r="CC98" s="232"/>
+      <c r="CD98" s="232"/>
+      <c r="CE98" s="235"/>
       <c r="CF98" s="97"/>
     </row>
     <row r="99" ht="18.35" spans="4:84">
       <c r="D99" s="29"/>
-      <c r="E99" s="182"/>
-      <c r="F99" s="182"/>
-      <c r="G99" s="182"/>
-      <c r="H99" s="182"/>
-      <c r="I99" s="182"/>
-      <c r="J99" s="182"/>
-      <c r="K99" s="184"/>
-      <c r="L99" s="185"/>
-      <c r="M99" s="185"/>
-      <c r="N99" s="185"/>
-      <c r="O99" s="185"/>
-      <c r="P99" s="185"/>
-      <c r="Q99" s="185"/>
-      <c r="R99" s="185"/>
-      <c r="S99" s="185"/>
-      <c r="T99" s="185"/>
-      <c r="U99" s="185"/>
+      <c r="E99" s="188"/>
+      <c r="F99" s="188"/>
+      <c r="G99" s="188"/>
+      <c r="H99" s="188"/>
+      <c r="I99" s="188"/>
+      <c r="J99" s="188"/>
+      <c r="K99" s="190"/>
+      <c r="L99" s="191"/>
+      <c r="M99" s="191"/>
+      <c r="N99" s="191"/>
+      <c r="O99" s="191"/>
+      <c r="P99" s="191"/>
+      <c r="Q99" s="191"/>
+      <c r="R99" s="191"/>
+      <c r="S99" s="191"/>
+      <c r="T99" s="191"/>
+      <c r="U99" s="191"/>
       <c r="V99" s="97"/>
-      <c r="Z99" s="172"/>
-      <c r="AA99" s="203" t="s">
-        <v>138</v>
-      </c>
-      <c r="AB99" s="204"/>
-      <c r="AC99" s="204"/>
-      <c r="AD99" s="204"/>
-      <c r="AE99" s="204"/>
-      <c r="AF99" s="204"/>
-      <c r="AG99" s="204"/>
-      <c r="AH99" s="204"/>
-      <c r="AI99" s="204"/>
-      <c r="AJ99" s="204"/>
-      <c r="AK99" s="204"/>
-      <c r="AL99" s="204"/>
-      <c r="AM99" s="204"/>
-      <c r="AN99" s="204"/>
-      <c r="AO99" s="204"/>
-      <c r="AP99" s="204"/>
-      <c r="AQ99" s="217"/>
+      <c r="Z99" s="178"/>
+      <c r="AA99" s="209" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB99" s="210"/>
+      <c r="AC99" s="210"/>
+      <c r="AD99" s="210"/>
+      <c r="AE99" s="210"/>
+      <c r="AF99" s="210"/>
+      <c r="AG99" s="210"/>
+      <c r="AH99" s="210"/>
+      <c r="AI99" s="210"/>
+      <c r="AJ99" s="210"/>
+      <c r="AK99" s="210"/>
+      <c r="AL99" s="210"/>
+      <c r="AM99" s="210"/>
+      <c r="AN99" s="210"/>
+      <c r="AO99" s="210"/>
+      <c r="AP99" s="210"/>
+      <c r="AQ99" s="220"/>
       <c r="AR99" s="97"/>
       <c r="AU99" s="29"/>
       <c r="AV99" s="16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AW99" s="16"/>
       <c r="AX99" s="16"/>
       <c r="AY99" s="16"/>
-      <c r="AZ99" s="221" t="s">
-        <v>139</v>
-      </c>
-      <c r="BA99" s="221"/>
-      <c r="BB99" s="221"/>
-      <c r="BC99" s="222"/>
-      <c r="BD99" s="221">
+      <c r="AZ99" s="224" t="s">
+        <v>136</v>
+      </c>
+      <c r="BA99" s="224"/>
+      <c r="BB99" s="224"/>
+      <c r="BC99" s="225"/>
+      <c r="BD99" s="224">
         <v>18000</v>
       </c>
-      <c r="BE99" s="221"/>
-      <c r="BF99" s="221"/>
-      <c r="BG99" s="221">
+      <c r="BE99" s="224"/>
+      <c r="BF99" s="224"/>
+      <c r="BG99" s="224">
         <v>2000</v>
       </c>
-      <c r="BH99" s="221"/>
-      <c r="BI99" s="221"/>
-      <c r="BJ99" s="223"/>
-      <c r="BK99" s="225"/>
+      <c r="BH99" s="224"/>
+      <c r="BI99" s="224"/>
+      <c r="BJ99" s="226"/>
+      <c r="BK99" s="228"/>
       <c r="BL99" s="97"/>
       <c r="BO99" s="29"/>
-      <c r="BP99" s="228"/>
-      <c r="BQ99" s="228"/>
-      <c r="BR99" s="228"/>
-      <c r="BS99" s="228"/>
-      <c r="BT99" s="231"/>
-      <c r="BU99" s="231"/>
-      <c r="BV99" s="231"/>
+      <c r="BP99" s="231"/>
+      <c r="BQ99" s="231"/>
+      <c r="BR99" s="231"/>
+      <c r="BS99" s="231"/>
+      <c r="BT99" s="234"/>
+      <c r="BU99" s="234"/>
+      <c r="BV99" s="234"/>
       <c r="BW99" s="87"/>
-      <c r="BX99" s="231"/>
-      <c r="BY99" s="231"/>
-      <c r="BZ99" s="231"/>
-      <c r="CA99" s="231"/>
-      <c r="CB99" s="231"/>
-      <c r="CC99" s="231"/>
-      <c r="CD99" s="234"/>
-      <c r="CE99" s="233"/>
+      <c r="BX99" s="234"/>
+      <c r="BY99" s="234"/>
+      <c r="BZ99" s="234"/>
+      <c r="CA99" s="234"/>
+      <c r="CB99" s="234"/>
+      <c r="CC99" s="234"/>
+      <c r="CD99" s="237"/>
+      <c r="CE99" s="236"/>
       <c r="CF99" s="97"/>
     </row>
     <row r="100" ht="17.6" spans="4:85">
@@ -10005,7 +9997,7 @@
       <c r="T100" s="34"/>
       <c r="U100" s="34"/>
       <c r="V100" s="97"/>
-      <c r="Z100" s="172"/>
+      <c r="Z100" s="178"/>
       <c r="AA100" s="106"/>
       <c r="AB100" s="106"/>
       <c r="AC100" s="106"/>
@@ -10029,61 +10021,61 @@
       <c r="AW100" s="16"/>
       <c r="AX100" s="16"/>
       <c r="AY100" s="16"/>
-      <c r="AZ100" s="221" t="s">
-        <v>140</v>
-      </c>
-      <c r="BA100" s="221"/>
-      <c r="BB100" s="221"/>
-      <c r="BC100" s="222"/>
-      <c r="BD100" s="221">
+      <c r="AZ100" s="224" t="s">
+        <v>137</v>
+      </c>
+      <c r="BA100" s="224"/>
+      <c r="BB100" s="224"/>
+      <c r="BC100" s="225"/>
+      <c r="BD100" s="224">
         <v>30000</v>
       </c>
-      <c r="BE100" s="221"/>
-      <c r="BF100" s="221"/>
-      <c r="BG100" s="221">
+      <c r="BE100" s="224"/>
+      <c r="BF100" s="224"/>
+      <c r="BG100" s="224">
         <v>3000</v>
       </c>
-      <c r="BH100" s="221"/>
-      <c r="BI100" s="221"/>
-      <c r="BJ100" s="223"/>
-      <c r="BK100" s="222"/>
+      <c r="BH100" s="224"/>
+      <c r="BI100" s="224"/>
+      <c r="BJ100" s="226"/>
+      <c r="BK100" s="225"/>
       <c r="BL100" s="97"/>
       <c r="BM100" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BO100" s="29"/>
-      <c r="BP100" s="228"/>
-      <c r="BQ100" s="228"/>
-      <c r="BR100" s="228"/>
-      <c r="BS100" s="228"/>
-      <c r="BT100" s="231"/>
-      <c r="BU100" s="231"/>
-      <c r="BV100" s="231"/>
+      <c r="BP100" s="231"/>
+      <c r="BQ100" s="231"/>
+      <c r="BR100" s="231"/>
+      <c r="BS100" s="231"/>
+      <c r="BT100" s="234"/>
+      <c r="BU100" s="234"/>
+      <c r="BV100" s="234"/>
       <c r="BW100" s="87"/>
-      <c r="BX100" s="231"/>
-      <c r="BY100" s="231"/>
-      <c r="BZ100" s="231"/>
-      <c r="CA100" s="231"/>
-      <c r="CB100" s="231"/>
-      <c r="CC100" s="231"/>
-      <c r="CD100" s="234"/>
+      <c r="BX100" s="234"/>
+      <c r="BY100" s="234"/>
+      <c r="BZ100" s="234"/>
+      <c r="CA100" s="234"/>
+      <c r="CB100" s="234"/>
+      <c r="CC100" s="234"/>
+      <c r="CD100" s="237"/>
       <c r="CE100" s="87"/>
       <c r="CF100" s="97"/>
       <c r="CG100" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="101" ht="17.6" spans="4:84">
       <c r="D101" s="29"/>
-      <c r="E101" s="181" t="s">
-        <v>141</v>
-      </c>
-      <c r="F101" s="181"/>
-      <c r="G101" s="181"/>
-      <c r="H101" s="181"/>
-      <c r="I101" s="181"/>
-      <c r="J101" s="181"/>
-      <c r="K101" s="181"/>
+      <c r="E101" s="187" t="s">
+        <v>138</v>
+      </c>
+      <c r="F101" s="187"/>
+      <c r="G101" s="187"/>
+      <c r="H101" s="187"/>
+      <c r="I101" s="187"/>
+      <c r="J101" s="187"/>
+      <c r="K101" s="187"/>
       <c r="L101" s="34"/>
       <c r="M101" s="34"/>
       <c r="N101" s="34"/>
@@ -10119,44 +10111,44 @@
       <c r="AW101" s="16"/>
       <c r="AX101" s="16"/>
       <c r="AY101" s="16"/>
-      <c r="AZ101" s="221" t="s">
-        <v>142</v>
-      </c>
-      <c r="BA101" s="221"/>
-      <c r="BB101" s="221"/>
-      <c r="BC101" s="222"/>
-      <c r="BD101" s="221">
+      <c r="AZ101" s="224" t="s">
+        <v>139</v>
+      </c>
+      <c r="BA101" s="224"/>
+      <c r="BB101" s="224"/>
+      <c r="BC101" s="225"/>
+      <c r="BD101" s="224">
         <v>25000</v>
       </c>
-      <c r="BE101" s="221"/>
-      <c r="BF101" s="221"/>
-      <c r="BG101" s="221">
+      <c r="BE101" s="224"/>
+      <c r="BF101" s="224"/>
+      <c r="BG101" s="224">
         <v>5000</v>
       </c>
-      <c r="BH101" s="221"/>
-      <c r="BI101" s="221"/>
-      <c r="BJ101" s="223"/>
-      <c r="BK101" s="225" t="s">
+      <c r="BH101" s="224"/>
+      <c r="BI101" s="224"/>
+      <c r="BJ101" s="226"/>
+      <c r="BK101" s="228" t="s">
         <v>36</v>
       </c>
       <c r="BL101" s="97"/>
       <c r="BO101" s="29"/>
-      <c r="BP101" s="228"/>
-      <c r="BQ101" s="228"/>
-      <c r="BR101" s="228"/>
-      <c r="BS101" s="228"/>
-      <c r="BT101" s="231"/>
-      <c r="BU101" s="231"/>
-      <c r="BV101" s="231"/>
+      <c r="BP101" s="231"/>
+      <c r="BQ101" s="231"/>
+      <c r="BR101" s="231"/>
+      <c r="BS101" s="231"/>
+      <c r="BT101" s="234"/>
+      <c r="BU101" s="234"/>
+      <c r="BV101" s="234"/>
       <c r="BW101" s="87"/>
-      <c r="BX101" s="231"/>
-      <c r="BY101" s="231"/>
-      <c r="BZ101" s="231"/>
-      <c r="CA101" s="231"/>
-      <c r="CB101" s="231"/>
-      <c r="CC101" s="231"/>
-      <c r="CD101" s="234"/>
-      <c r="CE101" s="233"/>
+      <c r="BX101" s="234"/>
+      <c r="BY101" s="234"/>
+      <c r="BZ101" s="234"/>
+      <c r="CA101" s="234"/>
+      <c r="CB101" s="234"/>
+      <c r="CC101" s="234"/>
+      <c r="CD101" s="237"/>
+      <c r="CE101" s="236"/>
       <c r="CF101" s="97"/>
     </row>
     <row r="102" ht="20.4" spans="4:84">
@@ -10203,65 +10195,65 @@
       <c r="AW102" s="16"/>
       <c r="AX102" s="16"/>
       <c r="AY102" s="16"/>
-      <c r="AZ102" s="221" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA102" s="221"/>
-      <c r="BB102" s="221"/>
-      <c r="BC102" s="222"/>
-      <c r="BD102" s="221">
+      <c r="AZ102" s="224" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA102" s="224"/>
+      <c r="BB102" s="224"/>
+      <c r="BC102" s="225"/>
+      <c r="BD102" s="224">
         <v>3000</v>
       </c>
-      <c r="BE102" s="221"/>
-      <c r="BF102" s="221"/>
-      <c r="BG102" s="221">
+      <c r="BE102" s="224"/>
+      <c r="BF102" s="224"/>
+      <c r="BG102" s="224">
         <v>1000</v>
       </c>
-      <c r="BH102" s="221"/>
-      <c r="BI102" s="221"/>
-      <c r="BJ102" s="223"/>
-      <c r="BK102" s="224"/>
+      <c r="BH102" s="224"/>
+      <c r="BI102" s="224"/>
+      <c r="BJ102" s="226"/>
+      <c r="BK102" s="227"/>
       <c r="BL102" s="97"/>
       <c r="BO102" s="29"/>
-      <c r="BP102" s="228"/>
-      <c r="BQ102" s="228"/>
-      <c r="BR102" s="228"/>
-      <c r="BS102" s="228"/>
-      <c r="BT102" s="231"/>
-      <c r="BU102" s="231"/>
-      <c r="BV102" s="231"/>
+      <c r="BP102" s="231"/>
+      <c r="BQ102" s="231"/>
+      <c r="BR102" s="231"/>
+      <c r="BS102" s="231"/>
+      <c r="BT102" s="234"/>
+      <c r="BU102" s="234"/>
+      <c r="BV102" s="234"/>
       <c r="BW102" s="87"/>
-      <c r="BX102" s="231"/>
-      <c r="BY102" s="231"/>
-      <c r="BZ102" s="231"/>
-      <c r="CA102" s="231"/>
-      <c r="CB102" s="231"/>
-      <c r="CC102" s="231"/>
-      <c r="CD102" s="234"/>
-      <c r="CE102" s="232"/>
+      <c r="BX102" s="234"/>
+      <c r="BY102" s="234"/>
+      <c r="BZ102" s="234"/>
+      <c r="CA102" s="234"/>
+      <c r="CB102" s="234"/>
+      <c r="CC102" s="234"/>
+      <c r="CD102" s="237"/>
+      <c r="CE102" s="235"/>
       <c r="CF102" s="97"/>
     </row>
     <row r="103" ht="17.6" spans="1:84">
-      <c r="A103" s="171" t="s">
-        <v>144</v>
-      </c>
-      <c r="B103" s="171"/>
-      <c r="D103" s="176" t="s">
-        <v>145</v>
+      <c r="A103" s="177" t="s">
+        <v>141</v>
+      </c>
+      <c r="B103" s="177"/>
+      <c r="D103" s="182" t="s">
+        <v>142</v>
       </c>
       <c r="E103" s="19"/>
       <c r="F103" s="19"/>
       <c r="G103" s="19"/>
       <c r="H103" s="19"/>
       <c r="I103" s="19"/>
-      <c r="J103" s="186"/>
-      <c r="K103" s="187">
+      <c r="J103" s="192"/>
+      <c r="K103" s="193">
         <v>50</v>
       </c>
-      <c r="L103" s="187"/>
+      <c r="L103" s="193"/>
       <c r="M103" s="107"/>
       <c r="N103" s="19" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="O103" s="16"/>
       <c r="P103" s="16"/>
@@ -10272,8 +10264,8 @@
       </c>
       <c r="T103" s="107"/>
       <c r="U103" s="107"/>
-      <c r="V103" s="193"/>
-      <c r="Z103" s="172"/>
+      <c r="V103" s="199"/>
+      <c r="Z103" s="178"/>
       <c r="AA103" s="106"/>
       <c r="AB103" s="106"/>
       <c r="AC103" s="106"/>
@@ -10297,56 +10289,56 @@
       <c r="AW103" s="16"/>
       <c r="AX103" s="16"/>
       <c r="AY103" s="16"/>
-      <c r="AZ103" s="221" t="s">
-        <v>135</v>
-      </c>
-      <c r="BA103" s="221"/>
-      <c r="BB103" s="221"/>
-      <c r="BC103" s="222"/>
-      <c r="BD103" s="221">
+      <c r="AZ103" s="224" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA103" s="224"/>
+      <c r="BB103" s="224"/>
+      <c r="BC103" s="225"/>
+      <c r="BD103" s="224">
         <v>6000</v>
       </c>
-      <c r="BE103" s="221"/>
-      <c r="BF103" s="221"/>
-      <c r="BG103" s="221">
+      <c r="BE103" s="224"/>
+      <c r="BF103" s="224"/>
+      <c r="BG103" s="224">
         <v>1000</v>
       </c>
-      <c r="BH103" s="221"/>
-      <c r="BI103" s="221"/>
-      <c r="BJ103" s="223"/>
-      <c r="BK103" s="222"/>
+      <c r="BH103" s="224"/>
+      <c r="BI103" s="224"/>
+      <c r="BJ103" s="226"/>
+      <c r="BK103" s="225"/>
       <c r="BL103" s="97"/>
       <c r="BO103" s="29"/>
-      <c r="BP103" s="228"/>
-      <c r="BQ103" s="228"/>
-      <c r="BR103" s="228"/>
-      <c r="BS103" s="228"/>
-      <c r="BT103" s="231"/>
-      <c r="BU103" s="231"/>
-      <c r="BV103" s="231"/>
+      <c r="BP103" s="231"/>
+      <c r="BQ103" s="231"/>
+      <c r="BR103" s="231"/>
+      <c r="BS103" s="231"/>
+      <c r="BT103" s="234"/>
+      <c r="BU103" s="234"/>
+      <c r="BV103" s="234"/>
       <c r="BW103" s="87"/>
-      <c r="BX103" s="231"/>
-      <c r="BY103" s="231"/>
-      <c r="BZ103" s="231"/>
-      <c r="CA103" s="231"/>
-      <c r="CB103" s="231"/>
-      <c r="CC103" s="231"/>
-      <c r="CD103" s="234"/>
+      <c r="BX103" s="234"/>
+      <c r="BY103" s="234"/>
+      <c r="BZ103" s="234"/>
+      <c r="CA103" s="234"/>
+      <c r="CB103" s="234"/>
+      <c r="CC103" s="234"/>
+      <c r="CD103" s="237"/>
       <c r="CE103" s="87"/>
       <c r="CF103" s="97"/>
     </row>
     <row r="104" ht="17.55" spans="1:84">
-      <c r="A104" s="171"/>
-      <c r="B104" s="171"/>
-      <c r="D104" s="176"/>
+      <c r="A104" s="177"/>
+      <c r="B104" s="177"/>
+      <c r="D104" s="182"/>
       <c r="E104" s="19"/>
       <c r="F104" s="19"/>
       <c r="G104" s="19"/>
       <c r="H104" s="19"/>
       <c r="I104" s="19"/>
-      <c r="J104" s="186"/>
-      <c r="K104" s="187"/>
-      <c r="L104" s="187"/>
+      <c r="J104" s="192"/>
+      <c r="K104" s="193"/>
+      <c r="L104" s="193"/>
       <c r="M104" s="107"/>
       <c r="N104" s="16"/>
       <c r="O104" s="16"/>
@@ -10356,26 +10348,26 @@
       <c r="S104" s="107"/>
       <c r="T104" s="107"/>
       <c r="U104" s="107"/>
-      <c r="V104" s="193"/>
-      <c r="Z104" s="205"/>
-      <c r="AA104" s="184"/>
-      <c r="AB104" s="184"/>
-      <c r="AC104" s="184"/>
-      <c r="AD104" s="184"/>
-      <c r="AE104" s="184"/>
-      <c r="AF104" s="184"/>
-      <c r="AG104" s="184"/>
-      <c r="AH104" s="184"/>
-      <c r="AI104" s="184"/>
-      <c r="AJ104" s="184"/>
-      <c r="AK104" s="184"/>
-      <c r="AL104" s="184"/>
-      <c r="AM104" s="184"/>
-      <c r="AN104" s="184"/>
-      <c r="AO104" s="184"/>
-      <c r="AP104" s="184"/>
-      <c r="AQ104" s="184"/>
-      <c r="AR104" s="218"/>
+      <c r="V104" s="199"/>
+      <c r="Z104" s="211"/>
+      <c r="AA104" s="190"/>
+      <c r="AB104" s="190"/>
+      <c r="AC104" s="190"/>
+      <c r="AD104" s="190"/>
+      <c r="AE104" s="190"/>
+      <c r="AF104" s="190"/>
+      <c r="AG104" s="190"/>
+      <c r="AH104" s="190"/>
+      <c r="AI104" s="190"/>
+      <c r="AJ104" s="190"/>
+      <c r="AK104" s="190"/>
+      <c r="AL104" s="190"/>
+      <c r="AM104" s="190"/>
+      <c r="AN104" s="190"/>
+      <c r="AO104" s="190"/>
+      <c r="AP104" s="190"/>
+      <c r="AQ104" s="190"/>
+      <c r="AR104" s="221"/>
       <c r="AU104" s="29"/>
       <c r="BL104" s="97"/>
       <c r="BO104" s="29"/>
@@ -10398,8 +10390,8 @@
       <c r="CF104" s="97"/>
     </row>
     <row r="105" ht="20.4" spans="1:84">
-      <c r="A105" s="171"/>
-      <c r="B105" s="171"/>
+      <c r="A105" s="177"/>
+      <c r="B105" s="177"/>
       <c r="D105" s="29"/>
       <c r="H105" s="27"/>
       <c r="I105" s="27"/>
@@ -10417,62 +10409,62 @@
       <c r="U105" s="27"/>
       <c r="V105" s="97"/>
       <c r="AU105" s="29"/>
-      <c r="AV105" s="219" t="s">
-        <v>147</v>
-      </c>
-      <c r="AW105" s="219"/>
-      <c r="AX105" s="219"/>
-      <c r="AY105" s="219"/>
-      <c r="AZ105" s="219"/>
-      <c r="BA105" s="219"/>
-      <c r="BB105" s="219"/>
-      <c r="BC105" s="219"/>
-      <c r="BD105" s="219"/>
+      <c r="AV105" s="222" t="s">
+        <v>144</v>
+      </c>
+      <c r="AW105" s="222"/>
+      <c r="AX105" s="222"/>
+      <c r="AY105" s="222"/>
+      <c r="AZ105" s="222"/>
+      <c r="BA105" s="222"/>
+      <c r="BB105" s="222"/>
+      <c r="BC105" s="222"/>
+      <c r="BD105" s="222"/>
       <c r="BE105" s="93"/>
       <c r="BF105" s="93"/>
       <c r="BG105" s="93"/>
       <c r="BH105" s="93"/>
       <c r="BI105" s="93"/>
       <c r="BJ105" s="93"/>
-      <c r="BK105" s="224"/>
+      <c r="BK105" s="227"/>
       <c r="BL105" s="97"/>
       <c r="BO105" s="29"/>
-      <c r="BP105" s="229"/>
-      <c r="BQ105" s="229"/>
-      <c r="BR105" s="229"/>
-      <c r="BS105" s="229"/>
-      <c r="BT105" s="229"/>
-      <c r="BU105" s="229"/>
-      <c r="BV105" s="229"/>
-      <c r="BW105" s="229"/>
-      <c r="BX105" s="229"/>
-      <c r="BY105" s="229"/>
-      <c r="BZ105" s="229"/>
-      <c r="CA105" s="229"/>
-      <c r="CB105" s="229"/>
-      <c r="CC105" s="229"/>
-      <c r="CD105" s="229"/>
-      <c r="CE105" s="232"/>
+      <c r="BP105" s="232"/>
+      <c r="BQ105" s="232"/>
+      <c r="BR105" s="232"/>
+      <c r="BS105" s="232"/>
+      <c r="BT105" s="232"/>
+      <c r="BU105" s="232"/>
+      <c r="BV105" s="232"/>
+      <c r="BW105" s="232"/>
+      <c r="BX105" s="232"/>
+      <c r="BY105" s="232"/>
+      <c r="BZ105" s="232"/>
+      <c r="CA105" s="232"/>
+      <c r="CB105" s="232"/>
+      <c r="CC105" s="232"/>
+      <c r="CD105" s="232"/>
+      <c r="CE105" s="235"/>
       <c r="CF105" s="97"/>
     </row>
     <row r="106" ht="18" customHeight="1" spans="1:84">
-      <c r="A106" s="171"/>
-      <c r="B106" s="171"/>
-      <c r="D106" s="176" t="s">
-        <v>148</v>
+      <c r="A106" s="177"/>
+      <c r="B106" s="177"/>
+      <c r="D106" s="182" t="s">
+        <v>145</v>
       </c>
       <c r="E106" s="19"/>
       <c r="F106" s="19"/>
       <c r="G106" s="19"/>
       <c r="H106" s="19"/>
       <c r="I106" s="19"/>
-      <c r="J106" s="186"/>
-      <c r="K106" s="187">
+      <c r="J106" s="192"/>
+      <c r="K106" s="193">
         <v>60</v>
       </c>
-      <c r="L106" s="187"/>
+      <c r="L106" s="193"/>
       <c r="N106" s="19" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="O106" s="16"/>
       <c r="P106" s="16"/>
@@ -10483,64 +10475,64 @@
       </c>
       <c r="T106" s="107"/>
       <c r="U106" s="107"/>
-      <c r="V106" s="193"/>
+      <c r="V106" s="199"/>
       <c r="AU106" s="29"/>
       <c r="AV106" s="16" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="AW106" s="16"/>
       <c r="AX106" s="16"/>
       <c r="AY106" s="16"/>
-      <c r="AZ106" s="221" t="s">
-        <v>139</v>
-      </c>
-      <c r="BA106" s="221"/>
-      <c r="BB106" s="221"/>
-      <c r="BC106" s="222"/>
-      <c r="BD106" s="221">
+      <c r="AZ106" s="224" t="s">
+        <v>136</v>
+      </c>
+      <c r="BA106" s="224"/>
+      <c r="BB106" s="224"/>
+      <c r="BC106" s="225"/>
+      <c r="BD106" s="224">
         <v>18000</v>
       </c>
-      <c r="BE106" s="221"/>
-      <c r="BF106" s="221"/>
-      <c r="BG106" s="221">
+      <c r="BE106" s="224"/>
+      <c r="BF106" s="224"/>
+      <c r="BG106" s="224">
         <v>2000</v>
       </c>
-      <c r="BH106" s="221"/>
-      <c r="BI106" s="221"/>
-      <c r="BJ106" s="223"/>
-      <c r="BK106" s="225"/>
+      <c r="BH106" s="224"/>
+      <c r="BI106" s="224"/>
+      <c r="BJ106" s="226"/>
+      <c r="BK106" s="228"/>
       <c r="BL106" s="97"/>
       <c r="BO106" s="29"/>
-      <c r="BP106" s="228"/>
-      <c r="BQ106" s="228"/>
-      <c r="BR106" s="228"/>
-      <c r="BS106" s="228"/>
-      <c r="BT106" s="231"/>
-      <c r="BU106" s="231"/>
-      <c r="BV106" s="231"/>
+      <c r="BP106" s="231"/>
+      <c r="BQ106" s="231"/>
+      <c r="BR106" s="231"/>
+      <c r="BS106" s="231"/>
+      <c r="BT106" s="234"/>
+      <c r="BU106" s="234"/>
+      <c r="BV106" s="234"/>
       <c r="BW106" s="87"/>
-      <c r="BX106" s="231"/>
-      <c r="BY106" s="231"/>
-      <c r="BZ106" s="231"/>
-      <c r="CA106" s="231"/>
-      <c r="CB106" s="231"/>
-      <c r="CC106" s="231"/>
-      <c r="CD106" s="234"/>
-      <c r="CE106" s="233"/>
+      <c r="BX106" s="234"/>
+      <c r="BY106" s="234"/>
+      <c r="BZ106" s="234"/>
+      <c r="CA106" s="234"/>
+      <c r="CB106" s="234"/>
+      <c r="CC106" s="234"/>
+      <c r="CD106" s="237"/>
+      <c r="CE106" s="236"/>
       <c r="CF106" s="97"/>
     </row>
     <row r="107" ht="17.6" spans="1:85">
-      <c r="A107" s="177"/>
-      <c r="B107" s="177"/>
-      <c r="D107" s="176"/>
+      <c r="A107" s="183"/>
+      <c r="B107" s="183"/>
+      <c r="D107" s="182"/>
       <c r="E107" s="19"/>
       <c r="F107" s="19"/>
       <c r="G107" s="19"/>
       <c r="H107" s="19"/>
       <c r="I107" s="19"/>
-      <c r="J107" s="186"/>
-      <c r="K107" s="187"/>
-      <c r="L107" s="187"/>
+      <c r="J107" s="192"/>
+      <c r="K107" s="193"/>
+      <c r="L107" s="193"/>
       <c r="N107" s="16"/>
       <c r="O107" s="16"/>
       <c r="P107" s="16"/>
@@ -10549,62 +10541,62 @@
       <c r="S107" s="107"/>
       <c r="T107" s="107"/>
       <c r="U107" s="107"/>
-      <c r="V107" s="193"/>
+      <c r="V107" s="199"/>
       <c r="AU107" s="29"/>
       <c r="AV107" s="16"/>
       <c r="AW107" s="16"/>
       <c r="AX107" s="16"/>
       <c r="AY107" s="16"/>
-      <c r="AZ107" s="221" t="s">
-        <v>140</v>
-      </c>
-      <c r="BA107" s="221"/>
-      <c r="BB107" s="221"/>
-      <c r="BC107" s="222"/>
-      <c r="BD107" s="221">
+      <c r="AZ107" s="224" t="s">
+        <v>137</v>
+      </c>
+      <c r="BA107" s="224"/>
+      <c r="BB107" s="224"/>
+      <c r="BC107" s="225"/>
+      <c r="BD107" s="224">
         <v>30000</v>
       </c>
-      <c r="BE107" s="221"/>
-      <c r="BF107" s="221"/>
-      <c r="BG107" s="221">
+      <c r="BE107" s="224"/>
+      <c r="BF107" s="224"/>
+      <c r="BG107" s="224">
         <v>3000</v>
       </c>
-      <c r="BH107" s="221"/>
-      <c r="BI107" s="221"/>
-      <c r="BJ107" s="223"/>
-      <c r="BK107" s="222"/>
+      <c r="BH107" s="224"/>
+      <c r="BI107" s="224"/>
+      <c r="BJ107" s="226"/>
+      <c r="BK107" s="225"/>
       <c r="BL107" s="97"/>
       <c r="BM107" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="BO107" s="29"/>
-      <c r="BP107" s="228"/>
-      <c r="BQ107" s="228"/>
-      <c r="BR107" s="228"/>
-      <c r="BS107" s="228"/>
-      <c r="BT107" s="231"/>
-      <c r="BU107" s="231"/>
-      <c r="BV107" s="231"/>
+      <c r="BP107" s="231"/>
+      <c r="BQ107" s="231"/>
+      <c r="BR107" s="231"/>
+      <c r="BS107" s="231"/>
+      <c r="BT107" s="234"/>
+      <c r="BU107" s="234"/>
+      <c r="BV107" s="234"/>
       <c r="BW107" s="87"/>
-      <c r="BX107" s="231"/>
-      <c r="BY107" s="231"/>
-      <c r="BZ107" s="231"/>
-      <c r="CA107" s="231"/>
-      <c r="CB107" s="231"/>
-      <c r="CC107" s="231"/>
-      <c r="CD107" s="234"/>
+      <c r="BX107" s="234"/>
+      <c r="BY107" s="234"/>
+      <c r="BZ107" s="234"/>
+      <c r="CA107" s="234"/>
+      <c r="CB107" s="234"/>
+      <c r="CC107" s="234"/>
+      <c r="CD107" s="237"/>
       <c r="CE107" s="87"/>
       <c r="CF107" s="97"/>
       <c r="CG107" s="25" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="108" ht="17.6" spans="1:84">
-      <c r="A108" s="177" t="s">
-        <v>150</v>
-      </c>
-      <c r="B108" s="177" t="s">
-        <v>151</v>
+      <c r="A108" s="183" t="s">
+        <v>147</v>
+      </c>
+      <c r="B108" s="183" t="s">
+        <v>148</v>
       </c>
       <c r="D108" s="29"/>
       <c r="J108" s="34"/>
@@ -10614,51 +10606,51 @@
       <c r="AW108" s="16"/>
       <c r="AX108" s="16"/>
       <c r="AY108" s="16"/>
-      <c r="AZ108" s="221" t="s">
-        <v>142</v>
-      </c>
-      <c r="BA108" s="221"/>
-      <c r="BB108" s="221"/>
-      <c r="BC108" s="222"/>
-      <c r="BD108" s="221">
+      <c r="AZ108" s="224" t="s">
+        <v>139</v>
+      </c>
+      <c r="BA108" s="224"/>
+      <c r="BB108" s="224"/>
+      <c r="BC108" s="225"/>
+      <c r="BD108" s="224">
         <v>25000</v>
       </c>
-      <c r="BE108" s="221"/>
-      <c r="BF108" s="221"/>
-      <c r="BG108" s="221">
+      <c r="BE108" s="224"/>
+      <c r="BF108" s="224"/>
+      <c r="BG108" s="224">
         <v>5000</v>
       </c>
-      <c r="BH108" s="221"/>
-      <c r="BI108" s="221"/>
-      <c r="BJ108" s="223"/>
-      <c r="BK108" s="225" t="s">
+      <c r="BH108" s="224"/>
+      <c r="BI108" s="224"/>
+      <c r="BJ108" s="226"/>
+      <c r="BK108" s="228" t="s">
         <v>36</v>
       </c>
       <c r="BL108" s="97"/>
       <c r="BO108" s="29"/>
-      <c r="BP108" s="228"/>
-      <c r="BQ108" s="228"/>
-      <c r="BR108" s="228"/>
-      <c r="BS108" s="228"/>
-      <c r="BT108" s="231"/>
-      <c r="BU108" s="231"/>
-      <c r="BV108" s="231"/>
+      <c r="BP108" s="231"/>
+      <c r="BQ108" s="231"/>
+      <c r="BR108" s="231"/>
+      <c r="BS108" s="231"/>
+      <c r="BT108" s="234"/>
+      <c r="BU108" s="234"/>
+      <c r="BV108" s="234"/>
       <c r="BW108" s="87"/>
-      <c r="BX108" s="231"/>
-      <c r="BY108" s="231"/>
-      <c r="BZ108" s="231"/>
-      <c r="CA108" s="231"/>
-      <c r="CB108" s="231"/>
-      <c r="CC108" s="231"/>
-      <c r="CD108" s="234"/>
-      <c r="CE108" s="233"/>
+      <c r="BX108" s="234"/>
+      <c r="BY108" s="234"/>
+      <c r="BZ108" s="234"/>
+      <c r="CA108" s="234"/>
+      <c r="CB108" s="234"/>
+      <c r="CC108" s="234"/>
+      <c r="CD108" s="237"/>
+      <c r="CE108" s="236"/>
       <c r="CF108" s="97"/>
     </row>
     <row r="109" ht="20.4" spans="1:84">
-      <c r="A109" s="177"/>
-      <c r="B109" s="177"/>
-      <c r="D109" s="178" t="s">
-        <v>152</v>
+      <c r="A109" s="183"/>
+      <c r="B109" s="183"/>
+      <c r="D109" s="184" t="s">
+        <v>149</v>
       </c>
       <c r="E109" s="16"/>
       <c r="F109" s="16"/>
@@ -10671,7 +10663,7 @@
       </c>
       <c r="L109" s="27"/>
       <c r="N109" s="16" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O109" s="16"/>
       <c r="P109" s="16"/>
@@ -10682,54 +10674,54 @@
       </c>
       <c r="T109" s="107"/>
       <c r="U109" s="107"/>
-      <c r="V109" s="193"/>
+      <c r="V109" s="199"/>
       <c r="AU109" s="29"/>
       <c r="AV109" s="16"/>
       <c r="AW109" s="16"/>
       <c r="AX109" s="16"/>
       <c r="AY109" s="16"/>
-      <c r="AZ109" s="221" t="s">
-        <v>143</v>
-      </c>
-      <c r="BA109" s="221"/>
-      <c r="BB109" s="221"/>
-      <c r="BC109" s="222"/>
-      <c r="BD109" s="221">
+      <c r="AZ109" s="224" t="s">
+        <v>140</v>
+      </c>
+      <c r="BA109" s="224"/>
+      <c r="BB109" s="224"/>
+      <c r="BC109" s="225"/>
+      <c r="BD109" s="224">
         <v>3000</v>
       </c>
-      <c r="BE109" s="221"/>
-      <c r="BF109" s="221"/>
-      <c r="BG109" s="221">
+      <c r="BE109" s="224"/>
+      <c r="BF109" s="224"/>
+      <c r="BG109" s="224">
         <v>1000</v>
       </c>
-      <c r="BH109" s="221"/>
-      <c r="BI109" s="221"/>
-      <c r="BJ109" s="223"/>
-      <c r="BK109" s="224"/>
+      <c r="BH109" s="224"/>
+      <c r="BI109" s="224"/>
+      <c r="BJ109" s="226"/>
+      <c r="BK109" s="227"/>
       <c r="BL109" s="97"/>
       <c r="BO109" s="29"/>
-      <c r="BP109" s="228"/>
-      <c r="BQ109" s="228"/>
-      <c r="BR109" s="228"/>
-      <c r="BS109" s="228"/>
-      <c r="BT109" s="231"/>
-      <c r="BU109" s="231"/>
-      <c r="BV109" s="231"/>
+      <c r="BP109" s="231"/>
+      <c r="BQ109" s="231"/>
+      <c r="BR109" s="231"/>
+      <c r="BS109" s="231"/>
+      <c r="BT109" s="234"/>
+      <c r="BU109" s="234"/>
+      <c r="BV109" s="234"/>
       <c r="BW109" s="87"/>
-      <c r="BX109" s="231"/>
-      <c r="BY109" s="231"/>
-      <c r="BZ109" s="231"/>
-      <c r="CA109" s="231"/>
-      <c r="CB109" s="231"/>
-      <c r="CC109" s="231"/>
-      <c r="CD109" s="234"/>
-      <c r="CE109" s="232"/>
+      <c r="BX109" s="234"/>
+      <c r="BY109" s="234"/>
+      <c r="BZ109" s="234"/>
+      <c r="CA109" s="234"/>
+      <c r="CB109" s="234"/>
+      <c r="CC109" s="234"/>
+      <c r="CD109" s="237"/>
+      <c r="CE109" s="235"/>
       <c r="CF109" s="97"/>
     </row>
     <row r="110" ht="17.6" spans="1:84">
-      <c r="A110" s="177"/>
-      <c r="B110" s="177"/>
-      <c r="D110" s="178"/>
+      <c r="A110" s="183"/>
+      <c r="B110" s="183"/>
+      <c r="D110" s="184"/>
       <c r="E110" s="16"/>
       <c r="F110" s="16"/>
       <c r="G110" s="16"/>
@@ -10746,53 +10738,53 @@
       <c r="S110" s="107"/>
       <c r="T110" s="107"/>
       <c r="U110" s="107"/>
-      <c r="V110" s="193"/>
+      <c r="V110" s="199"/>
       <c r="AU110" s="29"/>
       <c r="AV110" s="16"/>
       <c r="AW110" s="16"/>
       <c r="AX110" s="16"/>
       <c r="AY110" s="16"/>
-      <c r="AZ110" s="221" t="s">
-        <v>135</v>
-      </c>
-      <c r="BA110" s="221"/>
-      <c r="BB110" s="221"/>
-      <c r="BC110" s="222"/>
-      <c r="BD110" s="221">
+      <c r="AZ110" s="224" t="s">
+        <v>132</v>
+      </c>
+      <c r="BA110" s="224"/>
+      <c r="BB110" s="224"/>
+      <c r="BC110" s="225"/>
+      <c r="BD110" s="224">
         <v>6000</v>
       </c>
-      <c r="BE110" s="221"/>
-      <c r="BF110" s="221"/>
-      <c r="BG110" s="221">
+      <c r="BE110" s="224"/>
+      <c r="BF110" s="224"/>
+      <c r="BG110" s="224">
         <v>1000</v>
       </c>
-      <c r="BH110" s="221"/>
-      <c r="BI110" s="221"/>
-      <c r="BJ110" s="223"/>
-      <c r="BK110" s="222"/>
+      <c r="BH110" s="224"/>
+      <c r="BI110" s="224"/>
+      <c r="BJ110" s="226"/>
+      <c r="BK110" s="225"/>
       <c r="BL110" s="97"/>
       <c r="BO110" s="29"/>
-      <c r="BP110" s="228"/>
-      <c r="BQ110" s="228"/>
-      <c r="BR110" s="228"/>
-      <c r="BS110" s="228"/>
-      <c r="BT110" s="231"/>
-      <c r="BU110" s="231"/>
-      <c r="BV110" s="231"/>
+      <c r="BP110" s="231"/>
+      <c r="BQ110" s="231"/>
+      <c r="BR110" s="231"/>
+      <c r="BS110" s="231"/>
+      <c r="BT110" s="234"/>
+      <c r="BU110" s="234"/>
+      <c r="BV110" s="234"/>
       <c r="BW110" s="87"/>
-      <c r="BX110" s="231"/>
-      <c r="BY110" s="231"/>
-      <c r="BZ110" s="231"/>
-      <c r="CA110" s="231"/>
-      <c r="CB110" s="231"/>
-      <c r="CC110" s="231"/>
-      <c r="CD110" s="234"/>
+      <c r="BX110" s="234"/>
+      <c r="BY110" s="234"/>
+      <c r="BZ110" s="234"/>
+      <c r="CA110" s="234"/>
+      <c r="CB110" s="234"/>
+      <c r="CC110" s="234"/>
+      <c r="CD110" s="237"/>
       <c r="CE110" s="87"/>
       <c r="CF110" s="97"/>
     </row>
     <row r="111" spans="1:84">
-      <c r="A111" s="177"/>
-      <c r="B111" s="177"/>
+      <c r="A111" s="183"/>
+      <c r="B111" s="183"/>
       <c r="D111" s="29"/>
       <c r="J111" s="34"/>
       <c r="V111" s="97"/>
@@ -10818,8 +10810,8 @@
       <c r="CF111" s="97"/>
     </row>
     <row r="112" ht="17.55" spans="4:84">
-      <c r="D112" s="178" t="s">
-        <v>154</v>
+      <c r="D112" s="184" t="s">
+        <v>151</v>
       </c>
       <c r="E112" s="16"/>
       <c r="F112" s="16"/>
@@ -10831,7 +10823,7 @@
         <v>150</v>
       </c>
       <c r="N112" s="16" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O112" s="16"/>
       <c r="P112" s="16"/>
@@ -10842,46 +10834,46 @@
       </c>
       <c r="T112" s="107"/>
       <c r="U112" s="107"/>
-      <c r="V112" s="193"/>
-      <c r="AU112" s="220"/>
-      <c r="AV112" s="185"/>
-      <c r="AW112" s="185"/>
-      <c r="AX112" s="185"/>
-      <c r="AY112" s="185"/>
-      <c r="AZ112" s="185"/>
-      <c r="BA112" s="185"/>
-      <c r="BB112" s="185"/>
-      <c r="BC112" s="185"/>
-      <c r="BD112" s="185"/>
-      <c r="BE112" s="185"/>
-      <c r="BF112" s="185"/>
-      <c r="BG112" s="185"/>
-      <c r="BH112" s="185"/>
-      <c r="BI112" s="185"/>
-      <c r="BJ112" s="185"/>
-      <c r="BK112" s="185"/>
-      <c r="BL112" s="226"/>
-      <c r="BO112" s="220"/>
-      <c r="BP112" s="185"/>
-      <c r="BQ112" s="185"/>
-      <c r="BR112" s="185"/>
-      <c r="BS112" s="185"/>
-      <c r="BT112" s="185"/>
-      <c r="BU112" s="185"/>
-      <c r="BV112" s="185"/>
-      <c r="BW112" s="185"/>
-      <c r="BX112" s="185"/>
-      <c r="BY112" s="185"/>
-      <c r="BZ112" s="185"/>
-      <c r="CA112" s="185"/>
-      <c r="CB112" s="185"/>
-      <c r="CC112" s="185"/>
-      <c r="CD112" s="185"/>
-      <c r="CE112" s="185"/>
-      <c r="CF112" s="226"/>
+      <c r="V112" s="199"/>
+      <c r="AU112" s="223"/>
+      <c r="AV112" s="191"/>
+      <c r="AW112" s="191"/>
+      <c r="AX112" s="191"/>
+      <c r="AY112" s="191"/>
+      <c r="AZ112" s="191"/>
+      <c r="BA112" s="191"/>
+      <c r="BB112" s="191"/>
+      <c r="BC112" s="191"/>
+      <c r="BD112" s="191"/>
+      <c r="BE112" s="191"/>
+      <c r="BF112" s="191"/>
+      <c r="BG112" s="191"/>
+      <c r="BH112" s="191"/>
+      <c r="BI112" s="191"/>
+      <c r="BJ112" s="191"/>
+      <c r="BK112" s="191"/>
+      <c r="BL112" s="229"/>
+      <c r="BO112" s="223"/>
+      <c r="BP112" s="191"/>
+      <c r="BQ112" s="191"/>
+      <c r="BR112" s="191"/>
+      <c r="BS112" s="191"/>
+      <c r="BT112" s="191"/>
+      <c r="BU112" s="191"/>
+      <c r="BV112" s="191"/>
+      <c r="BW112" s="191"/>
+      <c r="BX112" s="191"/>
+      <c r="BY112" s="191"/>
+      <c r="BZ112" s="191"/>
+      <c r="CA112" s="191"/>
+      <c r="CB112" s="191"/>
+      <c r="CC112" s="191"/>
+      <c r="CD112" s="191"/>
+      <c r="CE112" s="191"/>
+      <c r="CF112" s="229"/>
     </row>
     <row r="113" ht="16" customHeight="1" spans="4:22">
-      <c r="D113" s="178"/>
+      <c r="D113" s="184"/>
       <c r="E113" s="16"/>
       <c r="F113" s="16"/>
       <c r="G113" s="16"/>
@@ -10896,7 +10888,7 @@
       <c r="S113" s="107"/>
       <c r="T113" s="107"/>
       <c r="U113" s="107"/>
-      <c r="V113" s="193"/>
+      <c r="V113" s="199"/>
     </row>
     <row r="114" ht="16" customHeight="1" spans="4:22">
       <c r="D114" s="29"/>
@@ -10904,8 +10896,8 @@
       <c r="V114" s="97"/>
     </row>
     <row r="115" spans="4:22">
-      <c r="D115" s="178" t="s">
-        <v>155</v>
+      <c r="D115" s="184" t="s">
+        <v>152</v>
       </c>
       <c r="E115" s="16"/>
       <c r="F115" s="16"/>
@@ -10917,7 +10909,7 @@
         <v>200</v>
       </c>
       <c r="N115" s="16" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O115" s="16"/>
       <c r="P115" s="16"/>
@@ -10928,10 +10920,10 @@
       </c>
       <c r="T115" s="107"/>
       <c r="U115" s="107"/>
-      <c r="V115" s="193"/>
+      <c r="V115" s="199"/>
     </row>
     <row r="116" spans="4:22">
-      <c r="D116" s="178"/>
+      <c r="D116" s="184"/>
       <c r="E116" s="16"/>
       <c r="F116" s="16"/>
       <c r="G116" s="16"/>
@@ -10946,7 +10938,7 @@
       <c r="S116" s="107"/>
       <c r="T116" s="107"/>
       <c r="U116" s="107"/>
-      <c r="V116" s="193"/>
+      <c r="V116" s="199"/>
     </row>
     <row r="117" spans="4:22">
       <c r="D117" s="29"/>
@@ -10971,33 +10963,33 @@
     </row>
     <row r="118" spans="4:22">
       <c r="D118" s="29"/>
-      <c r="E118" s="183"/>
-      <c r="F118" s="183"/>
-      <c r="G118" s="183"/>
-      <c r="H118" s="183"/>
-      <c r="I118" s="183"/>
-      <c r="J118" s="183"/>
-      <c r="K118" s="183"/>
-      <c r="L118" s="183"/>
-      <c r="M118" s="183"/>
-      <c r="N118" s="183"/>
-      <c r="O118" s="183"/>
-      <c r="P118" s="183"/>
-      <c r="Q118" s="183"/>
-      <c r="R118" s="183"/>
-      <c r="S118" s="183"/>
+      <c r="E118" s="189"/>
+      <c r="F118" s="189"/>
+      <c r="G118" s="189"/>
+      <c r="H118" s="189"/>
+      <c r="I118" s="189"/>
+      <c r="J118" s="189"/>
+      <c r="K118" s="189"/>
+      <c r="L118" s="189"/>
+      <c r="M118" s="189"/>
+      <c r="N118" s="189"/>
+      <c r="O118" s="189"/>
+      <c r="P118" s="189"/>
+      <c r="Q118" s="189"/>
+      <c r="R118" s="189"/>
+      <c r="S118" s="189"/>
       <c r="T118" s="34"/>
       <c r="U118" s="34"/>
       <c r="V118" s="97"/>
     </row>
     <row r="119" spans="4:22">
       <c r="D119" s="29"/>
-      <c r="E119" s="179" t="s">
-        <v>156</v>
-      </c>
-      <c r="F119" s="179"/>
-      <c r="G119" s="179"/>
-      <c r="H119" s="179"/>
+      <c r="E119" s="185" t="s">
+        <v>153</v>
+      </c>
+      <c r="F119" s="185"/>
+      <c r="G119" s="185"/>
+      <c r="H119" s="185"/>
       <c r="I119" s="34"/>
       <c r="J119" s="34"/>
       <c r="K119" s="34"/>
@@ -11035,68 +11027,68 @@
       <c r="V120" s="97"/>
     </row>
     <row r="121" spans="4:22">
-      <c r="D121" s="176" t="s">
-        <v>157</v>
+      <c r="D121" s="182" t="s">
+        <v>154</v>
       </c>
       <c r="E121" s="19"/>
       <c r="F121" s="19"/>
       <c r="G121" s="19"/>
       <c r="H121" s="19"/>
       <c r="I121" s="19"/>
-      <c r="J121" s="187">
+      <c r="J121" s="193">
         <v>50</v>
       </c>
-      <c r="K121" s="187"/>
-      <c r="L121" s="187"/>
-      <c r="M121" s="189"/>
+      <c r="K121" s="193"/>
+      <c r="L121" s="193"/>
+      <c r="M121" s="195"/>
       <c r="N121" s="19" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O121" s="16"/>
       <c r="P121" s="16"/>
       <c r="Q121" s="16"/>
       <c r="R121" s="16"/>
-      <c r="S121" s="192">
+      <c r="S121" s="198">
         <f>J121*500</f>
         <v>25000</v>
       </c>
-      <c r="T121" s="192"/>
-      <c r="U121" s="192"/>
-      <c r="V121" s="194"/>
+      <c r="T121" s="198"/>
+      <c r="U121" s="198"/>
+      <c r="V121" s="200"/>
     </row>
     <row r="122" spans="4:22">
-      <c r="D122" s="176"/>
+      <c r="D122" s="182"/>
       <c r="E122" s="19"/>
       <c r="F122" s="19"/>
       <c r="G122" s="19"/>
       <c r="H122" s="19"/>
       <c r="I122" s="19"/>
-      <c r="J122" s="187"/>
-      <c r="K122" s="187"/>
-      <c r="L122" s="187"/>
-      <c r="M122" s="189"/>
+      <c r="J122" s="193"/>
+      <c r="K122" s="193"/>
+      <c r="L122" s="193"/>
+      <c r="M122" s="195"/>
       <c r="N122" s="16"/>
       <c r="O122" s="16"/>
       <c r="P122" s="16"/>
       <c r="Q122" s="16"/>
       <c r="R122" s="16"/>
-      <c r="S122" s="192"/>
-      <c r="T122" s="192"/>
-      <c r="U122" s="192"/>
-      <c r="V122" s="194"/>
+      <c r="S122" s="198"/>
+      <c r="T122" s="198"/>
+      <c r="U122" s="198"/>
+      <c r="V122" s="200"/>
     </row>
     <row r="123" spans="1:22">
-      <c r="A123" s="173" t="s">
-        <v>116</v>
-      </c>
-      <c r="B123" s="174"/>
+      <c r="A123" s="179" t="s">
+        <v>113</v>
+      </c>
+      <c r="B123" s="180"/>
       <c r="D123" s="29"/>
       <c r="H123" s="27"/>
       <c r="I123" s="27"/>
       <c r="J123" s="66"/>
       <c r="K123" s="27"/>
       <c r="L123" s="27"/>
-      <c r="M123" s="190"/>
+      <c r="M123" s="196"/>
       <c r="N123" s="27"/>
       <c r="O123" s="27"/>
       <c r="P123" s="27"/>
@@ -11108,73 +11100,73 @@
       <c r="V123" s="97"/>
     </row>
     <row r="124" spans="1:22">
-      <c r="A124" s="174"/>
-      <c r="B124" s="174"/>
-      <c r="D124" s="176" t="s">
-        <v>159</v>
+      <c r="A124" s="180"/>
+      <c r="B124" s="180"/>
+      <c r="D124" s="182" t="s">
+        <v>156</v>
       </c>
       <c r="E124" s="19"/>
       <c r="F124" s="19"/>
       <c r="G124" s="19"/>
       <c r="H124" s="19"/>
       <c r="I124" s="19"/>
-      <c r="J124" s="187">
+      <c r="J124" s="193">
         <v>20</v>
       </c>
-      <c r="K124" s="187"/>
-      <c r="L124" s="187"/>
-      <c r="M124" s="191"/>
+      <c r="K124" s="193"/>
+      <c r="L124" s="193"/>
+      <c r="M124" s="197"/>
       <c r="N124" s="19" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O124" s="16"/>
       <c r="P124" s="16"/>
       <c r="Q124" s="16"/>
       <c r="R124" s="16"/>
-      <c r="S124" s="192">
+      <c r="S124" s="198">
         <f>J124*2500</f>
         <v>50000</v>
       </c>
-      <c r="T124" s="192"/>
-      <c r="U124" s="192"/>
-      <c r="V124" s="194"/>
+      <c r="T124" s="198"/>
+      <c r="U124" s="198"/>
+      <c r="V124" s="200"/>
     </row>
     <row r="125" spans="1:22">
-      <c r="A125" s="174"/>
-      <c r="B125" s="174"/>
-      <c r="D125" s="176"/>
+      <c r="A125" s="180"/>
+      <c r="B125" s="180"/>
+      <c r="D125" s="182"/>
       <c r="E125" s="19"/>
       <c r="F125" s="19"/>
       <c r="G125" s="19"/>
       <c r="H125" s="19"/>
       <c r="I125" s="19"/>
-      <c r="J125" s="187"/>
-      <c r="K125" s="187"/>
-      <c r="L125" s="187"/>
-      <c r="M125" s="191"/>
+      <c r="J125" s="193"/>
+      <c r="K125" s="193"/>
+      <c r="L125" s="193"/>
+      <c r="M125" s="197"/>
       <c r="N125" s="16"/>
       <c r="O125" s="16"/>
       <c r="P125" s="16"/>
       <c r="Q125" s="16"/>
       <c r="R125" s="16"/>
-      <c r="S125" s="192"/>
-      <c r="T125" s="192"/>
-      <c r="U125" s="192"/>
-      <c r="V125" s="194"/>
+      <c r="S125" s="198"/>
+      <c r="T125" s="198"/>
+      <c r="U125" s="198"/>
+      <c r="V125" s="200"/>
     </row>
     <row r="126" spans="1:22">
-      <c r="A126" s="174"/>
-      <c r="B126" s="174"/>
+      <c r="A126" s="180"/>
+      <c r="B126" s="180"/>
       <c r="D126" s="29"/>
       <c r="J126" s="34"/>
-      <c r="M126" s="191"/>
+      <c r="M126" s="197"/>
       <c r="V126" s="97"/>
     </row>
     <row r="127" spans="1:22">
-      <c r="A127" s="174"/>
-      <c r="B127" s="174"/>
-      <c r="D127" s="176" t="s">
-        <v>160</v>
+      <c r="A127" s="180"/>
+      <c r="B127" s="180"/>
+      <c r="D127" s="182" t="s">
+        <v>157</v>
       </c>
       <c r="E127" s="19"/>
       <c r="F127" s="19"/>
@@ -11186,26 +11178,26 @@
       </c>
       <c r="K127" s="27"/>
       <c r="L127" s="27"/>
-      <c r="M127" s="191"/>
+      <c r="M127" s="197"/>
       <c r="N127" s="19" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O127" s="16"/>
       <c r="P127" s="16"/>
       <c r="Q127" s="16"/>
       <c r="R127" s="16"/>
-      <c r="S127" s="192">
+      <c r="S127" s="198">
         <f>J127*15000</f>
         <v>75000</v>
       </c>
-      <c r="T127" s="192"/>
-      <c r="U127" s="192"/>
-      <c r="V127" s="194"/>
+      <c r="T127" s="198"/>
+      <c r="U127" s="198"/>
+      <c r="V127" s="200"/>
     </row>
     <row r="128" spans="1:22">
-      <c r="A128" s="174"/>
-      <c r="B128" s="174"/>
-      <c r="D128" s="176"/>
+      <c r="A128" s="180"/>
+      <c r="B128" s="180"/>
+      <c r="D128" s="182"/>
       <c r="E128" s="19"/>
       <c r="F128" s="19"/>
       <c r="G128" s="19"/>
@@ -11214,30 +11206,30 @@
       <c r="J128" s="27"/>
       <c r="K128" s="27"/>
       <c r="L128" s="27"/>
-      <c r="M128" s="191"/>
+      <c r="M128" s="197"/>
       <c r="N128" s="16"/>
       <c r="O128" s="16"/>
       <c r="P128" s="16"/>
       <c r="Q128" s="16"/>
       <c r="R128" s="16"/>
-      <c r="S128" s="192"/>
-      <c r="T128" s="192"/>
-      <c r="U128" s="192"/>
-      <c r="V128" s="194"/>
+      <c r="S128" s="198"/>
+      <c r="T128" s="198"/>
+      <c r="U128" s="198"/>
+      <c r="V128" s="200"/>
     </row>
     <row r="129" spans="1:22">
-      <c r="A129" s="174"/>
-      <c r="B129" s="174"/>
+      <c r="A129" s="180"/>
+      <c r="B129" s="180"/>
       <c r="D129" s="29"/>
       <c r="J129" s="34"/>
-      <c r="M129" s="191"/>
+      <c r="M129" s="197"/>
       <c r="V129" s="97"/>
     </row>
     <row r="130" spans="1:22">
-      <c r="A130" s="174"/>
-      <c r="B130" s="174"/>
-      <c r="D130" s="176" t="s">
-        <v>161</v>
+      <c r="A130" s="180"/>
+      <c r="B130" s="180"/>
+      <c r="D130" s="182" t="s">
+        <v>158</v>
       </c>
       <c r="E130" s="19"/>
       <c r="F130" s="19"/>
@@ -11247,50 +11239,50 @@
       <c r="J130" s="25">
         <v>1</v>
       </c>
-      <c r="M130" s="191"/>
+      <c r="M130" s="197"/>
       <c r="N130" s="19" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O130" s="16"/>
       <c r="P130" s="16"/>
       <c r="Q130" s="16"/>
       <c r="R130" s="16"/>
-      <c r="S130" s="192">
+      <c r="S130" s="198">
         <v>35000</v>
       </c>
-      <c r="T130" s="192"/>
-      <c r="U130" s="192"/>
-      <c r="V130" s="194"/>
+      <c r="T130" s="198"/>
+      <c r="U130" s="198"/>
+      <c r="V130" s="200"/>
     </row>
     <row r="131" spans="1:22">
-      <c r="A131" s="174"/>
-      <c r="B131" s="174"/>
-      <c r="D131" s="176"/>
+      <c r="A131" s="180"/>
+      <c r="B131" s="180"/>
+      <c r="D131" s="182"/>
       <c r="E131" s="19"/>
       <c r="F131" s="19"/>
       <c r="G131" s="19"/>
       <c r="H131" s="19"/>
       <c r="I131" s="19"/>
-      <c r="M131" s="191"/>
+      <c r="M131" s="197"/>
       <c r="N131" s="16"/>
       <c r="O131" s="16"/>
       <c r="P131" s="16"/>
       <c r="Q131" s="16"/>
       <c r="R131" s="16"/>
-      <c r="S131" s="192"/>
-      <c r="T131" s="192"/>
-      <c r="U131" s="192"/>
-      <c r="V131" s="194"/>
+      <c r="S131" s="198"/>
+      <c r="T131" s="198"/>
+      <c r="U131" s="198"/>
+      <c r="V131" s="200"/>
     </row>
     <row r="132" spans="4:22">
       <c r="D132" s="29"/>
       <c r="J132" s="34"/>
-      <c r="M132" s="191"/>
+      <c r="M132" s="197"/>
       <c r="V132" s="97"/>
     </row>
     <row r="133" spans="4:22">
-      <c r="D133" s="176" t="s">
-        <v>162</v>
+      <c r="D133" s="182" t="s">
+        <v>159</v>
       </c>
       <c r="E133" s="19"/>
       <c r="F133" s="19"/>
@@ -11300,47 +11292,47 @@
       <c r="J133" s="25">
         <v>0</v>
       </c>
-      <c r="M133" s="191"/>
+      <c r="M133" s="197"/>
       <c r="N133" s="19" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O133" s="16"/>
       <c r="P133" s="16"/>
       <c r="Q133" s="16"/>
       <c r="R133" s="16"/>
-      <c r="S133" s="192">
+      <c r="S133" s="198">
         <v>0</v>
       </c>
-      <c r="T133" s="192"/>
-      <c r="U133" s="192"/>
-      <c r="V133" s="194"/>
+      <c r="T133" s="198"/>
+      <c r="U133" s="198"/>
+      <c r="V133" s="200"/>
     </row>
     <row r="134" spans="4:22">
-      <c r="D134" s="176"/>
+      <c r="D134" s="182"/>
       <c r="E134" s="19"/>
       <c r="F134" s="19"/>
       <c r="G134" s="19"/>
       <c r="H134" s="19"/>
       <c r="I134" s="19"/>
-      <c r="M134" s="191"/>
+      <c r="M134" s="197"/>
       <c r="N134" s="16"/>
       <c r="O134" s="16"/>
       <c r="P134" s="16"/>
       <c r="Q134" s="16"/>
       <c r="R134" s="16"/>
-      <c r="S134" s="192"/>
-      <c r="T134" s="192"/>
-      <c r="U134" s="192"/>
-      <c r="V134" s="194"/>
+      <c r="S134" s="198"/>
+      <c r="T134" s="198"/>
+      <c r="U134" s="198"/>
+      <c r="V134" s="200"/>
     </row>
     <row r="135" spans="4:22">
       <c r="D135" s="29"/>
-      <c r="M135" s="191"/>
+      <c r="M135" s="197"/>
       <c r="V135" s="97"/>
     </row>
     <row r="136" spans="4:22">
-      <c r="D136" s="176" t="s">
-        <v>163</v>
+      <c r="D136" s="182" t="s">
+        <v>160</v>
       </c>
       <c r="E136" s="19"/>
       <c r="F136" s="19"/>
@@ -11350,38 +11342,38 @@
       <c r="J136" s="25">
         <v>0</v>
       </c>
-      <c r="M136" s="191"/>
+      <c r="M136" s="197"/>
       <c r="N136" s="19" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="O136" s="16"/>
       <c r="P136" s="16"/>
       <c r="Q136" s="16"/>
       <c r="R136" s="16"/>
-      <c r="S136" s="192">
+      <c r="S136" s="198">
         <v>0</v>
       </c>
-      <c r="T136" s="192"/>
-      <c r="U136" s="192"/>
-      <c r="V136" s="194"/>
+      <c r="T136" s="198"/>
+      <c r="U136" s="198"/>
+      <c r="V136" s="200"/>
     </row>
     <row r="137" spans="4:22">
-      <c r="D137" s="176"/>
+      <c r="D137" s="182"/>
       <c r="E137" s="19"/>
       <c r="F137" s="19"/>
       <c r="G137" s="19"/>
       <c r="H137" s="19"/>
       <c r="I137" s="19"/>
-      <c r="M137" s="191"/>
+      <c r="M137" s="197"/>
       <c r="N137" s="16"/>
       <c r="O137" s="16"/>
       <c r="P137" s="16"/>
       <c r="Q137" s="16"/>
       <c r="R137" s="16"/>
-      <c r="S137" s="192"/>
-      <c r="T137" s="192"/>
-      <c r="U137" s="192"/>
-      <c r="V137" s="194"/>
+      <c r="S137" s="198"/>
+      <c r="T137" s="198"/>
+      <c r="U137" s="198"/>
+      <c r="V137" s="200"/>
     </row>
     <row r="138" spans="4:22">
       <c r="D138" s="29"/>
@@ -11405,101 +11397,101 @@
       <c r="V138" s="97"/>
     </row>
     <row r="139" ht="16.5" customHeight="1" spans="4:22">
-      <c r="D139" s="235" t="s">
-        <v>164</v>
-      </c>
-      <c r="E139" s="237"/>
-      <c r="F139" s="237"/>
-      <c r="G139" s="237"/>
-      <c r="H139" s="237"/>
-      <c r="I139" s="237"/>
-      <c r="J139" s="237"/>
-      <c r="K139" s="237"/>
-      <c r="L139" s="237"/>
-      <c r="M139" s="237"/>
-      <c r="N139" s="238">
+      <c r="D139" s="238" t="s">
+        <v>161</v>
+      </c>
+      <c r="E139" s="240"/>
+      <c r="F139" s="240"/>
+      <c r="G139" s="240"/>
+      <c r="H139" s="240"/>
+      <c r="I139" s="240"/>
+      <c r="J139" s="240"/>
+      <c r="K139" s="240"/>
+      <c r="L139" s="240"/>
+      <c r="M139" s="240"/>
+      <c r="N139" s="241">
         <f>(S121+S124+S127+S130+S133+S136)/76</f>
         <v>2434.21052631579</v>
       </c>
-      <c r="O139" s="238"/>
-      <c r="P139" s="238"/>
-      <c r="Q139" s="238"/>
-      <c r="R139" s="238"/>
-      <c r="S139" s="237"/>
-      <c r="T139" s="237"/>
-      <c r="U139" s="237"/>
-      <c r="V139" s="241"/>
+      <c r="O139" s="241"/>
+      <c r="P139" s="241"/>
+      <c r="Q139" s="241"/>
+      <c r="R139" s="241"/>
+      <c r="S139" s="240"/>
+      <c r="T139" s="240"/>
+      <c r="U139" s="240"/>
+      <c r="V139" s="244"/>
     </row>
     <row r="140" ht="16.5" customHeight="1" spans="4:22">
-      <c r="D140" s="235"/>
-      <c r="E140" s="237"/>
-      <c r="F140" s="237"/>
-      <c r="G140" s="237"/>
-      <c r="H140" s="237"/>
-      <c r="I140" s="237"/>
-      <c r="J140" s="237"/>
-      <c r="K140" s="237"/>
-      <c r="L140" s="237"/>
-      <c r="M140" s="237"/>
-      <c r="N140" s="238"/>
-      <c r="O140" s="238"/>
-      <c r="P140" s="238"/>
-      <c r="Q140" s="238"/>
-      <c r="R140" s="238"/>
-      <c r="S140" s="237"/>
-      <c r="T140" s="237"/>
-      <c r="U140" s="237"/>
-      <c r="V140" s="241"/>
+      <c r="D140" s="238"/>
+      <c r="E140" s="240"/>
+      <c r="F140" s="240"/>
+      <c r="G140" s="240"/>
+      <c r="H140" s="240"/>
+      <c r="I140" s="240"/>
+      <c r="J140" s="240"/>
+      <c r="K140" s="240"/>
+      <c r="L140" s="240"/>
+      <c r="M140" s="240"/>
+      <c r="N140" s="241"/>
+      <c r="O140" s="241"/>
+      <c r="P140" s="241"/>
+      <c r="Q140" s="241"/>
+      <c r="R140" s="241"/>
+      <c r="S140" s="240"/>
+      <c r="T140" s="240"/>
+      <c r="U140" s="240"/>
+      <c r="V140" s="244"/>
     </row>
     <row r="141" spans="1:22">
-      <c r="A141" s="173" t="s">
-        <v>165</v>
-      </c>
-      <c r="B141" s="174"/>
+      <c r="A141" s="179" t="s">
+        <v>162</v>
+      </c>
+      <c r="B141" s="180"/>
       <c r="D141" s="29"/>
-      <c r="E141" s="183"/>
-      <c r="F141" s="183"/>
-      <c r="G141" s="183"/>
-      <c r="H141" s="183"/>
-      <c r="I141" s="183"/>
-      <c r="J141" s="183"/>
-      <c r="K141" s="183"/>
-      <c r="L141" s="183"/>
-      <c r="M141" s="183"/>
-      <c r="N141" s="183"/>
-      <c r="O141" s="183"/>
-      <c r="P141" s="183"/>
-      <c r="Q141" s="183"/>
-      <c r="R141" s="183"/>
-      <c r="S141" s="183"/>
+      <c r="E141" s="189"/>
+      <c r="F141" s="189"/>
+      <c r="G141" s="189"/>
+      <c r="H141" s="189"/>
+      <c r="I141" s="189"/>
+      <c r="J141" s="189"/>
+      <c r="K141" s="189"/>
+      <c r="L141" s="189"/>
+      <c r="M141" s="189"/>
+      <c r="N141" s="189"/>
+      <c r="O141" s="189"/>
+      <c r="P141" s="189"/>
+      <c r="Q141" s="189"/>
+      <c r="R141" s="189"/>
+      <c r="S141" s="189"/>
       <c r="T141" s="34"/>
       <c r="U141" s="34"/>
       <c r="V141" s="97"/>
     </row>
     <row r="142" spans="1:22">
-      <c r="A142" s="174"/>
-      <c r="B142" s="174"/>
-      <c r="D142" s="236" t="s">
-        <v>166</v>
-      </c>
-      <c r="E142" s="180"/>
-      <c r="F142" s="180"/>
-      <c r="G142" s="180"/>
-      <c r="H142" s="180"/>
-      <c r="I142" s="180"/>
+      <c r="A142" s="180"/>
+      <c r="B142" s="180"/>
+      <c r="D142" s="239" t="s">
+        <v>163</v>
+      </c>
+      <c r="E142" s="186"/>
+      <c r="F142" s="186"/>
+      <c r="G142" s="186"/>
+      <c r="H142" s="186"/>
+      <c r="I142" s="186"/>
       <c r="V142" s="97"/>
     </row>
     <row r="143" spans="1:22">
-      <c r="A143" s="174"/>
-      <c r="B143" s="174"/>
+      <c r="A143" s="180"/>
+      <c r="B143" s="180"/>
       <c r="D143" s="29"/>
       <c r="V143" s="97"/>
     </row>
     <row r="144" spans="1:22">
-      <c r="A144" s="174"/>
-      <c r="B144" s="174"/>
-      <c r="D144" s="176" t="s">
-        <v>167</v>
+      <c r="A144" s="180"/>
+      <c r="B144" s="180"/>
+      <c r="D144" s="182" t="s">
+        <v>164</v>
       </c>
       <c r="E144" s="19"/>
       <c r="F144" s="19"/>
@@ -11509,8 +11501,8 @@
       <c r="J144" s="25">
         <v>10</v>
       </c>
-      <c r="M144" s="239" t="s">
-        <v>168</v>
+      <c r="M144" s="242" t="s">
+        <v>165</v>
       </c>
       <c r="N144" s="19"/>
       <c r="O144" s="19"/>
@@ -11523,15 +11515,15 @@
       <c r="V144" s="97"/>
     </row>
     <row r="145" spans="1:22">
-      <c r="A145" s="174"/>
-      <c r="B145" s="174"/>
-      <c r="D145" s="176"/>
+      <c r="A145" s="180"/>
+      <c r="B145" s="180"/>
+      <c r="D145" s="182"/>
       <c r="E145" s="19"/>
       <c r="F145" s="19"/>
       <c r="G145" s="19"/>
       <c r="H145" s="19"/>
       <c r="I145" s="19"/>
-      <c r="M145" s="239"/>
+      <c r="M145" s="242"/>
       <c r="N145" s="19"/>
       <c r="O145" s="19"/>
       <c r="P145" s="19"/>
@@ -11540,16 +11532,16 @@
       <c r="V145" s="97"/>
     </row>
     <row r="146" spans="1:22">
-      <c r="A146" s="174"/>
-      <c r="B146" s="174"/>
+      <c r="A146" s="180"/>
+      <c r="B146" s="180"/>
       <c r="D146" s="29"/>
       <c r="V146" s="97"/>
     </row>
     <row r="147" spans="1:22">
-      <c r="A147" s="174"/>
-      <c r="B147" s="174"/>
-      <c r="D147" s="176" t="s">
-        <v>169</v>
+      <c r="A147" s="180"/>
+      <c r="B147" s="180"/>
+      <c r="D147" s="182" t="s">
+        <v>166</v>
       </c>
       <c r="E147" s="19"/>
       <c r="F147" s="19"/>
@@ -11560,64 +11552,64 @@
         <f>S144/J144</f>
         <v>3000</v>
       </c>
-      <c r="M147" s="239" t="s">
-        <v>170</v>
+      <c r="M147" s="242" t="s">
+        <v>167</v>
       </c>
       <c r="N147" s="19"/>
       <c r="O147" s="19"/>
       <c r="P147" s="19"/>
       <c r="Q147" s="19"/>
       <c r="R147" s="19"/>
-      <c r="S147" s="240">
+      <c r="S147" s="243">
         <f>J144/(H94+M94)</f>
         <v>0.125</v>
       </c>
-      <c r="T147" s="240"/>
-      <c r="U147" s="240"/>
-      <c r="V147" s="242"/>
+      <c r="T147" s="243"/>
+      <c r="U147" s="243"/>
+      <c r="V147" s="245"/>
     </row>
     <row r="148" spans="1:22">
-      <c r="A148" s="174"/>
-      <c r="B148" s="174"/>
-      <c r="D148" s="176"/>
+      <c r="A148" s="180"/>
+      <c r="B148" s="180"/>
+      <c r="D148" s="182"/>
       <c r="E148" s="19"/>
       <c r="F148" s="19"/>
       <c r="G148" s="19"/>
       <c r="H148" s="19"/>
       <c r="I148" s="19"/>
-      <c r="M148" s="239"/>
+      <c r="M148" s="242"/>
       <c r="N148" s="19"/>
       <c r="O148" s="19"/>
       <c r="P148" s="19"/>
       <c r="Q148" s="19"/>
       <c r="R148" s="19"/>
-      <c r="S148" s="240"/>
-      <c r="T148" s="240"/>
-      <c r="U148" s="240"/>
-      <c r="V148" s="242"/>
+      <c r="S148" s="243"/>
+      <c r="T148" s="243"/>
+      <c r="U148" s="243"/>
+      <c r="V148" s="245"/>
     </row>
     <row r="149" ht="17.55" spans="1:22">
-      <c r="A149" s="174"/>
-      <c r="B149" s="174"/>
-      <c r="D149" s="205"/>
-      <c r="E149" s="184"/>
-      <c r="F149" s="184"/>
-      <c r="G149" s="184"/>
-      <c r="H149" s="184"/>
-      <c r="I149" s="184"/>
-      <c r="J149" s="184"/>
-      <c r="K149" s="184"/>
-      <c r="L149" s="184"/>
-      <c r="M149" s="184"/>
-      <c r="N149" s="184"/>
-      <c r="O149" s="184"/>
-      <c r="P149" s="184"/>
-      <c r="Q149" s="184"/>
-      <c r="R149" s="184"/>
-      <c r="S149" s="184"/>
-      <c r="T149" s="184"/>
-      <c r="U149" s="184"/>
-      <c r="V149" s="218"/>
+      <c r="A149" s="180"/>
+      <c r="B149" s="180"/>
+      <c r="D149" s="211"/>
+      <c r="E149" s="190"/>
+      <c r="F149" s="190"/>
+      <c r="G149" s="190"/>
+      <c r="H149" s="190"/>
+      <c r="I149" s="190"/>
+      <c r="J149" s="190"/>
+      <c r="K149" s="190"/>
+      <c r="L149" s="190"/>
+      <c r="M149" s="190"/>
+      <c r="N149" s="190"/>
+      <c r="O149" s="190"/>
+      <c r="P149" s="190"/>
+      <c r="Q149" s="190"/>
+      <c r="R149" s="190"/>
+      <c r="S149" s="190"/>
+      <c r="T149" s="190"/>
+      <c r="U149" s="190"/>
+      <c r="V149" s="221"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
@@ -11902,7 +11894,6 @@
     <mergeCell ref="N33:O34"/>
     <mergeCell ref="P33:R34"/>
     <mergeCell ref="S33:T34"/>
-    <mergeCell ref="AX10:BB11"/>
     <mergeCell ref="BD10:BH11"/>
     <mergeCell ref="AA10:AE11"/>
     <mergeCell ref="BJ10:BN11"/>
@@ -12053,6 +12044,7 @@
     <mergeCell ref="A8:B9"/>
     <mergeCell ref="N62:S63"/>
     <mergeCell ref="BQ80:CD92"/>
+    <mergeCell ref="AX10:BB11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -12118,21 +12110,21 @@
     <row r="3" ht="23.2" spans="2:23">
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H3" s="14"/>
       <c r="J3" s="4"/>
       <c r="K3" s="5" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="N3" s="14"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="T3" s="14"/>
       <c r="W3" s="5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" ht="5.15" customHeight="1" spans="2:20">
@@ -12146,33 +12138,33 @@
     <row r="5" ht="38.25" customHeight="1" spans="2:25">
       <c r="B5" s="4"/>
       <c r="C5" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H5" s="14"/>
       <c r="J5" s="4"/>
       <c r="K5" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="N5" s="14"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="S5" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="T5" s="14"/>
       <c r="W5" s="6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="Y5" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" ht="6" customHeight="1" spans="2:20">
@@ -12186,41 +12178,41 @@
     <row r="7" ht="109.35" customHeight="1" spans="2:27">
       <c r="B7" s="4"/>
       <c r="C7" s="7" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H7" s="14"/>
       <c r="J7" s="4"/>
       <c r="K7" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="N7" s="14"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="S7" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="T7" s="14"/>
       <c r="U7" s="20"/>
       <c r="V7" s="20"/>
       <c r="W7" s="18" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="Y7" s="18" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AA7" s="18" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" ht="6.85" customHeight="1" spans="2:20">
@@ -12234,33 +12226,33 @@
     <row r="9" ht="84" spans="2:27">
       <c r="B9" s="4"/>
       <c r="C9" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H9" s="14"/>
       <c r="J9" s="4"/>
       <c r="K9" s="7" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M9" s="18" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="N9" s="14"/>
       <c r="P9" s="4"/>
       <c r="T9" s="14"/>
       <c r="W9" s="18" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Y9" s="18" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="AA9" s="18" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10" ht="6.85" customHeight="1" spans="2:20">
@@ -12274,25 +12266,25 @@
     <row r="11" ht="72" spans="2:23">
       <c r="B11" s="4"/>
       <c r="C11" s="8" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H11" s="14"/>
       <c r="J11" s="4"/>
       <c r="K11" s="7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="N11" s="14"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="19"/>
       <c r="T11" s="14"/>
       <c r="W11" s="21" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" ht="17.6" spans="2:29">
@@ -12305,13 +12297,13 @@
       <c r="P12" s="4"/>
       <c r="T12" s="14"/>
       <c r="W12" s="22" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="X12" s="23"/>
       <c r="Y12" s="22"/>
       <c r="Z12" s="23"/>
       <c r="AA12" s="24" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="AB12" s="23"/>
       <c r="AC12" s="16"/>
@@ -12319,61 +12311,61 @@
     <row r="13" spans="2:30">
       <c r="B13" s="4"/>
       <c r="C13" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H13" s="14"/>
       <c r="J13" s="4"/>
       <c r="K13" s="10" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="N13" s="14"/>
       <c r="P13" s="4"/>
       <c r="Q13" s="16" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="T13" s="14"/>
       <c r="W13" s="22" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="X13" s="22" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="Y13" s="22" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Z13" s="23"/>
       <c r="AA13" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="AB13" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="AC13" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="AD13" s="16" t="s">
         <v>205</v>
-      </c>
-      <c r="AB13" s="16" t="s">
-        <v>206</v>
-      </c>
-      <c r="AC13" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="AD13" s="16" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="14" spans="2:28">
       <c r="B14" s="4"/>
       <c r="C14" s="10" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E14" s="16"/>
       <c r="H14" s="14"/>
       <c r="J14" s="4"/>
       <c r="K14" s="10" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="N14" s="14"/>
       <c r="P14" s="4"/>
       <c r="Q14" s="10" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="T14" s="14"/>
       <c r="W14" s="22" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="X14" s="23"/>
       <c r="Y14" s="23"/>
@@ -12400,7 +12392,7 @@
       <c r="S15" s="12"/>
       <c r="T15" s="17"/>
       <c r="W15" s="22" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="X15" s="23"/>
       <c r="Y15" s="23"/>
@@ -12410,7 +12402,7 @@
     </row>
     <row r="16" spans="23:28">
       <c r="W16" s="22" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="X16" s="23"/>
       <c r="Y16" s="23"/>
@@ -12420,7 +12412,7 @@
     </row>
     <row r="17" spans="23:28">
       <c r="W17" s="22" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="X17" s="23"/>
       <c r="Y17" s="23"/>
@@ -12430,7 +12422,7 @@
     </row>
     <row r="18" spans="23:28">
       <c r="W18" s="22" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="X18" s="23"/>
       <c r="Y18" s="23"/>
